--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D397E00F-A932-4278-8453-8FEF4741B170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EF33CC-EC7C-48C8-B124-42C9B9E0F62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -300,25 +300,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>選択したタスクが削除されタスク削除完了画面が表示される</t>
-    <rPh sb="0" eb="2">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="17" eb="21">
-      <t>カンリョウガメン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>清山</t>
     <rPh sb="0" eb="2">
       <t>セイヤマ</t>
@@ -516,62 +497,67 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>選択したタスクがデータベースから削除されタスク削除完了画面が表示される</t>
+    <rPh sb="0" eb="2">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1-1:基本フロー6で利用者が「一覧画面へ」を押下する
+A1-2:システムは削除処理を実行しない
+A1-3:システムはタスク一覧画面を表示する</t>
+    <rPh sb="17" eb="21">
+      <t>イチランガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t>1.従業員がタスク一覧画面を表示する
 2.従業員が削除対象のタスクをラジオボタンで選択する
 3.従業員が「削除」ボタンを押下する
 4.システムが選択されたタスク情報を取得する
 5.システムがタスク削除確認画面を表示する
 6.従業員が「削除」ボタンを押下する
-7.システムが選択されたタスクを削除する
+7. システムが選択されたタスクをデータベースから削除する
 8.システムがタスク削除完了画面を表示する</t>
-    <rPh sb="2" eb="5">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="160" eb="166">
-      <t>サクジョカンリョウガメン</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1:タスク未選択で削除ボタン押下
-A1-1:基本フロー3でタスク未選択を検出
-A1-2:.削除確認画面で「タスクが存在しません」と表示される</t>
-    <rPh sb="33" eb="36">
-      <t>ミセンタク</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ケンシュツ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カクニン</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>E1:削除処理失敗
 E1-1:基本フロー7でシステムがタスク削除処理に失敗する
-E1-2:削除失敗画面を表示する
-E1-3:システムは「システムエラーが発生しました。」を表示する
+E1-2:システムは削除失敗画面を表示する
+E1-3:システムは「システムエラーが発生しました。タスクを削除できませんでした。」を表示する
 E2:データベース接続失敗した場合
-E2-1:システムは削除失敗画面を表示する。
-E2-2:システムは「次のタスクを削除できませんでした」というエラーメッセージを表示する。</t>
-    <rPh sb="45" eb="47">
+E2-1:基本フロー4または7でシステムがデータベース接続に失敗する
+E2-2:システムは削除失敗画面を表示する。
+E2-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
+    <rPh sb="50" eb="52">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="47" eb="49">
+    <rPh sb="52" eb="54">
       <t>シッパイ</t>
     </rPh>
-    <rPh sb="49" eb="51">
+    <rPh sb="54" eb="56">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="52" eb="54">
+    <rPh sb="57" eb="59">
       <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="176" eb="178">
+      <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1453,86 +1439,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1546,16 +1457,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1567,14 +1481,86 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1591,52 +1577,67 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1645,29 +1646,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3112,67 +3098,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="63"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3195,14 +3181,14 @@
       <c r="E8" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3212,26 +3198,26 @@
       <c r="G13" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="43"/>
+      <c r="H13" s="54"/>
       <c r="I13" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="43"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="54"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="79"/>
-      <c r="H14" s="43"/>
+      <c r="H14" s="54"/>
       <c r="I14" s="79"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="43"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="54"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="79"/>
-      <c r="H15" s="43"/>
+      <c r="H15" s="54"/>
       <c r="I15" s="79"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="43"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="54"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3243,10 +3229,10 @@
       <c r="G17" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="63"/>
-      <c r="K17" s="63"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="66"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4260,19 +4246,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4284,192 +4270,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="71">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46183</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="84" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="55"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="56"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="45"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="44" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="58"/>
+    </row>
+    <row r="8" spans="1:10" ht="47.25" customHeight="1">
+      <c r="A8" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="56"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="45"/>
-    </row>
-    <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="44" t="s">
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="58"/>
+    </row>
+    <row r="9" spans="1:10" ht="144" customHeight="1">
+      <c r="A9" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="78" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="58"/>
+    </row>
+    <row r="10" spans="1:10" ht="115.5" customHeight="1">
+      <c r="A10" s="72"/>
+      <c r="B10" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="58"/>
+    </row>
+    <row r="11" spans="1:10" ht="135.75" customHeight="1">
+      <c r="A11" s="73"/>
+      <c r="B11" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="54"/>
+      <c r="D11" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="58"/>
+    </row>
+    <row r="12" spans="1:10" ht="53.25" customHeight="1">
+      <c r="A12" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="56"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="45"/>
-    </row>
-    <row r="9" spans="1:10" ht="144" customHeight="1">
-      <c r="A9" s="93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="85" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="45"/>
-    </row>
-    <row r="10" spans="1:10" ht="115.5" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="96" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="85" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="45"/>
-    </row>
-    <row r="11" spans="1:10" ht="111" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="85" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="45"/>
-    </row>
-    <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="92" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="45"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="70"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="75"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5460,17 +5446,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5479,14 +5462,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5505,19 +5491,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5529,40 +5515,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="74"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6918,19 +6904,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6942,40 +6928,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="74"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8325,19 +8311,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8349,275 +8335,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="71">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="74"/>
+      <c r="I2" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="54" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="97" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="77"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="58"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="65"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="95"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="65"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="95"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="95"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="95"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="95"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="95"/>
+    </row>
+    <row r="14" spans="1:10" ht="24" customHeight="1">
+      <c r="A14" s="65"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="95"/>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1">
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="95"/>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1">
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="95"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="95"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="95"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="95"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="90" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="58"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="55"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="45"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="56"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="58"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="61"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="61"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="61"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="61"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="61"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="61"/>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="62"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="61"/>
-    </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="62"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="61"/>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="62"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="61"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="62"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="61"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="62"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="61"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="62"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="61"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="45"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="43"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="54"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -8630,119 +8616,119 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="64" t="s">
+      <c r="H22" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="45"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="58"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="88"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="56"/>
+      <c r="J23" s="58"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="44" t="s">
+      <c r="F24" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="I23" s="42"/>
-      <c r="J23" s="45"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H24" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="45"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="58"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="38"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="45"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="58"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="43"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="54"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="45"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="58"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="45"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="58"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="43"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="54"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="45"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="58"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="50"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
+      <c r="A29" s="86"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="61"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="70"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="75"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9723,22 +9709,6 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9754,6 +9724,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9776,19 +9762,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9800,287 +9786,287 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="71">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="74"/>
+      <c r="I2" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="54" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="97" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="77"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="58"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="95"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="95"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="95"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="95"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="95"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="98"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="95"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="98"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="99"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="95"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="95"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="95"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="95"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="95"/>
+    </row>
+    <row r="19" spans="1:10" ht="21" customHeight="1">
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="95"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="65"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="95"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="90" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="58"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="56"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="55"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="45"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="56"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="58"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="61"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="61"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="61"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="61"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="61"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="59"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="61"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="62"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="61"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="62"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="61"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="62"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="61"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="62"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="61"/>
-    </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="62"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="61"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="62"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="61"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="45"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="43"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="54"/>
       <c r="I22" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="43"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="15" t="s">
         <v>30</v>
       </c>
@@ -10093,131 +10079,131 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="64" t="s">
+      <c r="H23" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="42"/>
-      <c r="J23" s="45"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="58"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="I24" s="56"/>
+      <c r="J24" s="58"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="B25" s="88"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="44" t="s">
+      <c r="F25" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="45"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="38" t="s">
+      <c r="I25" s="56"/>
+      <c r="J25" s="58"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="17" t="s">
+      <c r="B26" s="88"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E26" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="17" t="s">
+      <c r="G26" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H26" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="42"/>
-      <c r="J25" s="45"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="42"/>
-      <c r="J26" s="45"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="58"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="45"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="58"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="43"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="54"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="45"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="58"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
+      <c r="A29" s="85"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="54"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="45"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="58"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="50"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
+      <c r="A30" s="86"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="61"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="70"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="75"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11198,22 +11184,6 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11229,6 +11199,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11251,19 +11237,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11275,275 +11261,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="71">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="74"/>
+      <c r="I2" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="55"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="45"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="56"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="58"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="61"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="61"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="61"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="61"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="61"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="62"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="61"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="95"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="62"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="61"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="95"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="62"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="61"/>
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="62"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="61"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="95"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="62"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="61"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="62"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="61"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="95"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="45"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="58"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="43"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="54"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -11556,107 +11542,107 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="64" t="s">
+      <c r="H22" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="45"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="58"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="88"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="56"/>
+      <c r="J23" s="58"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="17" t="s">
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="I23" s="42"/>
-      <c r="J23" s="45"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="F24" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>90</v>
-      </c>
       <c r="G24" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H24" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="45"/>
+        <v>84</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="56"/>
+      <c r="J24" s="58"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="41"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="43"/>
+      <c r="A25" s="85"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="54"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="45"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="58"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="43"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="54"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="45"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="58"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="45"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="58"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="50"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="52"/>
+      <c r="A28" s="86"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="61"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="70"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="75"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12637,11 +12623,14 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12658,14 +12647,11 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12685,182 +12671,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="49" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="49" t="s">
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="49" t="s">
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="49" t="s">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="48"/>
-      <c r="S1" s="49" t="s">
+      <c r="R1" s="39"/>
+      <c r="S1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="55"/>
+      <c r="T1" s="77"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="58"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="94"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="61"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="95"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="90"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="108"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="45"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="104"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="84" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="55"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="70"/>
+      <c r="S5" s="70"/>
+      <c r="T5" s="77"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44" t="s">
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="45"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="58"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="44" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="45"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="58"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13059,37 +13045,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="43"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="64" t="s">
+      <c r="D15" s="54"/>
+      <c r="E15" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="64" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="64" t="s">
+      <c r="H15" s="56"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="43"/>
-      <c r="L15" s="64" t="s">
+      <c r="K15" s="54"/>
+      <c r="L15" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="42"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="64" t="s">
+      <c r="M15" s="56"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="43"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="54"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -13101,37 +13087,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="100">
+      <c r="A16" s="105">
         <v>1</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="101" t="s">
+      <c r="B16" s="54"/>
+      <c r="C16" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="101" t="s">
+      <c r="D16" s="54"/>
+      <c r="E16" s="106" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="43"/>
-      <c r="G16" s="106" t="s">
+      <c r="F16" s="54"/>
+      <c r="G16" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="106" t="s">
+      <c r="H16" s="56"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="43"/>
-      <c r="L16" s="104" t="s">
+      <c r="K16" s="54"/>
+      <c r="L16" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="42"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="104" t="s">
+      <c r="M16" s="56"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="43"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="54"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13143,37 +13129,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="100">
+      <c r="A17" s="105">
         <v>2</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="101" t="s">
+      <c r="B17" s="54"/>
+      <c r="C17" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="101" t="s">
+      <c r="D17" s="54"/>
+      <c r="E17" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="106" t="s">
+      <c r="F17" s="54"/>
+      <c r="G17" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="106" t="s">
+      <c r="H17" s="56"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="43"/>
-      <c r="L17" s="104" t="s">
+      <c r="K17" s="54"/>
+      <c r="L17" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="42"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="104" t="s">
+      <c r="M17" s="56"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="43"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="54"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13185,23 +13171,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="43"/>
+      <c r="A18" s="105"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="54"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13213,23 +13199,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="104"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="43"/>
+      <c r="A19" s="105"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="56"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="56"/>
+      <c r="Q19" s="54"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13241,23 +13227,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="43"/>
+      <c r="A20" s="105"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="102"/>
+      <c r="M20" s="56"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="102"/>
+      <c r="P20" s="56"/>
+      <c r="Q20" s="54"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13269,23 +13255,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="104"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="43"/>
+      <c r="A21" s="105"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="102"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="102"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="54"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13297,23 +13283,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="100"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="104"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="43"/>
+      <c r="A22" s="105"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="100"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="102"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="54"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13325,23 +13311,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="100"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="43"/>
+      <c r="A23" s="105"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="102"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="54"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13353,23 +13339,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="100"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="43"/>
+      <c r="A24" s="105"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="102"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="54"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13381,23 +13367,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="100"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="43"/>
+      <c r="A25" s="105"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="102"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="102"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="54"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13409,23 +13395,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="100"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="104"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="43"/>
+      <c r="A26" s="105"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="56"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="54"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13437,23 +13423,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="104"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="43"/>
+      <c r="A27" s="105"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="102"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="54"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13465,23 +13451,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="100"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="104"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="43"/>
+      <c r="A28" s="105"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="106"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="102"/>
+      <c r="P28" s="56"/>
+      <c r="Q28" s="54"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13493,23 +13479,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="100"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="104"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="43"/>
+      <c r="A29" s="105"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="54"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13521,23 +13507,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="100"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="104"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="43"/>
+      <c r="A30" s="105"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="106"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="100"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="54"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13549,23 +13535,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="109"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="109"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="52"/>
+      <c r="A31" s="108"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="61"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14563,62 +14549,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14643,62 +14629,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EF33CC-EC7C-48C8-B124-42C9B9E0F62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BB95BA-6BC1-4D10-8086-1C02FC3F115A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="104">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -516,15 +516,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A1-1:基本フロー6で利用者が「一覧画面へ」を押下する
-A1-2:システムは削除処理を実行しない
-A1-3:システムはタスク一覧画面を表示する</t>
-    <rPh sb="17" eb="21">
-      <t>イチランガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>1.従業員がタスク一覧画面を表示する
 2.従業員が削除対象のタスクをラジオボタンで選択する
 3.従業員が「削除」ボタンを押下する
@@ -558,6 +549,32 @@
     </rPh>
     <rPh sb="176" eb="178">
       <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>福嶋秀幸</t>
+    <rPh sb="0" eb="4">
+      <t>フクシマヒデユキ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1:削除を止めたい場合
+A1-1:基本フロー6で利用者が「一覧画面へ」を押下する
+A1-2:システムは削除処理を実行しない
+A1-3:システムはタスク一覧画面を表示する</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="30" eb="34">
+      <t>イチランガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1439,74 +1456,38 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1526,16 +1507,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1547,20 +1540,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1580,25 +1597,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1619,25 +1618,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1646,14 +1648,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1673,6 +1690,61 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>28016</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>844250</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>138393</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644EF94E-832B-AC7B-3543-4BFD2B8DBB5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1070163" y="953901"/>
+          <a:ext cx="6363146" cy="4159904"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2023,7 +2095,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2522,7 +2594,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3098,67 +3170,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="66"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="66"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3181,14 +3253,14 @@
       <c r="E8" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="66"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="66"/>
-      <c r="M8" s="66"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3198,26 +3270,26 @@
       <c r="G13" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="54"/>
+      <c r="H13" s="62"/>
       <c r="I13" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="56"/>
-      <c r="K13" s="54"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="62"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="79"/>
-      <c r="H14" s="54"/>
+      <c r="H14" s="62"/>
       <c r="I14" s="79"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="54"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="79"/>
-      <c r="H15" s="54"/>
+      <c r="H15" s="62"/>
       <c r="I15" s="79"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="54"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3229,10 +3301,10 @@
       <c r="G17" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4246,19 +4318,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4270,192 +4342,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
         <v>46183</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="50"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="52"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="76" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="77"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="57" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="58"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="57" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="58"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="57" t="s">
+      <c r="B8" s="45"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="58"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" ht="144" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="78" t="s">
+      <c r="C9" s="62"/>
+      <c r="D9" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="46"/>
+    </row>
+    <row r="10" spans="1:10" ht="115.5" customHeight="1">
+      <c r="A10" s="64"/>
+      <c r="B10" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="62"/>
+      <c r="D10" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="46"/>
+    </row>
+    <row r="11" spans="1:10" ht="135.75" customHeight="1">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="62"/>
+      <c r="D11" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="115.5" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="135.75" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="78" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="58"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="46"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="57" t="s">
+      <c r="B12" s="45"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="58"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="75"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5446,6 +5518,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5454,25 +5545,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5494,16 +5566,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5515,40 +5587,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="52"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6907,16 +6979,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6928,40 +7000,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
+        <v>46190</v>
+      </c>
+      <c r="I2" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="52"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8294,6 +8374,7 @@
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8314,16 +8395,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8335,262 +8416,262 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="50"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="97" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="77"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="58"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="92"/>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="94"/>
+      <c r="A7" s="86"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="88"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="95"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="65"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="95"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="89"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="65"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="95"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="89"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="95"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="89"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="95"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="89"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="65"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="95"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="95"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="89"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="65"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="95"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="89"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="65"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="95"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="89"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="95"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="89"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="95"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="89"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="65"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="95"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="58"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="57" t="s">
+      <c r="B21" s="45"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="54"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="62"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
@@ -8599,11 +8680,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="54"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -8616,18 +8697,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="91" t="s">
+      <c r="H22" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="58"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="95"/>
       <c r="D23" s="17" t="s">
         <v>82</v>
       </c>
@@ -8640,18 +8721,18 @@
       <c r="G23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="H23" s="57" t="s">
+      <c r="H23" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="58"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
+      <c r="B24" s="94"/>
+      <c r="C24" s="95"/>
       <c r="D24" s="17" t="s">
         <v>84</v>
       </c>
@@ -8664,71 +8745,71 @@
       <c r="G24" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H24" s="57" t="s">
+      <c r="H24" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="58"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="46"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
+      <c r="A25" s="93"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="95"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="58"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="85"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="54"/>
+      <c r="A26" s="96"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="62"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="58"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="54"/>
+      <c r="A27" s="96"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="58"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="54"/>
+      <c r="A28" s="96"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="62"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="58"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="46"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="86"/>
-      <c r="B29" s="60"/>
-      <c r="C29" s="61"/>
+      <c r="A29" s="97"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="75"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="40"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9709,6 +9790,22 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9724,22 +9821,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9765,16 +9846,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9786,90 +9867,90 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="50"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="97" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="91" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="77"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="58"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="92"/>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="94"/>
+      <c r="A7" s="86"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="88"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="98"/>
@@ -9881,7 +9962,7 @@
       <c r="G8" s="99"/>
       <c r="H8" s="99"/>
       <c r="I8" s="99"/>
-      <c r="J8" s="95"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="98"/>
@@ -9893,7 +9974,7 @@
       <c r="G9" s="99"/>
       <c r="H9" s="99"/>
       <c r="I9" s="99"/>
-      <c r="J9" s="95"/>
+      <c r="J9" s="89"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="98"/>
@@ -9905,7 +9986,7 @@
       <c r="G10" s="99"/>
       <c r="H10" s="99"/>
       <c r="I10" s="99"/>
-      <c r="J10" s="95"/>
+      <c r="J10" s="89"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="98"/>
@@ -9917,7 +9998,7 @@
       <c r="G11" s="99"/>
       <c r="H11" s="99"/>
       <c r="I11" s="99"/>
-      <c r="J11" s="95"/>
+      <c r="J11" s="89"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="98"/>
@@ -9929,7 +10010,7 @@
       <c r="G12" s="99"/>
       <c r="H12" s="99"/>
       <c r="I12" s="99"/>
-      <c r="J12" s="95"/>
+      <c r="J12" s="89"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="98"/>
@@ -9941,7 +10022,7 @@
       <c r="G13" s="99"/>
       <c r="H13" s="99"/>
       <c r="I13" s="99"/>
-      <c r="J13" s="95"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="98"/>
@@ -9953,107 +10034,107 @@
       <c r="G14" s="99"/>
       <c r="H14" s="99"/>
       <c r="I14" s="99"/>
-      <c r="J14" s="95"/>
+      <c r="J14" s="89"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="65"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="95"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="89"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="65"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="95"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="89"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="95"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="89"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="95"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="89"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="65"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="95"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="65"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="95"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="89"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="58"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="46"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="57" t="s">
+      <c r="B22" s="45"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="54"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="62"/>
       <c r="I22" s="15" t="s">
         <v>28</v>
       </c>
@@ -10062,11 +10143,11 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="54"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="62"/>
       <c r="D23" s="15" t="s">
         <v>30</v>
       </c>
@@ -10079,18 +10160,18 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="91" t="s">
+      <c r="H23" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="58"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
+      <c r="B24" s="94"/>
+      <c r="C24" s="95"/>
       <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
@@ -10103,18 +10184,18 @@
       <c r="G24" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="H24" s="57" t="s">
+      <c r="H24" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="58"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="46"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87" t="s">
+      <c r="A25" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
+      <c r="B25" s="94"/>
+      <c r="C25" s="95"/>
       <c r="D25" s="17" t="s">
         <v>85</v>
       </c>
@@ -10127,18 +10208,18 @@
       <c r="G25" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="I25" s="56"/>
-      <c r="J25" s="58"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="87" t="s">
+      <c r="A26" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="89"/>
+      <c r="B26" s="94"/>
+      <c r="C26" s="95"/>
       <c r="D26" s="17" t="s">
         <v>86</v>
       </c>
@@ -10151,59 +10232,59 @@
       <c r="G26" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H26" s="57" t="s">
+      <c r="H26" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="56"/>
-      <c r="J26" s="58"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="54"/>
+      <c r="A27" s="96"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="58"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="54"/>
+      <c r="A28" s="96"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="62"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="58"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="46"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="85"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="54"/>
+      <c r="A29" s="96"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="62"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="58"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="46"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="86"/>
-      <c r="B30" s="60"/>
-      <c r="C30" s="61"/>
+      <c r="A30" s="97"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="49"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="75"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="40"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11184,6 +11265,22 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11199,22 +11296,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11240,16 +11321,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11261,90 +11342,90 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="50"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="97" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="77"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="58"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="92"/>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="94"/>
+      <c r="A7" s="86"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="88"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="98"/>
@@ -11356,7 +11437,7 @@
       <c r="G8" s="99"/>
       <c r="H8" s="99"/>
       <c r="I8" s="99"/>
-      <c r="J8" s="95"/>
+      <c r="J8" s="89"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="98"/>
@@ -11368,7 +11449,7 @@
       <c r="G9" s="99"/>
       <c r="H9" s="99"/>
       <c r="I9" s="99"/>
-      <c r="J9" s="95"/>
+      <c r="J9" s="89"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="98"/>
@@ -11380,7 +11461,7 @@
       <c r="G10" s="99"/>
       <c r="H10" s="99"/>
       <c r="I10" s="99"/>
-      <c r="J10" s="95"/>
+      <c r="J10" s="89"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="98"/>
@@ -11392,131 +11473,131 @@
       <c r="G11" s="99"/>
       <c r="H11" s="99"/>
       <c r="I11" s="99"/>
-      <c r="J11" s="95"/>
+      <c r="J11" s="89"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="95"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="89"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="65"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="95"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="95"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="89"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="65"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="95"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="89"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="65"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="95"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="89"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="95"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="89"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="95"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="89"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="65"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="95"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="58"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="57" t="s">
+      <c r="B21" s="45"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="54"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="62"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
@@ -11525,11 +11606,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="54"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -11542,18 +11623,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="91" t="s">
+      <c r="H22" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="58"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="95"/>
       <c r="D23" s="17" t="s">
         <v>83</v>
       </c>
@@ -11566,18 +11647,18 @@
       <c r="G23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="H23" s="57" t="s">
+      <c r="H23" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="58"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
+      <c r="B24" s="94"/>
+      <c r="C24" s="95"/>
       <c r="D24" s="17" t="s">
         <v>84</v>
       </c>
@@ -11590,59 +11671,59 @@
       <c r="G24" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H24" s="57" t="s">
+      <c r="H24" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="58"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="46"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="85"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="54"/>
+      <c r="A25" s="96"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="62"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="58"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="85"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="54"/>
+      <c r="A26" s="96"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="62"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="58"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="54"/>
+      <c r="A27" s="96"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="58"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="86"/>
-      <c r="B28" s="60"/>
-      <c r="C28" s="61"/>
+      <c r="A28" s="97"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="75"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="40"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12623,14 +12704,11 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12647,11 +12725,14 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12671,182 +12752,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="38" t="s">
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="38" t="s">
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="38" t="s">
+      <c r="P1" s="60"/>
+      <c r="Q1" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="38" t="s">
+      <c r="R1" s="60"/>
+      <c r="S1" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="77"/>
+      <c r="T1" s="43"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="94"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="88"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="95"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="89"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="104"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="108"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="76" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="70"/>
-      <c r="Q5" s="70"/>
-      <c r="R5" s="70"/>
-      <c r="S5" s="70"/>
-      <c r="T5" s="77"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="43"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="57" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="58"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="46"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="57" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="58"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="46"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13045,37 +13126,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="54"/>
+      <c r="B15" s="62"/>
       <c r="C15" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="54"/>
-      <c r="E15" s="91" t="s">
+      <c r="D15" s="62"/>
+      <c r="E15" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="91" t="s">
+      <c r="F15" s="62"/>
+      <c r="G15" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="56"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="91" t="s">
+      <c r="H15" s="45"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="54"/>
-      <c r="L15" s="91" t="s">
+      <c r="K15" s="62"/>
+      <c r="L15" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="56"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="91" t="s">
+      <c r="M15" s="45"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="56"/>
-      <c r="Q15" s="54"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="62"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -13087,37 +13168,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="105">
+      <c r="A16" s="100">
         <v>1</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="106" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="106" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="54"/>
-      <c r="G16" s="100" t="s">
+      <c r="F16" s="62"/>
+      <c r="G16" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="56"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="100" t="s">
+      <c r="H16" s="45"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="54"/>
-      <c r="L16" s="102" t="s">
+      <c r="K16" s="62"/>
+      <c r="L16" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="56"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="102" t="s">
+      <c r="M16" s="45"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="54"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="62"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13129,37 +13210,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="105">
+      <c r="A17" s="100">
         <v>2</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="106" t="s">
+      <c r="B17" s="62"/>
+      <c r="C17" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="106" t="s">
+      <c r="D17" s="62"/>
+      <c r="E17" s="101" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="54"/>
-      <c r="G17" s="100" t="s">
+      <c r="F17" s="62"/>
+      <c r="G17" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="56"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="100" t="s">
+      <c r="H17" s="45"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="54"/>
-      <c r="L17" s="102" t="s">
+      <c r="K17" s="62"/>
+      <c r="L17" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="56"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="102" t="s">
+      <c r="M17" s="45"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="56"/>
-      <c r="Q17" s="54"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="62"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13171,23 +13252,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="105"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="54"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="56"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="56"/>
-      <c r="Q18" s="54"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="62"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13199,23 +13280,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="105"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="56"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="56"/>
-      <c r="Q19" s="54"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="62"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13227,23 +13308,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="105"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="102"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="54"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="62"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13255,23 +13336,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="105"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="54"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="104"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="62"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13283,23 +13364,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="105"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="100"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="56"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="56"/>
-      <c r="Q22" s="54"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="104"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="62"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13311,23 +13392,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="105"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="54"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="62"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13339,23 +13420,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="105"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="54"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="62"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13367,23 +13448,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="105"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="100"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="54"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="54"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="62"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13395,23 +13476,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="105"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="56"/>
-      <c r="Q26" s="54"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="62"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13423,23 +13504,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="105"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="54"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="62"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13451,23 +13532,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="105"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="100"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="54"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="56"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="102"/>
-      <c r="P28" s="56"/>
-      <c r="Q28" s="54"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="106"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="62"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13479,23 +13560,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="105"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="56"/>
-      <c r="Q29" s="54"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="106"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="104"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="62"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13507,23 +13588,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="105"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="100"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="54"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="54"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="106"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="62"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13535,23 +13616,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="108"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="101"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="101"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="60"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="61"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="49"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14549,6 +14630,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14573,118 +14766,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BB95BA-6BC1-4D10-8086-1C02FC3F115A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4A8DC2-8C2F-46A6-BB5F-292125CD34B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,17 +516,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.従業員がタスク一覧画面を表示する
-2.従業員が削除対象のタスクをラジオボタンで選択する
-3.従業員が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得する
-5.システムがタスク削除確認画面を表示する
-6.従業員が「削除」ボタンを押下する
-7. システムが選択されたタスクをデータベースから削除する
-8.システムがタスク削除完了画面を表示する</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>E1:削除処理失敗
 E1-1:基本フロー7でシステムがタスク削除処理に失敗する
 E1-2:システムは削除失敗画面を表示する
@@ -560,10 +549,15 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A1:削除を止めたい場合
+    <t xml:space="preserve">A1:削除を止めたい場合
 A1-1:基本フロー6で利用者が「一覧画面へ」を押下する
 A1-2:システムは削除処理を実行しない
-A1-3:システムはタスク一覧画面を表示する</t>
+A1-3:システムはタスク一覧画面を表示する
+A1:タスク未選択で削除ボタン押下した場合
+A1-1:基本フロー3でシステムはタスク未選択を検出する
+A1-2:システムは一覧画面を再表示する
+A1-3:システムは「削除するタスクを選択してください。」と表示する
+</t>
     <rPh sb="3" eb="5">
       <t>サクジョ</t>
     </rPh>
@@ -575,6 +569,21 @@
     </rPh>
     <rPh sb="30" eb="34">
       <t>イチランガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.従業員がタスク一覧画面を表示する
+2..従業員は削除したいタスクに対応したラジオボタンを選択する
+(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
+3.従業員が「削除」ボタンを押下する
+4.システムが選択されたタスク情報を取得する
+5.システムがタスク削除確認画面を表示する
+6.従業員が「削除」ボタンを押下する
+7. システムが選択されたタスクをデータベースから削除する
+8.システムがタスク削除完了画面を表示する</t>
+    <rPh sb="26" eb="28">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1456,38 +1465,74 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1507,28 +1552,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1540,44 +1573,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1597,7 +1606,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1618,28 +1645,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1648,29 +1672,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3170,67 +3179,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3253,14 +3262,14 @@
       <c r="E8" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -3270,26 +3279,26 @@
       <c r="G13" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="62"/>
+      <c r="H13" s="54"/>
       <c r="I13" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="45"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="54"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="79"/>
-      <c r="H14" s="62"/>
+      <c r="H14" s="54"/>
       <c r="I14" s="79"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="62"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="54"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="79"/>
-      <c r="H15" s="62"/>
+      <c r="H15" s="54"/>
       <c r="I15" s="79"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="62"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="54"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3301,10 +3310,10 @@
       <c r="G17" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="66"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4318,19 +4327,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4342,192 +4351,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46183</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="56"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="44" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="58"/>
     </row>
     <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="44" t="s">
+      <c r="B8" s="56"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="144" customHeight="1">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="47" t="s">
+      <c r="C9" s="54"/>
+      <c r="D9" s="78" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="58"/>
+    </row>
+    <row r="10" spans="1:10" ht="187.5" customHeight="1">
+      <c r="A10" s="72"/>
+      <c r="B10" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="58"/>
+    </row>
+    <row r="11" spans="1:10" ht="135.75" customHeight="1">
+      <c r="A11" s="73"/>
+      <c r="B11" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="54"/>
+      <c r="D11" s="78" t="s">
         <v>100</v>
       </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="46"/>
-    </row>
-    <row r="10" spans="1:10" ht="115.5" customHeight="1">
-      <c r="A10" s="64"/>
-      <c r="B10" s="66" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="46"/>
-    </row>
-    <row r="11" spans="1:10" ht="135.75" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="46"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="44" t="s">
+      <c r="B12" s="56"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="46"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="75"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5518,17 +5527,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5537,14 +5543,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5566,16 +5575,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5587,40 +5596,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="70"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6979,16 +6988,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7000,48 +7009,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46190</v>
       </c>
-      <c r="I2" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="J2" s="70"/>
+      <c r="I2" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8395,16 +8404,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8416,262 +8425,262 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="91" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="86"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="88"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="89"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="89"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="89"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="89"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="89"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="89"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="89"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="95"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="89"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="95"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="89"/>
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="89"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="95"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="89"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="89"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="95"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="85" t="s">
+      <c r="A20" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="58"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="44" t="s">
+      <c r="B21" s="56"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="62"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="54"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
@@ -8680,11 +8689,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="62"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -8697,18 +8706,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="92" t="s">
+      <c r="H22" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="46"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="58"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="94"/>
-      <c r="C23" s="95"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="17" t="s">
         <v>82</v>
       </c>
@@ -8721,18 +8730,18 @@
       <c r="G23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="58"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="95"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="17" t="s">
         <v>84</v>
       </c>
@@ -8745,71 +8754,71 @@
       <c r="G24" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="58"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="93"/>
-      <c r="B25" s="94"/>
-      <c r="C25" s="95"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="58"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="96"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="62"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="54"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="58"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="96"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="62"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="58"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="96"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="62"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="54"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="58"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="97"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="49"/>
+      <c r="A29" s="86"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="61"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="75"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9790,22 +9799,6 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9821,6 +9814,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9846,16 +9855,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9867,90 +9876,90 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="91" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="86"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="88"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="98"/>
@@ -9962,7 +9971,7 @@
       <c r="G8" s="99"/>
       <c r="H8" s="99"/>
       <c r="I8" s="99"/>
-      <c r="J8" s="89"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="98"/>
@@ -9974,7 +9983,7 @@
       <c r="G9" s="99"/>
       <c r="H9" s="99"/>
       <c r="I9" s="99"/>
-      <c r="J9" s="89"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="98"/>
@@ -9986,7 +9995,7 @@
       <c r="G10" s="99"/>
       <c r="H10" s="99"/>
       <c r="I10" s="99"/>
-      <c r="J10" s="89"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="98"/>
@@ -9998,7 +10007,7 @@
       <c r="G11" s="99"/>
       <c r="H11" s="99"/>
       <c r="I11" s="99"/>
-      <c r="J11" s="89"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="98"/>
@@ -10010,7 +10019,7 @@
       <c r="G12" s="99"/>
       <c r="H12" s="99"/>
       <c r="I12" s="99"/>
-      <c r="J12" s="89"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="98"/>
@@ -10022,7 +10031,7 @@
       <c r="G13" s="99"/>
       <c r="H13" s="99"/>
       <c r="I13" s="99"/>
-      <c r="J13" s="89"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="98"/>
@@ -10034,107 +10043,107 @@
       <c r="G14" s="99"/>
       <c r="H14" s="99"/>
       <c r="I14" s="99"/>
-      <c r="J14" s="89"/>
+      <c r="J14" s="95"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="89"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="95"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="89"/>
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="89"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="95"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="89"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="89"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="95"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="53"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="89"/>
+      <c r="A20" s="65"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="95"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="46"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="58"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="44" t="s">
+      <c r="B22" s="56"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="62"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="54"/>
       <c r="I22" s="15" t="s">
         <v>28</v>
       </c>
@@ -10143,11 +10152,11 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="85" t="s">
+      <c r="A23" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="62"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="54"/>
       <c r="D23" s="15" t="s">
         <v>30</v>
       </c>
@@ -10160,18 +10169,18 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="92" t="s">
+      <c r="H23" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="58"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="95"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
@@ -10184,18 +10193,18 @@
       <c r="G24" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="58"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="93" t="s">
+      <c r="A25" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="94"/>
-      <c r="C25" s="95"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="17" t="s">
         <v>85</v>
       </c>
@@ -10208,18 +10217,18 @@
       <c r="G25" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="58"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="93" t="s">
+      <c r="A26" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="94"/>
-      <c r="C26" s="95"/>
+      <c r="B26" s="88"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="17" t="s">
         <v>86</v>
       </c>
@@ -10232,59 +10241,59 @@
       <c r="G26" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="58"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="96"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="62"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="58"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="96"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="62"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="54"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="58"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="96"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="62"/>
+      <c r="A29" s="85"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="54"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="46"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="58"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="97"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="49"/>
+      <c r="A30" s="86"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="61"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="40"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="75"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11265,22 +11274,6 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11296,6 +11289,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11321,16 +11330,16 @@
       <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11342,90 +11351,90 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="91" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="86"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="88"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="98"/>
@@ -11437,7 +11446,7 @@
       <c r="G8" s="99"/>
       <c r="H8" s="99"/>
       <c r="I8" s="99"/>
-      <c r="J8" s="89"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="98"/>
@@ -11449,7 +11458,7 @@
       <c r="G9" s="99"/>
       <c r="H9" s="99"/>
       <c r="I9" s="99"/>
-      <c r="J9" s="89"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="98"/>
@@ -11461,7 +11470,7 @@
       <c r="G10" s="99"/>
       <c r="H10" s="99"/>
       <c r="I10" s="99"/>
-      <c r="J10" s="89"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="98"/>
@@ -11473,131 +11482,131 @@
       <c r="G11" s="99"/>
       <c r="H11" s="99"/>
       <c r="I11" s="99"/>
-      <c r="J11" s="89"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="89"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="89"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="89"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="95"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="89"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="95"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="89"/>
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="89"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="95"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="89"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="89"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="95"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="85" t="s">
+      <c r="A20" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="58"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="44" t="s">
+      <c r="B21" s="56"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="62"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="54"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
@@ -11606,11 +11615,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="62"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="54"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -11623,18 +11632,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="92" t="s">
+      <c r="H22" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="46"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="58"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="94"/>
-      <c r="C23" s="95"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="17" t="s">
         <v>83</v>
       </c>
@@ -11647,18 +11656,18 @@
       <c r="G23" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="58"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="95"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="89"/>
       <c r="D24" s="17" t="s">
         <v>84</v>
       </c>
@@ -11671,59 +11680,59 @@
       <c r="G24" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="58"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="96"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="62"/>
+      <c r="A25" s="85"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="54"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="58"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="96"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="62"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="54"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="58"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="96"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="62"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="54"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="58"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="97"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="49"/>
+      <c r="A28" s="86"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="61"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="40"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="75"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12704,11 +12713,14 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12725,14 +12737,11 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12752,182 +12761,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="73" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="73" t="s">
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="73" t="s">
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="73" t="s">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="60"/>
-      <c r="S1" s="73" t="s">
+      <c r="R1" s="39"/>
+      <c r="S1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="43"/>
+      <c r="T1" s="77"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="88"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="94"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="89"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="95"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="108"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="45"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="104"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="41" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="43"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="70"/>
+      <c r="S5" s="70"/>
+      <c r="T5" s="77"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="44" t="s">
+      <c r="B6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="46"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="58"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="44" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="46"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="58"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13126,37 +13135,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="62"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="92" t="s">
+      <c r="D15" s="54"/>
+      <c r="E15" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="92" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="92" t="s">
+      <c r="H15" s="56"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="62"/>
-      <c r="L15" s="92" t="s">
+      <c r="K15" s="54"/>
+      <c r="L15" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="45"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="92" t="s">
+      <c r="M15" s="56"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="62"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="54"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -13168,37 +13177,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="100">
+      <c r="A16" s="105">
         <v>1</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="101" t="s">
+      <c r="B16" s="54"/>
+      <c r="C16" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="101" t="s">
+      <c r="D16" s="54"/>
+      <c r="E16" s="106" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="106" t="s">
+      <c r="F16" s="54"/>
+      <c r="G16" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="45"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="106" t="s">
+      <c r="H16" s="56"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="62"/>
-      <c r="L16" s="104" t="s">
+      <c r="K16" s="54"/>
+      <c r="L16" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="45"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="104" t="s">
+      <c r="M16" s="56"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="62"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="54"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13210,37 +13219,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="100">
+      <c r="A17" s="105">
         <v>2</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="101" t="s">
+      <c r="B17" s="54"/>
+      <c r="C17" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="101" t="s">
+      <c r="D17" s="54"/>
+      <c r="E17" s="106" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="106" t="s">
+      <c r="F17" s="54"/>
+      <c r="G17" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="106" t="s">
+      <c r="H17" s="56"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="62"/>
-      <c r="L17" s="104" t="s">
+      <c r="K17" s="54"/>
+      <c r="L17" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="45"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="104" t="s">
+      <c r="M17" s="56"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="62"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="54"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13252,23 +13261,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="62"/>
+      <c r="A18" s="105"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="54"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13280,23 +13289,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="104"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="62"/>
+      <c r="A19" s="105"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="56"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="56"/>
+      <c r="Q19" s="54"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13308,23 +13317,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="62"/>
+      <c r="A20" s="105"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="102"/>
+      <c r="M20" s="56"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="102"/>
+      <c r="P20" s="56"/>
+      <c r="Q20" s="54"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13336,23 +13345,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="104"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="62"/>
+      <c r="A21" s="105"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="102"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="102"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="54"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13364,23 +13373,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="100"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="104"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="62"/>
+      <c r="A22" s="105"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="100"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="100"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="102"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="54"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13392,23 +13401,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="100"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="62"/>
+      <c r="A23" s="105"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="56"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="102"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="54"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13420,23 +13429,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="100"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="62"/>
+      <c r="A24" s="105"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="102"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="54"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13448,23 +13457,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="100"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="62"/>
+      <c r="A25" s="105"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="102"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="102"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="54"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13476,23 +13485,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="100"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="104"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="62"/>
+      <c r="A26" s="105"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="100"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="56"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="54"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13504,23 +13513,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="104"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="62"/>
+      <c r="A27" s="105"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="100"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="100"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="102"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="54"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13532,23 +13541,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="100"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="104"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="62"/>
+      <c r="A28" s="105"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="106"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="102"/>
+      <c r="P28" s="56"/>
+      <c r="Q28" s="54"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13560,23 +13569,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="100"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="62"/>
-      <c r="O29" s="104"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="62"/>
+      <c r="A29" s="105"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="100"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="100"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="54"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13588,23 +13597,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="100"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="104"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="62"/>
+      <c r="A30" s="105"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="106"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="100"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="54"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13616,23 +13625,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="109"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="109"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="49"/>
+      <c r="A31" s="108"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="61"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14630,62 +14639,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14710,62 +14719,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4A8DC2-8C2F-46A6-BB5F-292125CD34B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AAC312-85F0-42F7-A62B-4D7853E867B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,34 +272,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク削除確認画面にて、削除するボタンを押下するとタスク削除完了画面に遷移する。</t>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="30" eb="34">
-      <t>カンリョウガメン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>清山</t>
     <rPh sb="0" eb="2">
       <t>セイヤマ</t>
@@ -516,32 +488,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>E1:削除処理失敗
-E1-1:基本フロー7でシステムがタスク削除処理に失敗する
-E1-2:システムは削除失敗画面を表示する
-E1-3:システムは「システムエラーが発生しました。タスクを削除できませんでした。」を表示する
-E2:データベース接続失敗した場合
-E2-1:基本フロー4または7でシステムがデータベース接続に失敗する
-E2-2:システムは削除失敗画面を表示する。
-E2-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
-    <rPh sb="50" eb="52">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="176" eb="178">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>福嶋秀幸</t>
     <rPh sb="0" eb="4">
       <t>フクシマヒデユキ</t>
@@ -549,26 +495,29 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">A1:削除を止めたい場合
-A1-1:基本フロー6で利用者が「一覧画面へ」を押下する
-A1-2:システムは削除処理を実行しない
-A1-3:システムはタスク一覧画面を表示する
+    <t xml:space="preserve">
 A1:タスク未選択で削除ボタン押下した場合
 A1-1:基本フロー3でシステムはタスク未選択を検出する
 A1-2:システムは一覧画面を再表示する
 A1-3:システムは「削除するタスクを選択してください。」と表示する
 </t>
-    <rPh sb="3" eb="5">
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、タスクを削除する。</t>
+    <rPh sb="32" eb="34">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="6" eb="7">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="30" eb="34">
-      <t>イチランガメン</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+E2:データベース接続失敗した場合
+E2-1:基本フロー4または7でシステムがデータベース接続に失敗する
+E2-2:システムは削除失敗画面を表示する。
+E2-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
+    <rPh sb="67" eb="69">
+      <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -581,9 +530,18 @@
 5.システムがタスク削除確認画面を表示する
 6.従業員が「削除」ボタンを押下する
 7. システムが選択されたタスクをデータベースから削除する
-8.システムがタスク削除完了画面を表示する</t>
+8.システムがタスク削除完了画面を表示する
+9.タスクの削除が完了する
+10.従業員はメニュー画面へを押下する
+11.システムはメニュー画面を表示する</t>
     <rPh sb="26" eb="28">
       <t>サクジョ</t>
+    </rPh>
+    <rPh sb="226" eb="228">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="229" eb="231">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1350,7 +1308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1465,74 +1423,38 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1552,41 +1474,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1606,25 +1558,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1645,25 +1579,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1672,14 +1609,134 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3161,85 +3218,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="66"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="66"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="66"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3259,46 +3316,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="66"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="66"/>
-      <c r="M8" s="66"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="54"/>
-      <c r="I13" s="79" t="s">
+      <c r="H13" s="62"/>
+      <c r="I13" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="56"/>
-      <c r="K13" s="54"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="62"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="79"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="54"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="79"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="54"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3307,13 +3364,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="80" t="s">
+      <c r="G17" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="66"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4327,19 +4384,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="142"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4351,192 +4408,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="123"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="137"/>
+      <c r="F2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="137"/>
+      <c r="H2" s="76">
         <v>46183</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="50"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="52"/>
+      <c r="A3" s="123"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="139"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="131"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="126"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="132"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="76" t="s">
+      <c r="B5" s="119"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="77"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="112"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="58"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="115"/>
+      <c r="D6" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="111"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="57" t="s">
+      <c r="B7" s="118"/>
+      <c r="C7" s="115"/>
+      <c r="D7" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="111"/>
+    </row>
+    <row r="8" spans="1:10" ht="47.25" customHeight="1">
+      <c r="A8" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="118"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="58"/>
-    </row>
-    <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="57" t="s">
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="111"/>
+    </row>
+    <row r="9" spans="1:10" ht="173.25" customHeight="1">
+      <c r="A9" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="115"/>
+      <c r="D9" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="108"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="109"/>
+    </row>
+    <row r="10" spans="1:10" ht="152.25" customHeight="1">
+      <c r="A10" s="116"/>
+      <c r="B10" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="115"/>
+      <c r="D10" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="109"/>
+    </row>
+    <row r="11" spans="1:10" ht="135.75" customHeight="1">
+      <c r="A11" s="117"/>
+      <c r="B11" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="115"/>
+      <c r="D11" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="109"/>
+    </row>
+    <row r="12" spans="1:10" ht="53.25" customHeight="1">
+      <c r="A12" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="118"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="144" customHeight="1">
-      <c r="A9" s="71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="54"/>
-      <c r="D9" s="78" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="187.5" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="78" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="135.75" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="59" t="s">
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="111"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="75"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="114"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5527,6 +5584,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5535,25 +5611,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5572,19 +5629,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5596,40 +5653,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="52"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6985,19 +7042,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7009,48 +7066,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="73"/>
+      <c r="H2" s="76">
         <v>46190</v>
       </c>
-      <c r="I2" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="J2" s="50"/>
+      <c r="I2" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="52"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8401,19 +8458,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8425,275 +8482,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="73"/>
+      <c r="H2" s="76">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="50"/>
+      <c r="I2" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="97" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="84"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="86"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="87"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="87"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="87"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="87"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="87"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="87"/>
+    </row>
+    <row r="14" spans="1:10" ht="24" customHeight="1">
+      <c r="A14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="87"/>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1">
+      <c r="A15" s="53"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="87"/>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1">
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="87"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="87"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="87"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="87"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="45"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="77"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="58"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="92"/>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="94"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="95"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="65"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="95"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="65"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="95"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="95"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="95"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="65"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="95"/>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="95"/>
-    </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="65"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="95"/>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="65"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="95"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="95"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="95"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="65"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="95"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="58"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="54"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="62"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="54"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -8706,119 +8763,119 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="91" t="s">
+      <c r="H22" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="58"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="92"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="B24" s="92"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="57" t="s">
+      <c r="F24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="58"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="58"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="46"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="93"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="58"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="85"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="54"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="62"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="58"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="54"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="58"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="54"/>
+      <c r="A28" s="94"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="62"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="58"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="46"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="86"/>
-      <c r="B29" s="60"/>
-      <c r="C29" s="61"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="75"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="40"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9799,6 +9856,22 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9814,22 +9887,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9852,19 +9909,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9876,287 +9933,287 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="73"/>
+      <c r="H2" s="76">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="50"/>
+      <c r="I2" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="97" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="84"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="86"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="96"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="87"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="87"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="96"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="87"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="96"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="87"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="96"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="87"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="96"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="87"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="96"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="87"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="53"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="87"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="87"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="87"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="87"/>
+    </row>
+    <row r="19" spans="1:10" ht="21" customHeight="1">
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="87"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="53"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="87"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="46"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="45"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="77"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="58"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="92"/>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="94"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="95"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="95"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="95"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="95"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="95"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="95"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="95"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="65"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="95"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="65"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="95"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="95"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="95"/>
-    </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="65"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="95"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="65"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="95"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="58"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="54"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="62"/>
       <c r="I22" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="54"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="62"/>
       <c r="D23" s="15" t="s">
         <v>30</v>
       </c>
@@ -10169,131 +10226,131 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="91" t="s">
+      <c r="H23" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="58"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="92"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="45"/>
+      <c r="J24" s="46"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="B25" s="92"/>
+      <c r="C25" s="93"/>
+      <c r="D25" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="57" t="s">
+      <c r="F25" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="58"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="87" t="s">
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="17" t="s">
+      <c r="B26" s="92"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E26" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="17" t="s">
+      <c r="G26" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H26" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="I25" s="56"/>
-      <c r="J25" s="58"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="87" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H26" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="I26" s="56"/>
-      <c r="J26" s="58"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="54"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="58"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="85"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="54"/>
+      <c r="A28" s="94"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="62"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="58"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="46"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="85"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="54"/>
+      <c r="A29" s="94"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="62"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="58"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="46"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="86"/>
-      <c r="B30" s="60"/>
-      <c r="C30" s="61"/>
+      <c r="A30" s="95"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="49"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="75"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="40"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11274,6 +11331,22 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11289,22 +11362,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11327,19 +11384,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11351,275 +11408,275 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="73"/>
+      <c r="H2" s="76">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="50"/>
+      <c r="I2" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="69"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="97" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="77"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="89" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="58"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="92"/>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="94"/>
+      <c r="A7" s="84"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="86"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="95"/>
+      <c r="A8" s="96"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="87"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="99"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
-      <c r="J9" s="95"/>
+      <c r="A9" s="96"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="87"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="95"/>
+      <c r="A10" s="96"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="87"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="95"/>
+      <c r="A11" s="96"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="87"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="95"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="87"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="65"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="95"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="87"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="95"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="87"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="65"/>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="95"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="87"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="65"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="95"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="87"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="95"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="87"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="65"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="95"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="87"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="65"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="95"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="87"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="58"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="54"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="62"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="56"/>
-      <c r="C22" s="54"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -11632,107 +11689,107 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="91" t="s">
+      <c r="H22" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="58"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="92"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" s="45"/>
+      <c r="J23" s="46"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="17" t="s">
+      <c r="B24" s="92"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="58"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="87" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="F24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>89</v>
-      </c>
       <c r="G24" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="58"/>
+        <v>83</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="45"/>
+      <c r="J24" s="46"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="85"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="54"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="62"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="58"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="46"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="85"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="54"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="62"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="58"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="46"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="85"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="54"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="58"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="46"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="86"/>
-      <c r="B28" s="60"/>
-      <c r="C28" s="61"/>
+      <c r="A28" s="95"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="75"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="40"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12713,14 +12770,11 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12737,11 +12791,14 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12761,182 +12818,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="38" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="38" t="s">
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="38" t="s">
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="38" t="s">
+      <c r="P1" s="60"/>
+      <c r="Q1" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="38" t="s">
+      <c r="R1" s="60"/>
+      <c r="S1" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="77"/>
+      <c r="T1" s="43"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="94"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="86"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="66"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="95"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="74"/>
+      <c r="T3" s="87"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="104"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="106"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="76" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="70"/>
-      <c r="Q5" s="70"/>
-      <c r="R5" s="70"/>
-      <c r="S5" s="70"/>
-      <c r="T5" s="77"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="43"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="57" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="58"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="46"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="57" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="58"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="46"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13135,37 +13192,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="107" t="s">
+      <c r="B15" s="62"/>
+      <c r="C15" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="54"/>
-      <c r="E15" s="91" t="s">
+      <c r="D15" s="62"/>
+      <c r="E15" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="54"/>
-      <c r="G15" s="91" t="s">
+      <c r="F15" s="62"/>
+      <c r="G15" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="56"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="91" t="s">
+      <c r="H15" s="45"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="54"/>
-      <c r="L15" s="91" t="s">
+      <c r="K15" s="62"/>
+      <c r="L15" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="56"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="91" t="s">
+      <c r="M15" s="45"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="56"/>
-      <c r="Q15" s="54"/>
+      <c r="P15" s="45"/>
+      <c r="Q15" s="62"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -13177,37 +13234,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="105">
+      <c r="A16" s="98">
         <v>1</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="106" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="106" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="54"/>
-      <c r="G16" s="100" t="s">
+      <c r="F16" s="62"/>
+      <c r="G16" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="56"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="100" t="s">
+      <c r="H16" s="45"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="54"/>
+      <c r="K16" s="62"/>
       <c r="L16" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="56"/>
-      <c r="N16" s="54"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="62"/>
       <c r="O16" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="54"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="62"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13219,37 +13276,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="105">
+      <c r="A17" s="98">
         <v>2</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="106" t="s">
+      <c r="B17" s="62"/>
+      <c r="C17" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="106" t="s">
+      <c r="D17" s="62"/>
+      <c r="E17" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="54"/>
-      <c r="G17" s="100" t="s">
+      <c r="F17" s="62"/>
+      <c r="G17" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="56"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="100" t="s">
+      <c r="H17" s="45"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="54"/>
+      <c r="K17" s="62"/>
       <c r="L17" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="56"/>
-      <c r="N17" s="54"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="62"/>
       <c r="O17" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="56"/>
-      <c r="Q17" s="54"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="62"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13261,23 +13318,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="105"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="54"/>
+      <c r="A18" s="98"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="62"/>
       <c r="L18" s="102"/>
-      <c r="M18" s="56"/>
-      <c r="N18" s="54"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="62"/>
       <c r="O18" s="102"/>
-      <c r="P18" s="56"/>
-      <c r="Q18" s="54"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="62"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13289,23 +13346,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="105"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="54"/>
+      <c r="A19" s="98"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="62"/>
       <c r="L19" s="102"/>
-      <c r="M19" s="56"/>
-      <c r="N19" s="54"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="62"/>
       <c r="O19" s="102"/>
-      <c r="P19" s="56"/>
-      <c r="Q19" s="54"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="62"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13317,23 +13374,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="105"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="106"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="100"/>
-      <c r="K20" s="54"/>
+      <c r="A20" s="98"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="62"/>
       <c r="L20" s="102"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="54"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="62"/>
       <c r="O20" s="102"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="54"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="62"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13345,23 +13402,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="105"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="54"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="62"/>
       <c r="L21" s="102"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="54"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="62"/>
       <c r="O21" s="102"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="54"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="62"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13373,23 +13430,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="105"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="106"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="100"/>
-      <c r="K22" s="54"/>
+      <c r="A22" s="98"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="62"/>
       <c r="L22" s="102"/>
-      <c r="M22" s="56"/>
-      <c r="N22" s="54"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="62"/>
       <c r="O22" s="102"/>
-      <c r="P22" s="56"/>
-      <c r="Q22" s="54"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="62"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13401,23 +13458,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="105"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="54"/>
+      <c r="A23" s="98"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="62"/>
       <c r="L23" s="102"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="54"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="62"/>
       <c r="O23" s="102"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="54"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="62"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13429,23 +13486,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="105"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="54"/>
+      <c r="A24" s="98"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="62"/>
       <c r="L24" s="102"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="54"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="62"/>
       <c r="O24" s="102"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="54"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="62"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13457,23 +13514,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="105"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="100"/>
-      <c r="K25" s="54"/>
+      <c r="A25" s="98"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="62"/>
       <c r="L25" s="102"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="54"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="62"/>
       <c r="O25" s="102"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="54"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="62"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13485,23 +13542,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="105"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="54"/>
+      <c r="A26" s="98"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="62"/>
       <c r="L26" s="102"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="54"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="62"/>
       <c r="O26" s="102"/>
-      <c r="P26" s="56"/>
-      <c r="Q26" s="54"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="62"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13513,23 +13570,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="105"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="100"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="100"/>
-      <c r="K27" s="54"/>
+      <c r="A27" s="98"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="62"/>
       <c r="L27" s="102"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="54"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="62"/>
       <c r="O27" s="102"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="54"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="62"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13541,23 +13598,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="105"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="100"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="54"/>
+      <c r="A28" s="98"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="62"/>
       <c r="L28" s="102"/>
-      <c r="M28" s="56"/>
-      <c r="N28" s="54"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="62"/>
       <c r="O28" s="102"/>
-      <c r="P28" s="56"/>
-      <c r="Q28" s="54"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="62"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13569,23 +13626,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="105"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="100"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="100"/>
-      <c r="K29" s="54"/>
+      <c r="A29" s="98"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="62"/>
       <c r="L29" s="102"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="54"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="62"/>
       <c r="O29" s="102"/>
-      <c r="P29" s="56"/>
-      <c r="Q29" s="54"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="62"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13597,23 +13654,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="105"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="100"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="54"/>
+      <c r="A30" s="98"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="62"/>
       <c r="L30" s="102"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="54"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="62"/>
       <c r="O30" s="102"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="54"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="62"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13625,23 +13682,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="108"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="101"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="101"/>
-      <c r="K31" s="61"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="49"/>
       <c r="L31" s="103"/>
-      <c r="M31" s="60"/>
-      <c r="N31" s="61"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="49"/>
       <c r="O31" s="103"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="61"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="49"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14639,6 +14696,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14663,118 +14832,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AAC312-85F0-42F7-A62B-4D7853E867B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B8367F-771F-4386-AD33-AA29704C7BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -465,10 +465,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>削除したいタスクを担当している従業員がログインしており、一覧表示画面を表示している</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>選択したタスクがデータベースから削除されタスク削除完了画面が表示される</t>
     <rPh sb="0" eb="2">
       <t>センタク</t>
@@ -495,18 +491,20 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">
-A1:タスク未選択で削除ボタン押下した場合
-A1-1:基本フロー3でシステムはタスク未選択を検出する
-A1-2:システムは一覧画面を再表示する
-A1-3:システムは「削除するタスクを選択してください。」と表示する
-</t>
+    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、タスクを削除する。</t>
+    <rPh sb="32" eb="34">
+      <t>サクジョ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、タスクを削除する。</t>
-    <rPh sb="32" eb="34">
-      <t>サクジョ</t>
+    <t>削除対象のタスクを担当している従業員がログインしており、
+一覧表示画面でタスクを１件以上表示している</t>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>ケンイジョウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -516,13 +514,13 @@
 E2-1:基本フロー4または7でシステムがデータベース接続に失敗する
 E2-2:システムは削除失敗画面を表示する。
 E2-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
-    <rPh sb="67" eb="69">
+    <rPh sb="66" eb="68">
       <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.従業員がタスク一覧画面を表示する
+    <t xml:space="preserve">1.従業員がタスク一覧画面を表示する
 2..従業員は削除したいタスクに対応したラジオボタンを選択する
 (従業員本人が担当者でないタスクにはラジオボタンが表示されません)
 3.従業員が「削除」ボタンを押下する
@@ -531,17 +529,77 @@
 6.従業員が「削除」ボタンを押下する
 7. システムが選択されたタスクをデータベースから削除する
 8.システムがタスク削除完了画面を表示する
-9.タスクの削除が完了する
-10.従業員はメニュー画面へを押下する
-11.システムはメニュー画面を表示する</t>
+9.従業員は「メニュー画面へ」を押下する
+10.システムはメニュー画面を表示する
+</t>
     <rPh sb="26" eb="28">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="226" eb="228">
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+A1:タスク未選択で削除ボタン押下した場合
+A1-1:基本フロー3でシステムはタスク未選択を検出する
+A1-2:システムは一覧画面を再表示する
+A1-3:システムは「削除するタスクを選択してください。」と表示する
+A2:削除をキャンセルする場合
+A2-1:基本フロー5で従業員はタスク削除確認画面で「一覧表示へ」を押下する
+A2-2:システムは削除処理を実行しない
+A2-3:システムは一覧表示画面を表示する
+A3：ログインユーザとタスク担当者が不一致の状態で削除実行した場合
+A3-1：基本フロー4でシステムは選択されたタスクの担当者IDを取得する
+A3-2：システムはログイン中のユーザIDと担当者IDを比較する
+A3-3：担当者IDが一致しないことを検出する
+A3-4：システムは削除処理を実行しない
+A3-5：システムは削除失敗画面を表示する
+A3-6：従業員は削除失敗画面で「メニューへ」を押下する
+A3-7：システムはメニュー画面を表示する
+</t>
+    <rPh sb="113" eb="115">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="229" eb="231">
-      <t>カンリョウ</t>
+    <rPh sb="123" eb="125">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="138" eb="141">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="147" eb="151">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="153" eb="157">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="160" eb="162">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="196" eb="200">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="200" eb="202">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="203" eb="205">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="234" eb="236">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="367" eb="373">
+      <t>サクジョシッパイガメン</t>
+    </rPh>
+    <rPh sb="384" eb="387">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="403" eb="405">
+      <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1423,44 +1481,197 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1469,9 +1680,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1486,47 +1694,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1537,28 +1706,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1576,31 +1754,31 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1609,134 +1787,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3218,85 +3276,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="93"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="93"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3316,46 +3374,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="81" t="s">
+      <c r="E8" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="77" t="s">
+      <c r="G13" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="62"/>
-      <c r="I13" s="77" t="s">
+      <c r="H13" s="91"/>
+      <c r="I13" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="45"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="91"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="77"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="62"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="91"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="77"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="62"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="91"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3364,13 +3422,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="78" t="s">
+      <c r="G17" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="93"/>
+      <c r="K17" s="93"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4384,19 +4442,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="142"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="142"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4408,192 +4466,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="72" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="137"/>
-      <c r="F2" s="72" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="137"/>
-      <c r="H2" s="76">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46183</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="131"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="132"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="112"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="61"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="58"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
+    </row>
+    <row r="8" spans="1:10" ht="47.25" customHeight="1">
+      <c r="A8" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+    </row>
+    <row r="9" spans="1:10" ht="220.5" customHeight="1">
+      <c r="A9" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="56"/>
+      <c r="D9" s="86" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="88"/>
+    </row>
+    <row r="10" spans="1:10" ht="302.25" customHeight="1">
+      <c r="A10" s="78"/>
+      <c r="B10" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="86" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="88"/>
+    </row>
+    <row r="11" spans="1:10" ht="135.75" customHeight="1">
+      <c r="A11" s="79"/>
+      <c r="B11" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="86" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="111"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="115"/>
-      <c r="D7" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="111"/>
-    </row>
-    <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="61" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="44" t="s">
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="88"/>
+    </row>
+    <row r="12" spans="1:10" ht="53.25" customHeight="1">
+      <c r="A12" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="111"/>
-    </row>
-    <row r="9" spans="1:10" ht="173.25" customHeight="1">
-      <c r="A9" s="63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="115"/>
-      <c r="D9" s="47" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="109"/>
-    </row>
-    <row r="10" spans="1:10" ht="152.25" customHeight="1">
-      <c r="A10" s="116"/>
-      <c r="B10" s="64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="109"/>
-    </row>
-    <row r="11" spans="1:10" ht="135.75" customHeight="1">
-      <c r="A11" s="117"/>
-      <c r="B11" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="115"/>
-      <c r="D11" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="108"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
-    </row>
-    <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="118"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="111"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="129"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="114"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="82"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5584,17 +5642,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5603,14 +5658,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5629,19 +5687,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5653,40 +5711,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="68"/>
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7042,19 +7100,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7066,48 +7124,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="72" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="72" t="s">
+      <c r="E2" s="110"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="76">
+      <c r="G2" s="110"/>
+      <c r="H2" s="46">
         <v>46190</v>
       </c>
-      <c r="I2" s="65" t="s">
-        <v>99</v>
-      </c>
-      <c r="J2" s="68"/>
+      <c r="I2" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8458,19 +8516,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8482,262 +8540,262 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="72" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="72" t="s">
+      <c r="E2" s="110"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="76">
+      <c r="G2" s="110"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="69"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="129"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="130"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="86"/>
+      <c r="A7" s="124"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="126"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="87"/>
+      <c r="A8" s="104"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="127"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="87"/>
+      <c r="A9" s="104"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="127"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="87"/>
+      <c r="A10" s="104"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="127"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="87"/>
+      <c r="A11" s="104"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="127"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="87"/>
+      <c r="A12" s="104"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="127"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="87"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="127"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="87"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="127"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="87"/>
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="127"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="87"/>
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="127"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="87"/>
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="127"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="87"/>
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="127"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="87"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="127"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="44" t="s">
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="62"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
@@ -8746,11 +8804,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="62"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -8763,18 +8821,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="90" t="s">
+      <c r="H22" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="46"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="17" t="s">
         <v>81</v>
       </c>
@@ -8787,18 +8845,18 @@
       <c r="G23" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="93"/>
+      <c r="B24" s="120"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="17" t="s">
         <v>83</v>
       </c>
@@ -8811,71 +8869,71 @@
       <c r="G24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="93"/>
+      <c r="A25" s="119"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="121"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="94"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="62"/>
+      <c r="A26" s="113"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="94"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="62"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="94"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="62"/>
+      <c r="A28" s="113"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="95"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="49"/>
+      <c r="A29" s="115"/>
+      <c r="B29" s="116"/>
+      <c r="C29" s="117"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="118"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9856,22 +9914,6 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9887,6 +9929,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9909,19 +9967,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -9933,274 +9991,274 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="72" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="72" t="s">
+      <c r="E2" s="110"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="76">
+      <c r="G2" s="110"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="69"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="129"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="130"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="86"/>
+      <c r="A7" s="124"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="126"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="96"/>
-      <c r="B8" s="97"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="87"/>
+      <c r="A8" s="131"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="127"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="96"/>
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="97"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="97"/>
-      <c r="I9" s="97"/>
-      <c r="J9" s="87"/>
+      <c r="A9" s="131"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="127"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="96"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97"/>
-      <c r="H10" s="97"/>
-      <c r="I10" s="97"/>
-      <c r="J10" s="87"/>
+      <c r="A10" s="131"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="127"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="96"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="87"/>
+      <c r="A11" s="131"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="127"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="96"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="97"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="97"/>
-      <c r="I12" s="97"/>
-      <c r="J12" s="87"/>
+      <c r="A12" s="131"/>
+      <c r="B12" s="132"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="132"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="127"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="96"/>
-      <c r="B13" s="97"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
-      <c r="H13" s="97"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="87"/>
+      <c r="A13" s="131"/>
+      <c r="B13" s="132"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="127"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="96"/>
-      <c r="B14" s="97"/>
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="87"/>
+      <c r="A14" s="131"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="127"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="87"/>
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="127"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="87"/>
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="127"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="87"/>
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="127"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="87"/>
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="127"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="87"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="127"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="53"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="87"/>
+      <c r="A20" s="104"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="127"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="46"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="44" t="s">
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="62"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
       <c r="I22" s="15" t="s">
         <v>28</v>
       </c>
@@ -10209,11 +10267,11 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="83" t="s">
+      <c r="A23" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="62"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="91"/>
       <c r="D23" s="15" t="s">
         <v>30</v>
       </c>
@@ -10226,18 +10284,18 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="90" t="s">
+      <c r="H23" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="93"/>
+      <c r="B24" s="120"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="17" t="s">
         <v>81</v>
       </c>
@@ -10250,18 +10308,18 @@
       <c r="G24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="91" t="s">
+      <c r="A25" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="92"/>
-      <c r="C25" s="93"/>
+      <c r="B25" s="120"/>
+      <c r="C25" s="121"/>
       <c r="D25" s="17" t="s">
         <v>84</v>
       </c>
@@ -10274,18 +10332,18 @@
       <c r="G25" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="119" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="93"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="121"/>
       <c r="D26" s="17" t="s">
         <v>85</v>
       </c>
@@ -10298,59 +10356,59 @@
       <c r="G26" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="94"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="62"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="94"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="62"/>
+      <c r="A28" s="113"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="46"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="94"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="62"/>
+      <c r="A29" s="113"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="91"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="46"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="95"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="49"/>
+      <c r="A30" s="115"/>
+      <c r="B30" s="116"/>
+      <c r="C30" s="117"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="40"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="116"/>
+      <c r="J30" s="118"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11331,22 +11389,6 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11362,6 +11404,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11384,19 +11442,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="71" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11408,262 +11466,262 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="72" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="72" t="s">
+      <c r="E2" s="110"/>
+      <c r="F2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="76">
+      <c r="G2" s="110"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="69"/>
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="129"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="84" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="130"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="86"/>
+      <c r="A7" s="124"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="126"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="96"/>
-      <c r="B8" s="97"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="87"/>
+      <c r="A8" s="131"/>
+      <c r="B8" s="132"/>
+      <c r="C8" s="132"/>
+      <c r="D8" s="132"/>
+      <c r="E8" s="132"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="127"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="96"/>
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="97"/>
-      <c r="G9" s="97"/>
-      <c r="H9" s="97"/>
-      <c r="I9" s="97"/>
-      <c r="J9" s="87"/>
+      <c r="A9" s="131"/>
+      <c r="B9" s="132"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="127"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="96"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97"/>
-      <c r="H10" s="97"/>
-      <c r="I10" s="97"/>
-      <c r="J10" s="87"/>
+      <c r="A10" s="131"/>
+      <c r="B10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+      <c r="J10" s="127"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="96"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="87"/>
+      <c r="A11" s="131"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="127"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="87"/>
+      <c r="A12" s="104"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="127"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="87"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="127"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="87"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="127"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="87"/>
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="127"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="87"/>
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="127"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="87"/>
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="127"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="87"/>
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="127"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="87"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="127"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="45"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="44" t="s">
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="62"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
@@ -11672,11 +11730,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="62"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -11689,18 +11747,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="90" t="s">
+      <c r="H22" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="46"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="17" t="s">
         <v>82</v>
       </c>
@@ -11713,18 +11771,18 @@
       <c r="G23" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="I23" s="45"/>
-      <c r="J23" s="46"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="93"/>
+      <c r="B24" s="120"/>
+      <c r="C24" s="121"/>
       <c r="D24" s="17" t="s">
         <v>83</v>
       </c>
@@ -11737,59 +11795,59 @@
       <c r="G24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="45"/>
-      <c r="J24" s="46"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="94"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="62"/>
+      <c r="A25" s="113"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="46"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="94"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="62"/>
+      <c r="A26" s="113"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="46"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="94"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="62"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="46"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="95"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="49"/>
+      <c r="A28" s="115"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="117"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="40"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="116"/>
+      <c r="J28" s="118"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12770,11 +12828,14 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12791,14 +12852,11 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12818,182 +12876,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="71" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="71" t="s">
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="71" t="s">
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="71" t="s">
+      <c r="P1" s="109"/>
+      <c r="Q1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="60"/>
-      <c r="S1" s="71" t="s">
+      <c r="R1" s="109"/>
+      <c r="S1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="43"/>
+      <c r="T1" s="130"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="86"/>
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="110"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="126"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="87"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="127"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="106"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="137"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="128" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="41" t="s">
+      <c r="B5" s="129"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="43"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="129"/>
+      <c r="K5" s="129"/>
+      <c r="L5" s="129"/>
+      <c r="M5" s="129"/>
+      <c r="N5" s="129"/>
+      <c r="O5" s="129"/>
+      <c r="P5" s="129"/>
+      <c r="Q5" s="129"/>
+      <c r="R5" s="129"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="130"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="44" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="46"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
+      <c r="T6" s="114"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="44" t="s">
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="46"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="90"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="90"/>
+      <c r="T7" s="114"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13192,37 +13250,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="83" t="s">
+      <c r="A15" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="105" t="s">
+      <c r="B15" s="91"/>
+      <c r="C15" s="140" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="90" t="s">
+      <c r="D15" s="91"/>
+      <c r="E15" s="123" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="90" t="s">
+      <c r="F15" s="91"/>
+      <c r="G15" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="90" t="s">
+      <c r="H15" s="90"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="123" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="62"/>
-      <c r="L15" s="90" t="s">
+      <c r="K15" s="91"/>
+      <c r="L15" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="45"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="90" t="s">
+      <c r="M15" s="90"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="123" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="62"/>
+      <c r="P15" s="90"/>
+      <c r="Q15" s="91"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -13234,37 +13292,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="98">
+      <c r="A16" s="138">
         <v>1</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="99" t="s">
+      <c r="B16" s="91"/>
+      <c r="C16" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="99" t="s">
+      <c r="D16" s="91"/>
+      <c r="E16" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="104" t="s">
+      <c r="F16" s="91"/>
+      <c r="G16" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="45"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="104" t="s">
+      <c r="H16" s="90"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="62"/>
-      <c r="L16" s="102" t="s">
+      <c r="K16" s="91"/>
+      <c r="L16" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="45"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="102" t="s">
+      <c r="M16" s="90"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="62"/>
+      <c r="P16" s="90"/>
+      <c r="Q16" s="91"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13276,37 +13334,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="98">
+      <c r="A17" s="138">
         <v>2</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="99" t="s">
+      <c r="B17" s="91"/>
+      <c r="C17" s="139" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="99" t="s">
+      <c r="D17" s="91"/>
+      <c r="E17" s="139" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="104" t="s">
+      <c r="F17" s="91"/>
+      <c r="G17" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="104" t="s">
+      <c r="H17" s="90"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="62"/>
-      <c r="L17" s="102" t="s">
+      <c r="K17" s="91"/>
+      <c r="L17" s="135" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="45"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="102" t="s">
+      <c r="M17" s="90"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="62"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="91"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13318,23 +13376,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="98"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="62"/>
+      <c r="A18" s="138"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="133"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13346,23 +13404,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="98"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="104"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="62"/>
+      <c r="A19" s="138"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="135"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="135"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="91"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13374,23 +13432,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="98"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="102"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="62"/>
+      <c r="A20" s="138"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="133"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="135"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="91"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13402,23 +13460,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="98"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="99"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="62"/>
+      <c r="A21" s="138"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="90"/>
+      <c r="Q21" s="91"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13430,23 +13488,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="98"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="62"/>
+      <c r="A22" s="138"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="135"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="91"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13458,23 +13516,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="98"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="62"/>
+      <c r="A23" s="138"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="139"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="91"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13486,23 +13544,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="98"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="62"/>
+      <c r="A24" s="138"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="135"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="135"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="91"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13514,23 +13572,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="98"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="62"/>
+      <c r="A25" s="138"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="135"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="91"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13542,23 +13600,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="98"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="62"/>
+      <c r="A26" s="138"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="133"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="135"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="135"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="91"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13570,23 +13628,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="98"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="62"/>
+      <c r="A27" s="138"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="91"/>
+      <c r="L27" s="135"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="135"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="91"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13598,23 +13656,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="98"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="102"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="62"/>
+      <c r="A28" s="138"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="135"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="135"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="91"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13626,23 +13684,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="98"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="62"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="62"/>
+      <c r="A29" s="138"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="139"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="91"/>
+      <c r="L29" s="135"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="135"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="91"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13654,23 +13712,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="98"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="62"/>
+      <c r="A30" s="138"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="133"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="91"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="135"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="91"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13682,23 +13740,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="100"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="101"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="101"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="49"/>
+      <c r="A31" s="141"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="142"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="134"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="134"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="136"/>
+      <c r="M31" s="116"/>
+      <c r="N31" s="117"/>
+      <c r="O31" s="136"/>
+      <c r="P31" s="116"/>
+      <c r="Q31" s="117"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14696,62 +14754,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14776,62 +14834,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B8367F-771F-4386-AD33-AA29704C7BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DE35C9-A39A-423B-AAFC-CB883FEE6633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -510,35 +510,6 @@
   </si>
   <si>
     <t xml:space="preserve">
-E2:データベース接続失敗した場合
-E2-1:基本フロー4または7でシステムがデータベース接続に失敗する
-E2-2:システムは削除失敗画面を表示する。
-E2-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
-    <rPh sb="66" eb="68">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.従業員がタスク一覧画面を表示する
-2..従業員は削除したいタスクに対応したラジオボタンを選択する
-(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
-3.従業員が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得する
-5.システムがタスク削除確認画面を表示する
-6.従業員が「削除」ボタンを押下する
-7. システムが選択されたタスクをデータベースから削除する
-8.システムがタスク削除完了画面を表示する
-9.従業員は「メニュー画面へ」を押下する
-10.システムはメニュー画面を表示する
-</t>
-    <rPh sb="26" eb="28">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
 A1:タスク未選択で削除ボタン押下した場合
 A1-1:基本フロー3でシステムはタスク未選択を検出する
 A1-2:システムは一覧画面を再表示する
@@ -548,13 +519,12 @@
 A2-2:システムは削除処理を実行しない
 A2-3:システムは一覧表示画面を表示する
 A3：ログインユーザとタスク担当者が不一致の状態で削除実行した場合
-A3-1：基本フロー4でシステムは選択されたタスクの担当者IDを取得する
-A3-2：システムはログイン中のユーザIDと担当者IDを比較する
-A3-3：担当者IDが一致しないことを検出する
-A3-4：システムは削除処理を実行しない
-A3-5：システムは削除失敗画面を表示する
-A3-6：従業員は削除失敗画面で「メニューへ」を押下する
-A3-7：システムはメニュー画面を表示する
+A3-1:基本フロー4でシステムはログイン中のユーザIDと担当者IDを比較する
+A3-2：担当者IDが一致しないことを検出する
+A3-3：システムは削除処理を実行しない
+A3-4：システムは削除失敗画面を表示する
+A3-5：従業員は削除失敗画面で「メニューへ」を押下する
+A3-6：システムはメニュー画面を表示する
 </t>
     <rPh sb="113" eb="115">
       <t>サクジョ</t>
@@ -592,14 +562,59 @@
     <rPh sb="234" eb="236">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="367" eb="373">
+    <rPh sb="337" eb="343">
       <t>サクジョシッパイガメン</t>
     </rPh>
-    <rPh sb="384" eb="387">
+    <rPh sb="354" eb="357">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="403" eb="405">
+    <rPh sb="373" eb="375">
       <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+E2:データベース接続失敗した場合
+E2-1:基本フロー4または8でシステムがデータベース接続に失敗する
+E2-2:システムは削除失敗画面を表示する。
+E2-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
+    <rPh sb="66" eb="68">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.従業員がタスク一覧表示画面を表示する
+2..従業員は削除したいタスクに対応したラジオボタンを選択する
+(一覧表示画面ではログイン確認済み従業員本人が担当者でないタスクにはラジオボタンが表示されません)
+3.従業員が「削除」ボタンを押下する
+4.システムが選択されたタスク情報を取得する
+5.システムがタスク削除確認画面を表示する
+6.従業員が「削除」ボタンを押下する
+7.システムがログインユーザとタスク担当者の一致を確認
+8. システムが選択されたタスクをデータベースから削除する
+9.システムがタスク削除完了画面を表示する
+10.従業員は「メニュー画面へ」を押下する
+11.システムはメニュー画面を表示する
+</t>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="208" eb="210">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="211" eb="213">
+      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1481,67 +1496,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1552,6 +1522,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1598,6 +1577,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1607,32 +1595,59 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1706,38 +1721,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1760,25 +1748,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1787,14 +1787,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4442,19 +4457,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4466,192 +4481,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="81"/>
+      <c r="H2" s="86">
         <v>46183</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="83" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="59" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="61"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="59" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="86" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" ht="220.5" customHeight="1">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="86" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
+    </row>
+    <row r="10" spans="1:10" ht="302.25" customHeight="1">
+      <c r="A10" s="69"/>
+      <c r="B10" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="67"/>
+      <c r="D10" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="49"/>
+    </row>
+    <row r="11" spans="1:10" ht="135.75" customHeight="1">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="67"/>
+      <c r="D11" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="88"/>
-    </row>
-    <row r="10" spans="1:10" ht="302.25" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="88"/>
-    </row>
-    <row r="11" spans="1:10" ht="135.75" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="86" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="88"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="59" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="61"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="82"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5642,6 +5657,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5650,25 +5684,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5692,11 +5707,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -5714,13 +5729,13 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40"/>
+      <c r="D2" s="80"/>
       <c r="E2" s="110"/>
-      <c r="F2" s="40"/>
+      <c r="F2" s="80"/>
       <c r="G2" s="110"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="52"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -7105,11 +7120,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -7127,21 +7142,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="80" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="80" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="86">
         <v>46190</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -8521,11 +8536,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -8543,21 +8558,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="80" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="80" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -8584,23 +8599,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="129"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="129"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="130"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="113" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="90"/>
@@ -8614,16 +8629,16 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="124"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="126"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="104"/>
@@ -8635,7 +8650,7 @@
       <c r="G8" s="93"/>
       <c r="H8" s="93"/>
       <c r="I8" s="93"/>
-      <c r="J8" s="127"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="104"/>
@@ -8647,7 +8662,7 @@
       <c r="G9" s="93"/>
       <c r="H9" s="93"/>
       <c r="I9" s="93"/>
-      <c r="J9" s="127"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="104"/>
@@ -8659,7 +8674,7 @@
       <c r="G10" s="93"/>
       <c r="H10" s="93"/>
       <c r="I10" s="93"/>
-      <c r="J10" s="127"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="104"/>
@@ -8671,7 +8686,7 @@
       <c r="G11" s="93"/>
       <c r="H11" s="93"/>
       <c r="I11" s="93"/>
-      <c r="J11" s="127"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="104"/>
@@ -8683,7 +8698,7 @@
       <c r="G12" s="93"/>
       <c r="H12" s="93"/>
       <c r="I12" s="93"/>
-      <c r="J12" s="127"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="104"/>
@@ -8695,7 +8710,7 @@
       <c r="G13" s="93"/>
       <c r="H13" s="93"/>
       <c r="I13" s="93"/>
-      <c r="J13" s="127"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
       <c r="A14" s="104"/>
@@ -8707,7 +8722,7 @@
       <c r="G14" s="93"/>
       <c r="H14" s="93"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="127"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
       <c r="A15" s="104"/>
@@ -8719,7 +8734,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="127"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
       <c r="A16" s="104"/>
@@ -8731,7 +8746,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="127"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -8743,7 +8758,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="127"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -8755,7 +8770,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="127"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="104"/>
@@ -8767,10 +8782,10 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="127"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="122" t="s">
+      <c r="A20" s="113" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="90"/>
@@ -8784,12 +8799,12 @@
       <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="122" t="s">
+      <c r="A21" s="113" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="90"/>
       <c r="C21" s="91"/>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="44" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="90"/>
@@ -8804,7 +8819,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="122" t="s">
+      <c r="A22" s="113" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="90"/>
@@ -8821,18 +8836,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="122" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="90"/>
       <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="121"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
       <c r="D23" s="17" t="s">
         <v>81</v>
       </c>
@@ -8845,18 +8860,18 @@
       <c r="G23" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="59" t="s">
+      <c r="H23" s="44" t="s">
         <v>92</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="119" t="s">
+      <c r="A24" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="120"/>
-      <c r="C24" s="121"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>83</v>
       </c>
@@ -8869,71 +8884,71 @@
       <c r="G24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="44" t="s">
         <v>93</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="119"/>
-      <c r="B25" s="120"/>
-      <c r="C25" s="121"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="59"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="113"/>
+      <c r="A26" s="126"/>
       <c r="B26" s="90"/>
       <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="59"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="113"/>
+      <c r="A28" s="126"/>
       <c r="B28" s="90"/>
       <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="59"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="90"/>
       <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="115"/>
-      <c r="B29" s="116"/>
-      <c r="C29" s="117"/>
+      <c r="A29" s="127"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="129"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="118"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="130"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9914,6 +9929,22 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9929,22 +9960,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9972,11 +9987,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -9994,21 +10009,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="80" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="80" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -10035,23 +10050,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="129"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="129"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="130"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="113" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="90"/>
@@ -10065,16 +10080,16 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="124"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="126"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="131"/>
@@ -10086,7 +10101,7 @@
       <c r="G8" s="132"/>
       <c r="H8" s="132"/>
       <c r="I8" s="132"/>
-      <c r="J8" s="127"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="131"/>
@@ -10098,7 +10113,7 @@
       <c r="G9" s="132"/>
       <c r="H9" s="132"/>
       <c r="I9" s="132"/>
-      <c r="J9" s="127"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="131"/>
@@ -10110,7 +10125,7 @@
       <c r="G10" s="132"/>
       <c r="H10" s="132"/>
       <c r="I10" s="132"/>
-      <c r="J10" s="127"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="131"/>
@@ -10122,7 +10137,7 @@
       <c r="G11" s="132"/>
       <c r="H11" s="132"/>
       <c r="I11" s="132"/>
-      <c r="J11" s="127"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="131"/>
@@ -10134,7 +10149,7 @@
       <c r="G12" s="132"/>
       <c r="H12" s="132"/>
       <c r="I12" s="132"/>
-      <c r="J12" s="127"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="131"/>
@@ -10146,7 +10161,7 @@
       <c r="G13" s="132"/>
       <c r="H13" s="132"/>
       <c r="I13" s="132"/>
-      <c r="J13" s="127"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="131"/>
@@ -10158,7 +10173,7 @@
       <c r="G14" s="132"/>
       <c r="H14" s="132"/>
       <c r="I14" s="132"/>
-      <c r="J14" s="127"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="104"/>
@@ -10170,7 +10185,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="127"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
       <c r="A16" s="104"/>
@@ -10182,7 +10197,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="127"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -10194,7 +10209,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="127"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -10206,7 +10221,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="127"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
       <c r="A19" s="104"/>
@@ -10218,7 +10233,7 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="127"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="104"/>
@@ -10230,10 +10245,10 @@
       <c r="G20" s="93"/>
       <c r="H20" s="93"/>
       <c r="I20" s="93"/>
-      <c r="J20" s="127"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="122" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="90"/>
@@ -10247,12 +10262,12 @@
       <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="122" t="s">
+      <c r="A22" s="113" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="90"/>
       <c r="C22" s="91"/>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="44" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="90"/>
@@ -10267,7 +10282,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="122" t="s">
+      <c r="A23" s="113" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="90"/>
@@ -10284,18 +10299,18 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="122" t="s">
         <v>20</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="119" t="s">
+      <c r="A24" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="120"/>
-      <c r="C24" s="121"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>81</v>
       </c>
@@ -10308,18 +10323,18 @@
       <c r="G24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="44" t="s">
         <v>89</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="119" t="s">
+      <c r="A25" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="120"/>
-      <c r="C25" s="121"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
       <c r="D25" s="17" t="s">
         <v>84</v>
       </c>
@@ -10332,18 +10347,18 @@
       <c r="G25" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="59" t="s">
+      <c r="H25" s="44" t="s">
         <v>90</v>
       </c>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="119" t="s">
+      <c r="A26" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="120"/>
-      <c r="C26" s="121"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="125"/>
       <c r="D26" s="17" t="s">
         <v>85</v>
       </c>
@@ -10356,59 +10371,59 @@
       <c r="G26" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="59" t="s">
+      <c r="H26" s="44" t="s">
         <v>91</v>
       </c>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="113"/>
+      <c r="A28" s="126"/>
       <c r="B28" s="90"/>
       <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="59"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="90"/>
       <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="113"/>
+      <c r="A29" s="126"/>
       <c r="B29" s="90"/>
       <c r="C29" s="91"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="59"/>
+      <c r="H29" s="44"/>
       <c r="I29" s="90"/>
       <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="115"/>
-      <c r="B30" s="116"/>
-      <c r="C30" s="117"/>
+      <c r="A30" s="127"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="129"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="116"/>
-      <c r="J30" s="118"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="128"/>
+      <c r="J30" s="130"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11389,6 +11404,22 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11404,22 +11435,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11447,11 +11462,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -11469,21 +11484,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="80" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="80" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -11510,23 +11525,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="129"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="129"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="130"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="113" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="90"/>
@@ -11540,16 +11555,16 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="124"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="126"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="131"/>
@@ -11561,7 +11576,7 @@
       <c r="G8" s="132"/>
       <c r="H8" s="132"/>
       <c r="I8" s="132"/>
-      <c r="J8" s="127"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="131"/>
@@ -11573,7 +11588,7 @@
       <c r="G9" s="132"/>
       <c r="H9" s="132"/>
       <c r="I9" s="132"/>
-      <c r="J9" s="127"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="131"/>
@@ -11585,7 +11600,7 @@
       <c r="G10" s="132"/>
       <c r="H10" s="132"/>
       <c r="I10" s="132"/>
-      <c r="J10" s="127"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="131"/>
@@ -11597,7 +11612,7 @@
       <c r="G11" s="132"/>
       <c r="H11" s="132"/>
       <c r="I11" s="132"/>
-      <c r="J11" s="127"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="104"/>
@@ -11609,7 +11624,7 @@
       <c r="G12" s="93"/>
       <c r="H12" s="93"/>
       <c r="I12" s="93"/>
-      <c r="J12" s="127"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="104"/>
@@ -11621,7 +11636,7 @@
       <c r="G13" s="93"/>
       <c r="H13" s="93"/>
       <c r="I13" s="93"/>
-      <c r="J13" s="127"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="104"/>
@@ -11633,7 +11648,7 @@
       <c r="G14" s="93"/>
       <c r="H14" s="93"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="127"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="104"/>
@@ -11645,7 +11660,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="127"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
       <c r="A16" s="104"/>
@@ -11657,7 +11672,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="127"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -11669,7 +11684,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="127"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -11681,7 +11696,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="127"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="104"/>
@@ -11693,10 +11708,10 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="127"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="122" t="s">
+      <c r="A20" s="113" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="90"/>
@@ -11710,12 +11725,12 @@
       <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="122" t="s">
+      <c r="A21" s="113" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="90"/>
       <c r="C21" s="91"/>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="44" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="90"/>
@@ -11730,7 +11745,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="122" t="s">
+      <c r="A22" s="113" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="90"/>
@@ -11747,18 +11762,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="122" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="90"/>
       <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="119" t="s">
+      <c r="A23" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="120"/>
-      <c r="C23" s="121"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
       <c r="D23" s="17" t="s">
         <v>82</v>
       </c>
@@ -11771,18 +11786,18 @@
       <c r="G23" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="59" t="s">
+      <c r="H23" s="44" t="s">
         <v>95</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="119" t="s">
+      <c r="A24" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="120"/>
-      <c r="C24" s="121"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>83</v>
       </c>
@@ -11795,59 +11810,59 @@
       <c r="G24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="44" t="s">
         <v>94</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="113"/>
+      <c r="A25" s="126"/>
       <c r="B25" s="90"/>
       <c r="C25" s="91"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="59"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="113"/>
+      <c r="A26" s="126"/>
       <c r="B26" s="90"/>
       <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="59"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="115"/>
-      <c r="B28" s="116"/>
-      <c r="C28" s="117"/>
+      <c r="A28" s="127"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="129"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="80"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="118"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="130"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12828,14 +12843,11 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12852,11 +12864,14 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12876,7 +12891,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="53" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="102"/>
@@ -12884,30 +12899,30 @@
       <c r="D1" s="102"/>
       <c r="E1" s="102"/>
       <c r="F1" s="103"/>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
       <c r="J1" s="109"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
       <c r="N1" s="109"/>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="78" t="s">
         <v>8</v>
       </c>
       <c r="P1" s="109"/>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="78" t="s">
         <v>9</v>
       </c>
       <c r="R1" s="109"/>
-      <c r="S1" s="38" t="s">
+      <c r="S1" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="130"/>
+      <c r="T1" s="121"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="104"/>
@@ -12916,20 +12931,20 @@
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
       <c r="F2" s="105"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
       <c r="J2" s="110"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
       <c r="N2" s="110"/>
-      <c r="O2" s="40"/>
+      <c r="O2" s="80"/>
       <c r="P2" s="110"/>
-      <c r="Q2" s="40"/>
+      <c r="Q2" s="80"/>
       <c r="R2" s="110"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="126"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="117"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -12951,7 +12966,7 @@
       <c r="Q3" s="111"/>
       <c r="R3" s="105"/>
       <c r="S3" s="111"/>
-      <c r="T3" s="127"/>
+      <c r="T3" s="118"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="106"/>
@@ -12973,36 +12988,36 @@
       <c r="Q4" s="112"/>
       <c r="R4" s="108"/>
       <c r="S4" s="112"/>
-      <c r="T4" s="137"/>
+      <c r="T4" s="141"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="129"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="129"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
       <c r="F5" s="109"/>
-      <c r="G5" s="83" t="s">
+      <c r="G5" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="129"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="129"/>
-      <c r="K5" s="129"/>
-      <c r="L5" s="129"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="129"/>
-      <c r="O5" s="129"/>
-      <c r="P5" s="129"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="129"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="130"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="121"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="122" t="s">
+      <c r="A6" s="113" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="90"/>
@@ -13010,7 +13025,7 @@
       <c r="D6" s="90"/>
       <c r="E6" s="90"/>
       <c r="F6" s="91"/>
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="44" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="90"/>
@@ -13028,7 +13043,7 @@
       <c r="T6" s="114"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="122" t="s">
+      <c r="A7" s="113" t="s">
         <v>38</v>
       </c>
       <c r="B7" s="90"/>
@@ -13036,7 +13051,7 @@
       <c r="D7" s="90"/>
       <c r="E7" s="90"/>
       <c r="F7" s="91"/>
-      <c r="G7" s="59" t="s">
+      <c r="G7" s="44" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="90"/>
@@ -13250,7 +13265,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="122" t="s">
+      <c r="A15" s="113" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="91"/>
@@ -13258,25 +13273,25 @@
         <v>40</v>
       </c>
       <c r="D15" s="91"/>
-      <c r="E15" s="123" t="s">
+      <c r="E15" s="122" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="91"/>
-      <c r="G15" s="123" t="s">
+      <c r="G15" s="122" t="s">
         <v>48</v>
       </c>
       <c r="H15" s="90"/>
       <c r="I15" s="91"/>
-      <c r="J15" s="123" t="s">
+      <c r="J15" s="122" t="s">
         <v>49</v>
       </c>
       <c r="K15" s="91"/>
-      <c r="L15" s="123" t="s">
+      <c r="L15" s="122" t="s">
         <v>50</v>
       </c>
       <c r="M15" s="90"/>
       <c r="N15" s="91"/>
-      <c r="O15" s="123" t="s">
+      <c r="O15" s="122" t="s">
         <v>51</v>
       </c>
       <c r="P15" s="90"/>
@@ -13292,33 +13307,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="138">
+      <c r="A16" s="133">
         <v>1</v>
       </c>
       <c r="B16" s="91"/>
-      <c r="C16" s="139" t="s">
+      <c r="C16" s="134" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="91"/>
-      <c r="E16" s="139" t="s">
+      <c r="E16" s="134" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="91"/>
-      <c r="G16" s="133" t="s">
+      <c r="G16" s="139" t="s">
         <v>57</v>
       </c>
       <c r="H16" s="90"/>
       <c r="I16" s="91"/>
-      <c r="J16" s="133" t="s">
+      <c r="J16" s="139" t="s">
         <v>58</v>
       </c>
       <c r="K16" s="91"/>
-      <c r="L16" s="135" t="s">
+      <c r="L16" s="137" t="s">
         <v>59</v>
       </c>
       <c r="M16" s="90"/>
       <c r="N16" s="91"/>
-      <c r="O16" s="135" t="s">
+      <c r="O16" s="137" t="s">
         <v>60</v>
       </c>
       <c r="P16" s="90"/>
@@ -13334,33 +13349,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="138">
+      <c r="A17" s="133">
         <v>2</v>
       </c>
       <c r="B17" s="91"/>
-      <c r="C17" s="139" t="s">
+      <c r="C17" s="134" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="91"/>
-      <c r="E17" s="139" t="s">
+      <c r="E17" s="134" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="91"/>
-      <c r="G17" s="133" t="s">
+      <c r="G17" s="139" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="133" t="s">
+      <c r="J17" s="139" t="s">
         <v>64</v>
       </c>
       <c r="K17" s="91"/>
-      <c r="L17" s="135" t="s">
+      <c r="L17" s="137" t="s">
         <v>65</v>
       </c>
       <c r="M17" s="90"/>
       <c r="N17" s="91"/>
-      <c r="O17" s="135" t="s">
+      <c r="O17" s="137" t="s">
         <v>66</v>
       </c>
       <c r="P17" s="90"/>
@@ -13376,21 +13391,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="138"/>
+      <c r="A18" s="133"/>
       <c r="B18" s="91"/>
-      <c r="C18" s="139"/>
+      <c r="C18" s="134"/>
       <c r="D18" s="91"/>
-      <c r="E18" s="139"/>
+      <c r="E18" s="134"/>
       <c r="F18" s="91"/>
-      <c r="G18" s="133"/>
+      <c r="G18" s="139"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="133"/>
+      <c r="J18" s="139"/>
       <c r="K18" s="91"/>
-      <c r="L18" s="135"/>
+      <c r="L18" s="137"/>
       <c r="M18" s="90"/>
       <c r="N18" s="91"/>
-      <c r="O18" s="135"/>
+      <c r="O18" s="137"/>
       <c r="P18" s="90"/>
       <c r="Q18" s="91"/>
       <c r="R18" s="33"/>
@@ -13404,21 +13419,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="138"/>
+      <c r="A19" s="133"/>
       <c r="B19" s="91"/>
-      <c r="C19" s="139"/>
+      <c r="C19" s="134"/>
       <c r="D19" s="91"/>
-      <c r="E19" s="139"/>
+      <c r="E19" s="134"/>
       <c r="F19" s="91"/>
-      <c r="G19" s="133"/>
+      <c r="G19" s="139"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91"/>
-      <c r="J19" s="133"/>
+      <c r="J19" s="139"/>
       <c r="K19" s="91"/>
-      <c r="L19" s="135"/>
+      <c r="L19" s="137"/>
       <c r="M19" s="90"/>
       <c r="N19" s="91"/>
-      <c r="O19" s="135"/>
+      <c r="O19" s="137"/>
       <c r="P19" s="90"/>
       <c r="Q19" s="91"/>
       <c r="R19" s="33"/>
@@ -13432,21 +13447,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="138"/>
+      <c r="A20" s="133"/>
       <c r="B20" s="91"/>
-      <c r="C20" s="139"/>
+      <c r="C20" s="134"/>
       <c r="D20" s="91"/>
-      <c r="E20" s="139"/>
+      <c r="E20" s="134"/>
       <c r="F20" s="91"/>
-      <c r="G20" s="133"/>
+      <c r="G20" s="139"/>
       <c r="H20" s="90"/>
       <c r="I20" s="91"/>
-      <c r="J20" s="133"/>
+      <c r="J20" s="139"/>
       <c r="K20" s="91"/>
-      <c r="L20" s="135"/>
+      <c r="L20" s="137"/>
       <c r="M20" s="90"/>
       <c r="N20" s="91"/>
-      <c r="O20" s="135"/>
+      <c r="O20" s="137"/>
       <c r="P20" s="90"/>
       <c r="Q20" s="91"/>
       <c r="R20" s="33"/>
@@ -13460,21 +13475,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="138"/>
+      <c r="A21" s="133"/>
       <c r="B21" s="91"/>
-      <c r="C21" s="139"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="91"/>
-      <c r="E21" s="139"/>
+      <c r="E21" s="134"/>
       <c r="F21" s="91"/>
-      <c r="G21" s="133"/>
+      <c r="G21" s="139"/>
       <c r="H21" s="90"/>
       <c r="I21" s="91"/>
-      <c r="J21" s="133"/>
+      <c r="J21" s="139"/>
       <c r="K21" s="91"/>
-      <c r="L21" s="135"/>
+      <c r="L21" s="137"/>
       <c r="M21" s="90"/>
       <c r="N21" s="91"/>
-      <c r="O21" s="135"/>
+      <c r="O21" s="137"/>
       <c r="P21" s="90"/>
       <c r="Q21" s="91"/>
       <c r="R21" s="33"/>
@@ -13488,21 +13503,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="138"/>
+      <c r="A22" s="133"/>
       <c r="B22" s="91"/>
-      <c r="C22" s="139"/>
+      <c r="C22" s="134"/>
       <c r="D22" s="91"/>
-      <c r="E22" s="139"/>
+      <c r="E22" s="134"/>
       <c r="F22" s="91"/>
-      <c r="G22" s="133"/>
+      <c r="G22" s="139"/>
       <c r="H22" s="90"/>
       <c r="I22" s="91"/>
-      <c r="J22" s="133"/>
+      <c r="J22" s="139"/>
       <c r="K22" s="91"/>
-      <c r="L22" s="135"/>
+      <c r="L22" s="137"/>
       <c r="M22" s="90"/>
       <c r="N22" s="91"/>
-      <c r="O22" s="135"/>
+      <c r="O22" s="137"/>
       <c r="P22" s="90"/>
       <c r="Q22" s="91"/>
       <c r="R22" s="33"/>
@@ -13516,21 +13531,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="138"/>
+      <c r="A23" s="133"/>
       <c r="B23" s="91"/>
-      <c r="C23" s="139"/>
+      <c r="C23" s="134"/>
       <c r="D23" s="91"/>
-      <c r="E23" s="139"/>
+      <c r="E23" s="134"/>
       <c r="F23" s="91"/>
-      <c r="G23" s="133"/>
+      <c r="G23" s="139"/>
       <c r="H23" s="90"/>
       <c r="I23" s="91"/>
-      <c r="J23" s="133"/>
+      <c r="J23" s="139"/>
       <c r="K23" s="91"/>
-      <c r="L23" s="135"/>
+      <c r="L23" s="137"/>
       <c r="M23" s="90"/>
       <c r="N23" s="91"/>
-      <c r="O23" s="135"/>
+      <c r="O23" s="137"/>
       <c r="P23" s="90"/>
       <c r="Q23" s="91"/>
       <c r="R23" s="33"/>
@@ -13544,21 +13559,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="138"/>
+      <c r="A24" s="133"/>
       <c r="B24" s="91"/>
-      <c r="C24" s="139"/>
+      <c r="C24" s="134"/>
       <c r="D24" s="91"/>
-      <c r="E24" s="139"/>
+      <c r="E24" s="134"/>
       <c r="F24" s="91"/>
-      <c r="G24" s="133"/>
+      <c r="G24" s="139"/>
       <c r="H24" s="90"/>
       <c r="I24" s="91"/>
-      <c r="J24" s="133"/>
+      <c r="J24" s="139"/>
       <c r="K24" s="91"/>
-      <c r="L24" s="135"/>
+      <c r="L24" s="137"/>
       <c r="M24" s="90"/>
       <c r="N24" s="91"/>
-      <c r="O24" s="135"/>
+      <c r="O24" s="137"/>
       <c r="P24" s="90"/>
       <c r="Q24" s="91"/>
       <c r="R24" s="33"/>
@@ -13572,21 +13587,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="138"/>
+      <c r="A25" s="133"/>
       <c r="B25" s="91"/>
-      <c r="C25" s="139"/>
+      <c r="C25" s="134"/>
       <c r="D25" s="91"/>
-      <c r="E25" s="139"/>
+      <c r="E25" s="134"/>
       <c r="F25" s="91"/>
-      <c r="G25" s="133"/>
+      <c r="G25" s="139"/>
       <c r="H25" s="90"/>
       <c r="I25" s="91"/>
-      <c r="J25" s="133"/>
+      <c r="J25" s="139"/>
       <c r="K25" s="91"/>
-      <c r="L25" s="135"/>
+      <c r="L25" s="137"/>
       <c r="M25" s="90"/>
       <c r="N25" s="91"/>
-      <c r="O25" s="135"/>
+      <c r="O25" s="137"/>
       <c r="P25" s="90"/>
       <c r="Q25" s="91"/>
       <c r="R25" s="33"/>
@@ -13600,21 +13615,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="138"/>
+      <c r="A26" s="133"/>
       <c r="B26" s="91"/>
-      <c r="C26" s="139"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="91"/>
-      <c r="E26" s="139"/>
+      <c r="E26" s="134"/>
       <c r="F26" s="91"/>
-      <c r="G26" s="133"/>
+      <c r="G26" s="139"/>
       <c r="H26" s="90"/>
       <c r="I26" s="91"/>
-      <c r="J26" s="133"/>
+      <c r="J26" s="139"/>
       <c r="K26" s="91"/>
-      <c r="L26" s="135"/>
+      <c r="L26" s="137"/>
       <c r="M26" s="90"/>
       <c r="N26" s="91"/>
-      <c r="O26" s="135"/>
+      <c r="O26" s="137"/>
       <c r="P26" s="90"/>
       <c r="Q26" s="91"/>
       <c r="R26" s="33"/>
@@ -13628,21 +13643,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="138"/>
+      <c r="A27" s="133"/>
       <c r="B27" s="91"/>
-      <c r="C27" s="139"/>
+      <c r="C27" s="134"/>
       <c r="D27" s="91"/>
-      <c r="E27" s="139"/>
+      <c r="E27" s="134"/>
       <c r="F27" s="91"/>
-      <c r="G27" s="133"/>
+      <c r="G27" s="139"/>
       <c r="H27" s="90"/>
       <c r="I27" s="91"/>
-      <c r="J27" s="133"/>
+      <c r="J27" s="139"/>
       <c r="K27" s="91"/>
-      <c r="L27" s="135"/>
+      <c r="L27" s="137"/>
       <c r="M27" s="90"/>
       <c r="N27" s="91"/>
-      <c r="O27" s="135"/>
+      <c r="O27" s="137"/>
       <c r="P27" s="90"/>
       <c r="Q27" s="91"/>
       <c r="R27" s="33"/>
@@ -13656,21 +13671,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="138"/>
+      <c r="A28" s="133"/>
       <c r="B28" s="91"/>
-      <c r="C28" s="139"/>
+      <c r="C28" s="134"/>
       <c r="D28" s="91"/>
-      <c r="E28" s="139"/>
+      <c r="E28" s="134"/>
       <c r="F28" s="91"/>
-      <c r="G28" s="133"/>
+      <c r="G28" s="139"/>
       <c r="H28" s="90"/>
       <c r="I28" s="91"/>
-      <c r="J28" s="133"/>
+      <c r="J28" s="139"/>
       <c r="K28" s="91"/>
-      <c r="L28" s="135"/>
+      <c r="L28" s="137"/>
       <c r="M28" s="90"/>
       <c r="N28" s="91"/>
-      <c r="O28" s="135"/>
+      <c r="O28" s="137"/>
       <c r="P28" s="90"/>
       <c r="Q28" s="91"/>
       <c r="R28" s="33"/>
@@ -13684,21 +13699,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="138"/>
+      <c r="A29" s="133"/>
       <c r="B29" s="91"/>
-      <c r="C29" s="139"/>
+      <c r="C29" s="134"/>
       <c r="D29" s="91"/>
-      <c r="E29" s="139"/>
+      <c r="E29" s="134"/>
       <c r="F29" s="91"/>
-      <c r="G29" s="133"/>
+      <c r="G29" s="139"/>
       <c r="H29" s="90"/>
       <c r="I29" s="91"/>
-      <c r="J29" s="133"/>
+      <c r="J29" s="139"/>
       <c r="K29" s="91"/>
-      <c r="L29" s="135"/>
+      <c r="L29" s="137"/>
       <c r="M29" s="90"/>
       <c r="N29" s="91"/>
-      <c r="O29" s="135"/>
+      <c r="O29" s="137"/>
       <c r="P29" s="90"/>
       <c r="Q29" s="91"/>
       <c r="R29" s="33"/>
@@ -13712,21 +13727,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="138"/>
+      <c r="A30" s="133"/>
       <c r="B30" s="91"/>
-      <c r="C30" s="139"/>
+      <c r="C30" s="134"/>
       <c r="D30" s="91"/>
-      <c r="E30" s="139"/>
+      <c r="E30" s="134"/>
       <c r="F30" s="91"/>
-      <c r="G30" s="133"/>
+      <c r="G30" s="139"/>
       <c r="H30" s="90"/>
       <c r="I30" s="91"/>
-      <c r="J30" s="133"/>
+      <c r="J30" s="139"/>
       <c r="K30" s="91"/>
-      <c r="L30" s="135"/>
+      <c r="L30" s="137"/>
       <c r="M30" s="90"/>
       <c r="N30" s="91"/>
-      <c r="O30" s="135"/>
+      <c r="O30" s="137"/>
       <c r="P30" s="90"/>
       <c r="Q30" s="91"/>
       <c r="R30" s="33"/>
@@ -13740,23 +13755,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="141"/>
-      <c r="B31" s="117"/>
-      <c r="C31" s="142"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="142"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="134"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="136"/>
-      <c r="M31" s="116"/>
-      <c r="N31" s="117"/>
-      <c r="O31" s="136"/>
-      <c r="P31" s="116"/>
-      <c r="Q31" s="117"/>
+      <c r="A31" s="135"/>
+      <c r="B31" s="129"/>
+      <c r="C31" s="136"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="136"/>
+      <c r="F31" s="129"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="128"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="142"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="138"/>
+      <c r="M31" s="128"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="138"/>
+      <c r="P31" s="128"/>
+      <c r="Q31" s="129"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14754,6 +14769,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14778,118 +14905,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DE35C9-A39A-423B-AAFC-CB883FEE6633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E351B892-5CA4-4F47-BE51-752095D8301E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -509,6 +509,24 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t xml:space="preserve">1.従業員がタスク一覧画面を表示する
+2.従業員は削除したいタスクに対応したラジオボタンを選択する
+(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
+3.従業員が「削除」ボタンを押下する
+4.システムが選択されたタスク情報を取得し、対象タスクが存在することを確認する。
+5.システムは削除対象タスクの内容を表示したタスク削除確認画面を表示する
+6.従業員が「削除」ボタンを押下する
+7. システムは削除対象タスクをデータベースから削除する。
+8. システムは削除したタスクの内容を表示したタスク削除完了画面を表示する
+9.従業員は「メニュー画面へ」を押下する
+10.システムはメニュー画面を表示する
+</t>
+    <rPh sb="25" eb="27">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t xml:space="preserve">
 A1:タスク未選択で削除ボタン押下した場合
 A1-1:基本フロー3でシステムはタスク未選択を検出する
@@ -519,12 +537,19 @@
 A2-2:システムは削除処理を実行しない
 A2-3:システムは一覧表示画面を表示する
 A3：ログインユーザとタスク担当者が不一致の状態で削除実行した場合
-A3-1:基本フロー4でシステムはログイン中のユーザIDと担当者IDを比較する
-A3-2：担当者IDが一致しないことを検出する
-A3-3：システムは削除処理を実行しない
-A3-4：システムは削除失敗画面を表示する
-A3-5：従業員は削除失敗画面で「メニューへ」を押下する
-A3-6：システムはメニュー画面を表示する
+A3-1：基本フロー4でシステムは選択されたタスクの担当者IDを取得する
+A3-2：システムはログイン中のユーザIDと担当者IDを比較する
+A3-3：担当者IDが一致しないことを検出する
+A3-4：システムは削除処理を実行しない
+A3-5：システムは削除失敗画面を表示する
+A3-6：従業員は削除失敗画面で「メニューへ」を押下する
+A3-7：システムはメニュー画面を表示する
+A4：対象タスクが既に削除されている場合
+A4-1. 基本フロー4または8で、システムは対象タスクが存在しないことを検出する。
+A4-2. システムは削除処理を実行しない。
+A4-3：システムは削除失敗画面を表示する
+A4-4：従業員は削除失敗画面で「メニューへ」を押下する
+A4-5：システムはメニュー画面を表示する
 </t>
     <rPh sb="113" eb="115">
       <t>サクジョ</t>
@@ -562,59 +587,25 @@
     <rPh sb="234" eb="236">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="337" eb="343">
+    <rPh sb="367" eb="373">
       <t>サクジョシッパイガメン</t>
     </rPh>
-    <rPh sb="354" eb="357">
+    <rPh sb="384" eb="387">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="373" eb="375">
+    <rPh sb="403" eb="405">
       <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">
-E2:データベース接続失敗した場合
-E2-1:基本フロー4または8でシステムがデータベース接続に失敗する
-E2-2:システムは削除失敗画面を表示する。
-E2-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
+E1:データベース接続失敗した場合
+E1-1:基本フロー4または7でシステムがデータベース接続に失敗する
+E1-2:システムは削除失敗画面を表示する。
+E1-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
     <rPh sb="66" eb="68">
       <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.従業員がタスク一覧表示画面を表示する
-2..従業員は削除したいタスクに対応したラジオボタンを選択する
-(一覧表示画面ではログイン確認済み従業員本人が担当者でないタスクにはラジオボタンが表示されません)
-3.従業員が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得する
-5.システムがタスク削除確認画面を表示する
-6.従業員が「削除」ボタンを押下する
-7.システムがログインユーザとタスク担当者の一致を確認
-8. システムが選択されたタスクをデータベースから削除する
-9.システムがタスク削除完了画面を表示する
-10.従業員は「メニュー画面へ」を押下する
-11.システムはメニュー画面を表示する
-</t>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="208" eb="210">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="211" eb="213">
-      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -4597,7 +4588,7 @@
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="47" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E9" s="48"/>
       <c r="F9" s="48"/>
@@ -4606,14 +4597,14 @@
       <c r="I9" s="48"/>
       <c r="J9" s="49"/>
     </row>
-    <row r="10" spans="1:10" ht="302.25" customHeight="1">
+    <row r="10" spans="1:10" ht="393.75" customHeight="1">
       <c r="A10" s="69"/>
       <c r="B10" s="71" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E10" s="48"/>
       <c r="F10" s="48"/>
@@ -4629,7 +4620,7 @@
       </c>
       <c r="C11" s="67"/>
       <c r="D11" s="47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11" s="48"/>
       <c r="F11" s="48"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E351B892-5CA4-4F47-BE51-752095D8301E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707515D4-9580-45A0-9942-1B51903FE6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="735" windowWidth="17910" windowHeight="9975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -513,16 +513,47 @@
 2.従業員は削除したいタスクに対応したラジオボタンを選択する
 (従業員本人が担当者でないタスクにはラジオボタンが表示されません)
 3.従業員が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得し、対象タスクが存在することを確認する。
+4.システムが選択されたタスク情報を取得する。
 5.システムは削除対象タスクの内容を表示したタスク削除確認画面を表示する
 6.従業員が「削除」ボタンを押下する
-7. システムは削除対象タスクをデータベースから削除する。
-8. システムは削除したタスクの内容を表示したタスク削除完了画面を表示する
-9.従業員は「メニュー画面へ」を押下する
-10.システムはメニュー画面を表示する
+7.システムは削除対象タスクの担当者とログインユーザが一致していること確認する。
+8.システムは削除対象タスクが存在していることを確認する。
+9. システムは削除対象タスクをデータベースから削除する。
+10. システムは削除したタスクの内容を表示したタスク削除完了画面を表示する
+11.従業員は「メニュー画面へ」を押下する
+12.システムはメニュー画面を表示する
 </t>
     <rPh sb="25" eb="27">
       <t>サクジョ</t>
+    </rPh>
+    <rPh sb="190" eb="192">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="218" eb="220">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="231" eb="233">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="233" eb="235">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="239" eb="241">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="248" eb="250">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+E1:データベース接続失敗した場合
+E1-1:基本フロー4または9でシステムがデータベース接続に失敗する
+E1-2:システムは削除失敗画面を表示する。
+E1-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
+    <rPh sb="66" eb="68">
+      <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -538,10 +569,10 @@
 A2-3:システムは一覧表示画面を表示する
 A3：ログインユーザとタスク担当者が不一致の状態で削除実行した場合
 A3-1：基本フロー4でシステムは選択されたタスクの担当者IDを取得する
-A3-2：システムはログイン中のユーザIDと担当者IDを比較する
+A3-2：基本フロー7でログイン中のユーザIDと担当者IDを比較する
 A3-3：担当者IDが一致しないことを検出する
 A3-4：システムは削除処理を実行しない
-A3-5：システムは削除失敗画面を表示する
+A3-5：システムは削除失敗画面でエラーメッセージ「削除できるタスクがありません」を表示する
 A3-6：従業員は削除失敗画面で「メニューへ」を押下する
 A3-7：システムはメニュー画面を表示する
 A4：対象タスクが既に削除されている場合
@@ -587,25 +618,20 @@
     <rPh sb="234" eb="236">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="367" eb="373">
+    <rPh sb="285" eb="287">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="369" eb="375">
       <t>サクジョシッパイガメン</t>
     </rPh>
-    <rPh sb="384" eb="387">
+    <rPh sb="386" eb="388">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="411" eb="414">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="403" eb="405">
+    <rPh sb="430" eb="432">
       <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-E1:データベース接続失敗した場合
-E1-1:基本フロー4または7でシステムがデータベース接続に失敗する
-E1-2:システムは削除失敗画面を表示する。
-E1-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
-    <rPh sb="66" eb="68">
-      <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -4604,7 +4630,7 @@
       </c>
       <c r="C10" s="67"/>
       <c r="D10" s="47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E10" s="48"/>
       <c r="F10" s="48"/>
@@ -4620,7 +4646,7 @@
       </c>
       <c r="C11" s="67"/>
       <c r="D11" s="47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E11" s="48"/>
       <c r="F11" s="48"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707515D4-9580-45A0-9942-1B51903FE6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAC3DD3-C99C-4275-9A76-5A7051871FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="735" windowWidth="17910" windowHeight="9975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -39,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="105">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -509,44 +531,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1.従業員がタスク一覧画面を表示する
-2.従業員は削除したいタスクに対応したラジオボタンを選択する
-(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
-3.従業員が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得する。
-5.システムは削除対象タスクの内容を表示したタスク削除確認画面を表示する
-6.従業員が「削除」ボタンを押下する
-7.システムは削除対象タスクの担当者とログインユーザが一致していること確認する。
-8.システムは削除対象タスクが存在していることを確認する。
-9. システムは削除対象タスクをデータベースから削除する。
-10. システムは削除したタスクの内容を表示したタスク削除完了画面を表示する
-11.従業員は「メニュー画面へ」を押下する
-12.システムはメニュー画面を表示する
-</t>
-    <rPh sb="25" eb="27">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="190" eb="192">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="218" eb="220">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="231" eb="233">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="233" eb="235">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="239" eb="241">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="248" eb="250">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t xml:space="preserve">
 E1:データベース接続失敗した場合
 E1-1:基本フロー4または9でシステムがデータベース接続に失敗する
@@ -558,8 +542,49 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t xml:space="preserve">1.従業員がタスク一覧画面を表示する
+2.従業員は削除したいタスクに対応したラジオボタンを選択する
+(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
+3.従業員が「削除」ボタンを押下する
+4.システムが選択されたタスク情報を取得する。
+5.システムは削除対象タスクの内容を表示したタスク削除確認画面を表示する
+6.従業員が「削除実行」ボタンを押下する
+7.システムは削除対象タスクの担当者とログインユーザが一致していること確認する。
+8.システムは削除対象タスクが存在していることを確認する。
+9. システムは削除対象タスクをデータベースから削除する。
+10. システムは削除したタスクの内容を表示したタスク削除完了画面を表示する
+11.従業員は「メニュー画面へ」を押下する
+12.システムはメニュー画面を表示する
+</t>
+    <rPh sb="25" eb="27">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="173" eb="175">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="192" eb="194">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="220" eb="222">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="233" eb="235">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="235" eb="237">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="241" eb="243">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="250" eb="252">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t xml:space="preserve">
-A1:タスク未選択で削除ボタン押下した場合
+A1:タスク未選択で削除実行ボタン押下した場合
 A1-1:基本フロー3でシステムはタスク未選択を検出する
 A1-2:システムは一覧画面を再表示する
 A1-3:システムは「削除するタスクを選択してください。」と表示する
@@ -582,56 +607,78 @@
 A4-4：従業員は削除失敗画面で「メニューへ」を押下する
 A4-5：システムはメニュー画面を表示する
 </t>
-    <rPh sb="113" eb="115">
+    <rPh sb="14" eb="16">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="123" eb="125">
+    <rPh sb="125" eb="127">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="131" eb="133">
+    <rPh sb="133" eb="135">
       <t>キホン</t>
     </rPh>
-    <rPh sb="138" eb="141">
+    <rPh sb="140" eb="143">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="145" eb="147">
+    <rPh sb="147" eb="149">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="147" eb="151">
+    <rPh sb="149" eb="153">
       <t>カクニンガメン</t>
     </rPh>
-    <rPh sb="153" eb="157">
+    <rPh sb="155" eb="159">
       <t>イチランヒョウジ</t>
     </rPh>
-    <rPh sb="160" eb="162">
+    <rPh sb="162" eb="164">
       <t>オウカ</t>
     </rPh>
-    <rPh sb="196" eb="200">
+    <rPh sb="198" eb="202">
       <t>イチランヒョウジ</t>
     </rPh>
-    <rPh sb="200" eb="202">
+    <rPh sb="202" eb="204">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="203" eb="205">
+    <rPh sb="205" eb="207">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="234" eb="236">
+    <rPh sb="236" eb="238">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="285" eb="287">
+    <rPh sb="287" eb="289">
       <t>キホン</t>
     </rPh>
-    <rPh sb="369" eb="375">
+    <rPh sb="371" eb="377">
       <t>サクジョシッパイガメン</t>
     </rPh>
-    <rPh sb="386" eb="388">
+    <rPh sb="388" eb="390">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="411" eb="414">
+    <rPh sb="413" eb="416">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="430" eb="432">
+    <rPh sb="432" eb="434">
       <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除対象の確認画面表示後に対象タスクが削除・改ざんされる可能性を考慮し、削除実行時に存在確認および権限確認を行う</t>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>カクニンガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>オコナ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1398,7 +1445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1828,6 +1875,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2253,68 +2303,18 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>857811</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>35298</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>159075</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>236859</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D2358C9-D228-3579-F7D3-50EACDBE9D64}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="733425" y="1571625"/>
-          <a:ext cx="3797625" cy="3675384"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>923925</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>643778</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>63873</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2329,8 +2329,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4400550" y="1990725"/>
-          <a:ext cx="2009775" cy="828675"/>
+          <a:off x="6337487" y="2097180"/>
+          <a:ext cx="2004732" cy="835399"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -2387,16 +2387,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>170330</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>145676</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>617444</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>13446</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2411,8 +2411,74 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647700" y="4743450"/>
-          <a:ext cx="1552575" cy="381000"/>
+          <a:off x="2321859" y="4896970"/>
+          <a:ext cx="1556497" cy="383241"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>602317</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>167528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>126068</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>245969</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="楕円 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D2E5F77-8BAB-4B5B-BD3D-BD7379FC2F38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3863229" y="4918822"/>
+          <a:ext cx="1742515" cy="347382"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2454,81 +2520,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1095376</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>257175</xdr:rowOff>
+      <xdr:colOff>759198</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>143995</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>619126</xdr:colOff>
+      <xdr:colOff>558612</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="楕円 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D2E5F77-8BAB-4B5B-BD3D-BD7379FC2F38}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2124076" y="4733925"/>
-          <a:ext cx="1752600" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:rowOff>172570</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2543,8 +2543,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="142875" y="4143375"/>
-          <a:ext cx="2009775" cy="828675"/>
+          <a:off x="1801345" y="4357407"/>
+          <a:ext cx="2018179" cy="835398"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -2601,16 +2601,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>399491</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
+      <xdr:rowOff>251011</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>699247</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
+      <xdr:rowOff>184336</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2625,8 +2625,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4295775" y="4705349"/>
-          <a:ext cx="1419225" cy="200025"/>
+          <a:off x="5879167" y="4733364"/>
+          <a:ext cx="1409139" cy="202266"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -2683,16 +2683,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>241488</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>50987</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>741270</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>3362</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2707,8 +2707,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="714375" y="2562225"/>
-          <a:ext cx="3838575" cy="2085975"/>
+          <a:off x="2393017" y="2650752"/>
+          <a:ext cx="3827929" cy="2103904"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3099,6 +3099,70 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4614,7 +4678,7 @@
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E9" s="48"/>
       <c r="F9" s="48"/>
@@ -4646,7 +4710,7 @@
       </c>
       <c r="C11" s="67"/>
       <c r="D11" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" s="48"/>
       <c r="F11" s="48"/>
@@ -4677,7 +4741,9 @@
       </c>
       <c r="B13" s="51"/>
       <c r="C13" s="52"/>
-      <c r="D13" s="38"/>
+      <c r="D13" s="143" t="s">
+        <v>104</v>
+      </c>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
       <c r="G13" s="39"/>
@@ -10097,7 +10163,9 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
+      <c r="A7" s="115" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="B7" s="116"/>
       <c r="C7" s="116"/>
       <c r="D7" s="116"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAC3DD3-C99C-4275-9A76-5A7051871FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D9607E-664B-427F-8C0E-D1FBA40FF2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="17910" windowHeight="9975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -664,7 +664,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>削除対象の確認画面表示後に対象タスクが削除・改ざんされる可能性を考慮し、削除実行時に存在確認および権限確認を行う</t>
+    <t>削除対象の確認画面表示後に対象タスクが削除・改ざんされる可能性を考慮し、削除実行時に存在確認および権限確認を行う。</t>
     <rPh sb="2" eb="4">
       <t>タイショウ</t>
     </rPh>
@@ -1560,25 +1560,190 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1586,15 +1751,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1641,15 +1797,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1659,109 +1806,34 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1773,76 +1845,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1851,32 +1869,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3372,85 +3372,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="60"/>
+      <c r="O3" s="60"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="93"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="60"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="60"/>
+      <c r="O6" s="60"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3470,46 +3470,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="96" t="s">
+      <c r="E8" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="60"/>
+      <c r="M8" s="60"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="89" t="s">
+      <c r="G13" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="91"/>
-      <c r="I13" s="89" t="s">
+      <c r="H13" s="40"/>
+      <c r="I13" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="90"/>
-      <c r="K13" s="91"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="89"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="91"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="40"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="89"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="91"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3518,13 +3518,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="92" t="s">
+      <c r="G17" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4538,19 +4538,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="79"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="84"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="79"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4562,194 +4562,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="85"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="86">
+      <c r="G2" s="85"/>
+      <c r="H2" s="70">
         <v>46183</v>
       </c>
       <c r="I2" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="94"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="95"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="124"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="99"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="101"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="44" t="s">
+      <c r="B7" s="99"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="47" t="s">
+      <c r="B8" s="99"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="125" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="101"/>
     </row>
     <row r="9" spans="1:10" ht="220.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="47" t="s">
+      <c r="C9" s="97"/>
+      <c r="D9" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="127"/>
     </row>
     <row r="10" spans="1:10" ht="393.75" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="71" t="s">
+      <c r="A10" s="118"/>
+      <c r="B10" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="47" t="s">
+      <c r="C10" s="97"/>
+      <c r="D10" s="125" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="127"/>
     </row>
     <row r="11" spans="1:10" ht="135.75" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="119"/>
+      <c r="B11" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="47" t="s">
+      <c r="C11" s="97"/>
+      <c r="D11" s="125" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="127"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="65" t="s">
+      <c r="A12" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="44" t="s">
+      <c r="B12" s="99"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="46"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="143" t="s">
+      <c r="B13" s="103"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="120" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="121"/>
+      <c r="I13" s="121"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5740,17 +5740,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5759,14 +5756,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5785,19 +5785,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="109"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5809,40 +5809,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="110"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="68"/>
       <c r="H2" s="72"/>
       <c r="I2" s="72"/>
-      <c r="J2" s="75"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="99"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="100"/>
+      <c r="A4" s="130"/>
+      <c r="B4" s="131"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="129"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7198,19 +7198,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="109"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7222,48 +7222,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="86">
+      <c r="G2" s="68"/>
+      <c r="H2" s="70">
         <v>46190</v>
       </c>
       <c r="I2" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="99"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="100"/>
+      <c r="A4" s="130"/>
+      <c r="B4" s="131"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="129"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8614,19 +8614,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="109"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8638,262 +8638,262 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="86">
+      <c r="G2" s="68"/>
+      <c r="H2" s="70">
         <v>46188</v>
       </c>
       <c r="I2" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="99"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="99"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="42" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="114"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="104"/>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="118"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="104"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="118"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="104"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="118"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="104"/>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="118"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="104"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="118"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="104"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="118"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="104"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="118"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="58"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="104"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="118"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="58"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="104"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="118"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="58"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="104"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="118"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="58"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="104"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="118"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="104"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="118"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="58"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="114"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="44" t="s">
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="91"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
@@ -8902,11 +8902,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -8919,18 +8919,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="122" t="s">
+      <c r="H22" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="90"/>
-      <c r="J22" s="114"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="124"/>
-      <c r="C23" s="125"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="17" t="s">
         <v>81</v>
       </c>
@@ -8943,18 +8943,18 @@
       <c r="G23" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="90"/>
-      <c r="J23" s="114"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="123" t="s">
+      <c r="A24" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="124"/>
-      <c r="C24" s="125"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="17" t="s">
         <v>83</v>
       </c>
@@ -8967,71 +8967,71 @@
       <c r="G24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="I24" s="90"/>
-      <c r="J24" s="114"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="42"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="123"/>
-      <c r="B25" s="124"/>
-      <c r="C25" s="125"/>
+      <c r="A25" s="48"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="114"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="42"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="126"/>
-      <c r="B26" s="90"/>
-      <c r="C26" s="91"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="114"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="42"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="126"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="91"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="114"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="42"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="126"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="91"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="114"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="42"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="127"/>
-      <c r="B29" s="128"/>
-      <c r="C29" s="129"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="130"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="47"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10012,22 +10012,6 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -10043,6 +10027,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10065,19 +10065,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="109"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -10089,276 +10089,276 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="86">
+      <c r="G2" s="68"/>
+      <c r="H2" s="70">
         <v>46188</v>
       </c>
       <c r="I2" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="99"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="99"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="42" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="114"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115" t="e" vm="1">
+      <c r="A7" s="53" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="118"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="118"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="132"/>
-      <c r="J10" s="118"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="118"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="131"/>
-      <c r="B12" s="132"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="132"/>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="118"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="131"/>
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="118"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="131"/>
-      <c r="B14" s="132"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="118"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="58"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="104"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="118"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="58"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="104"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="118"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="58"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="104"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="118"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="58"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="104"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="118"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="104"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="118"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="58"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="104"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="118"/>
+      <c r="A20" s="59"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="58"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="114"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="44" t="s">
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="91"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
       <c r="I22" s="15" t="s">
         <v>28</v>
       </c>
@@ -10367,11 +10367,11 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="113" t="s">
+      <c r="A23" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="90"/>
-      <c r="C23" s="91"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="15" t="s">
         <v>30</v>
       </c>
@@ -10384,18 +10384,18 @@
       <c r="G23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="122" t="s">
+      <c r="H23" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="90"/>
-      <c r="J23" s="114"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="123" t="s">
+      <c r="A24" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="124"/>
-      <c r="C24" s="125"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="17" t="s">
         <v>81</v>
       </c>
@@ -10408,18 +10408,18 @@
       <c r="G24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="90"/>
-      <c r="J24" s="114"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="42"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="123" t="s">
+      <c r="A25" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="124"/>
-      <c r="C25" s="125"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="17" t="s">
         <v>84</v>
       </c>
@@ -10432,18 +10432,18 @@
       <c r="G25" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="90"/>
-      <c r="J25" s="114"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="42"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="123" t="s">
+      <c r="A26" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="124"/>
-      <c r="C26" s="125"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="50"/>
       <c r="D26" s="17" t="s">
         <v>85</v>
       </c>
@@ -10456,59 +10456,59 @@
       <c r="G26" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="I26" s="90"/>
-      <c r="J26" s="114"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="42"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="126"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="91"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="114"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="42"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="126"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="91"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="114"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="42"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="126"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="91"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="90"/>
-      <c r="J29" s="114"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="42"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="127"/>
-      <c r="B30" s="128"/>
-      <c r="C30" s="129"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="45"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="130"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="47"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11489,22 +11489,6 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11520,6 +11504,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11542,19 +11542,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="109"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11566,262 +11566,262 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="86">
+      <c r="G2" s="68"/>
+      <c r="H2" s="70">
         <v>46188</v>
       </c>
       <c r="I2" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="99"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="104"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="99"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="42" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="114"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="131"/>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="118"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="118"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="131"/>
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="132"/>
-      <c r="J10" s="118"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
-      <c r="J11" s="118"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="104"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="118"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="104"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="118"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="104"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="118"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="58"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="104"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="118"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="58"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="104"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="118"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="58"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="104"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="118"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="58"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="104"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="118"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="104"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="118"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="58"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="114"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="44" t="s">
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="91"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="15" t="s">
         <v>28</v>
       </c>
@@ -11830,11 +11830,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="15" t="s">
         <v>30</v>
       </c>
@@ -11847,18 +11847,18 @@
       <c r="G22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="122" t="s">
+      <c r="H22" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="90"/>
-      <c r="J22" s="114"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="124"/>
-      <c r="C23" s="125"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="17" t="s">
         <v>82</v>
       </c>
@@ -11871,18 +11871,18 @@
       <c r="G23" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="I23" s="90"/>
-      <c r="J23" s="114"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="123" t="s">
+      <c r="A24" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="124"/>
-      <c r="C24" s="125"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="17" t="s">
         <v>83</v>
       </c>
@@ -11895,59 +11895,59 @@
       <c r="G24" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="90"/>
-      <c r="J24" s="114"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="42"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="126"/>
-      <c r="B25" s="90"/>
-      <c r="C25" s="91"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="114"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="42"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="126"/>
-      <c r="B26" s="90"/>
-      <c r="C26" s="91"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="114"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="42"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="126"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="91"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="114"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="42"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="127"/>
-      <c r="B28" s="128"/>
-      <c r="C28" s="129"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="45"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="128"/>
-      <c r="J28" s="130"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="47"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12928,11 +12928,14 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12949,14 +12952,11 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12976,182 +12976,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="78" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="78" t="s">
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="78" t="s">
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="78" t="s">
+      <c r="P1" s="66"/>
+      <c r="Q1" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="109"/>
-      <c r="S1" s="78" t="s">
+      <c r="R1" s="66"/>
+      <c r="S1" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="121"/>
+      <c r="T1" s="78"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="110"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="117"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="55"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="105"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="118"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="69"/>
+      <c r="T3" s="58"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="106"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="107"/>
-      <c r="M4" s="107"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="141"/>
+      <c r="A4" s="130"/>
+      <c r="B4" s="131"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="132"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="132"/>
+      <c r="Q4" s="133"/>
+      <c r="R4" s="132"/>
+      <c r="S4" s="133"/>
+      <c r="T4" s="138"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="41" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="120"/>
-      <c r="M5" s="120"/>
-      <c r="N5" s="120"/>
-      <c r="O5" s="120"/>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="120"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="120"/>
-      <c r="T5" s="121"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="78"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="44" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="90"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="114"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="42"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="44" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="90"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="90"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
-      <c r="T7" s="114"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="42"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13350,37 +13350,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="91"/>
-      <c r="C15" s="140" t="s">
+      <c r="B15" s="40"/>
+      <c r="C15" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="91"/>
-      <c r="E15" s="122" t="s">
+      <c r="D15" s="40"/>
+      <c r="E15" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="122" t="s">
+      <c r="F15" s="40"/>
+      <c r="G15" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="90"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="122" t="s">
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="91"/>
-      <c r="L15" s="122" t="s">
+      <c r="K15" s="40"/>
+      <c r="L15" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="90"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="122" t="s">
+      <c r="M15" s="39"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="91"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="40"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -13392,37 +13392,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="133">
+      <c r="A16" s="139">
         <v>1</v>
       </c>
-      <c r="B16" s="91"/>
-      <c r="C16" s="134" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="91"/>
-      <c r="E16" s="134" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="91"/>
-      <c r="G16" s="139" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="90"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="139" t="s">
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="91"/>
-      <c r="L16" s="137" t="s">
+      <c r="K16" s="40"/>
+      <c r="L16" s="136" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="90"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="137" t="s">
+      <c r="M16" s="39"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="136" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="91"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13434,37 +13434,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="133">
+      <c r="A17" s="139">
         <v>2</v>
       </c>
-      <c r="B17" s="91"/>
-      <c r="C17" s="134" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="91"/>
-      <c r="E17" s="134" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="91"/>
-      <c r="G17" s="139" t="s">
+      <c r="F17" s="40"/>
+      <c r="G17" s="134" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="90"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="139" t="s">
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="134" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="91"/>
-      <c r="L17" s="137" t="s">
+      <c r="K17" s="40"/>
+      <c r="L17" s="136" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="90"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="137" t="s">
+      <c r="M17" s="39"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="136" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="91"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="40"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13476,23 +13476,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="133"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="134"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="134"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="139"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="139"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="137"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="137"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="91"/>
+      <c r="A18" s="139"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13504,23 +13504,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="133"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="134"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="134"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="139"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="137"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="137"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="91"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="140"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="134"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="134"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13532,23 +13532,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="133"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="134"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="134"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="139"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="137"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="91"/>
+      <c r="A20" s="139"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13560,23 +13560,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="133"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="134"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="139"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="139"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="137"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="137"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="91"/>
+      <c r="A21" s="139"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13588,23 +13588,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="133"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="134"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="139"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="139"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="137"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="91"/>
+      <c r="A22" s="139"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="134"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="136"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13616,23 +13616,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="133"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="139"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="139"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="137"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="137"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="91"/>
+      <c r="A23" s="139"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13644,23 +13644,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="133"/>
-      <c r="B24" s="91"/>
-      <c r="C24" s="134"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="139"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="137"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="137"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="91"/>
+      <c r="A24" s="139"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="136"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="136"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13672,23 +13672,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="133"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="134"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="134"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="139"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="137"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="137"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="91"/>
+      <c r="A25" s="139"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13700,23 +13700,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="133"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="134"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="137"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="137"/>
-      <c r="P26" s="90"/>
-      <c r="Q26" s="91"/>
+      <c r="A26" s="139"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="134"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13728,23 +13728,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="133"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="134"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="134"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="139"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="139"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="137"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="137"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="91"/>
+      <c r="A27" s="139"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="134"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="134"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13756,23 +13756,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="133"/>
-      <c r="B28" s="91"/>
-      <c r="C28" s="134"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="139"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="139"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="137"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="137"/>
-      <c r="P28" s="90"/>
-      <c r="Q28" s="91"/>
+      <c r="A28" s="139"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="134"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="134"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="136"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13784,23 +13784,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="133"/>
-      <c r="B29" s="91"/>
-      <c r="C29" s="134"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="134"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="139"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="91"/>
+      <c r="A29" s="139"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="134"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13812,23 +13812,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="133"/>
-      <c r="B30" s="91"/>
-      <c r="C30" s="134"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="134"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="139"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="139"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="137"/>
-      <c r="M30" s="90"/>
-      <c r="N30" s="91"/>
-      <c r="O30" s="137"/>
-      <c r="P30" s="90"/>
-      <c r="Q30" s="91"/>
+      <c r="A30" s="139"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="140"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="134"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="134"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="136"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13840,23 +13840,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="135"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="129"/>
-      <c r="E31" s="136"/>
-      <c r="F31" s="129"/>
-      <c r="G31" s="142"/>
-      <c r="H31" s="128"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="142"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="138"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="138"/>
-      <c r="P31" s="128"/>
-      <c r="Q31" s="129"/>
+      <c r="A31" s="142"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="143"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="143"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="137"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="137"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="45"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14854,62 +14854,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14934,62 +14934,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D9607E-664B-427F-8C0E-D1FBA40FF2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D719740-C0DB-43D8-82FC-F69BF89960C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="17910" windowHeight="9975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>イベントフロー</t>
-  </si>
-  <si>
-    <t>基本フロー</t>
   </si>
   <si>
     <t>代替フロー</t>
@@ -520,166 +517,69 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>削除対象のタスクを担当している従業員がログインしており、
-一覧表示画面でタスクを１件以上表示している</t>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="41" eb="44">
-      <t>ケンイジョウ</t>
-    </rPh>
+    <t>・従業員がログインしており、タスク一覧表示画面が表示されていること。
+・削除対象のタスクがデータベースに登録されていること。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.従業員は削除したいタスクに対応したラジオボタンを選択する
+（従業員本人が担当者でないタスクにはラジオボタンが表示されません）
+2.従業員は「削除」ボタンを押下する
+3.システムは削除対象タスクを取得し、以下の内容を確認する
+・選択されたタスクがデータベース上に存在していること
+・削除対象タスクの担当者とログインユーザが一致していること
+4.システムはタスク削除確認画面を表示する
+（この際、削除対象タスクの情報を表示する）
+5.従業員は「削除」ボタンを押下する
+6.システムは以下の内容を確認する
+・削除対象タスクが存在していること
+・削除対象タスクの担当者とログインユーザが一致していること
+7.システムは選択されたタスクをデータベースから削除する
+8.システムはタスク削除成功画面を表示する
+</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>基本フロー</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除確認画面表示後に対象タスクが削除・改ざんされる可能性を考慮し、削除実行時にも存在確認および権限確認を再実施する。</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">
-E1:データベース接続失敗した場合
-E1-1:基本フロー4または9でシステムがデータベース接続に失敗する
-E1-2:システムは削除失敗画面を表示する。
-E1-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
-    <rPh sb="66" eb="68">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.従業員がタスク一覧画面を表示する
-2.従業員は削除したいタスクに対応したラジオボタンを選択する
-(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
-3.従業員が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得する。
-5.システムは削除対象タスクの内容を表示したタスク削除確認画面を表示する
-6.従業員が「削除実行」ボタンを押下する
-7.システムは削除対象タスクの担当者とログインユーザが一致していること確認する。
-8.システムは削除対象タスクが存在していることを確認する。
-9. システムは削除対象タスクをデータベースから削除する。
-10. システムは削除したタスクの内容を表示したタスク削除完了画面を表示する
-11.従業員は「メニュー画面へ」を押下する
-12.システムはメニュー画面を表示する
-</t>
-    <rPh sb="25" eb="27">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="173" eb="175">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="192" eb="194">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="220" eb="222">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="233" eb="235">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="235" eb="237">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="241" eb="243">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="250" eb="252">
-      <t>カクニン</t>
-    </rPh>
+E1.基本フロー7において、データベースへの削除処理に失敗した場合
+E1-1.システムはタスク情報を削除せず、タスク削除失敗画面を表示する
+E1-2.従業員はエラー画面に従い、「メニュー画面へ」ボタンを押下する
+E1-3.システムはメニュー画面を表示する
+E1-4.従業員は必要に応じて本ユースケースを再実行する
+E2.基本フロー3でデータ取得に失敗した場合
+E2-1.システムはタスク削除確認画面を表示せず、タスク一覧表示画面を再表示する
+E2-2.システムは「データベース情報の取得に失敗しました。」とエラーメッセージを表示する
+E2-3.従業員は必要に応じて本ユースケースを再実行する</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">
-A1:タスク未選択で削除実行ボタン押下した場合
-A1-1:基本フロー3でシステムはタスク未選択を検出する
-A1-2:システムは一覧画面を再表示する
-A1-3:システムは「削除するタスクを選択してください。」と表示する
-A2:削除をキャンセルする場合
-A2-1:基本フロー5で従業員はタスク削除確認画面で「一覧表示へ」を押下する
-A2-2:システムは削除処理を実行しない
-A2-3:システムは一覧表示画面を表示する
-A3：ログインユーザとタスク担当者が不一致の状態で削除実行した場合
-A3-1：基本フロー4でシステムは選択されたタスクの担当者IDを取得する
-A3-2：基本フロー7でログイン中のユーザIDと担当者IDを比較する
-A3-3：担当者IDが一致しないことを検出する
-A3-4：システムは削除処理を実行しない
-A3-5：システムは削除失敗画面でエラーメッセージ「削除できるタスクがありません」を表示する
-A3-6：従業員は削除失敗画面で「メニューへ」を押下する
-A3-7：システムはメニュー画面を表示する
-A4：対象タスクが既に削除されている場合
-A4-1. 基本フロー4または8で、システムは対象タスクが存在しないことを検出する。
-A4-2. システムは削除処理を実行しない。
-A4-3：システムは削除失敗画面を表示する
-A4-4：従業員は削除失敗画面で「メニューへ」を押下する
-A4-5：システムはメニュー画面を表示する
+A1.タスク一覧表示画面にて、タスク未選択で削除ボタンを押下した場合
+A1-1.基本フロー2において、システムはタスク未選択を検出する
+A1-2.システムはタスク一覧表示画面を再表示する
+A1-3.システムは「削除するタスクを選択してください。」というエラーメッセージを表示する
+A1-4.従業員はエラーメッセージに従いタスクを選択し、基本フロー1から再試行する
+A2.基本フロー3において、削除対象タスクが存在しない、または削除対象タスクの担当者とログインユーザが一致しない場合
+A2-1.システムは削除対象タスクの担当者とログインユーザが一致しないこと、または削除対象タスクが存在していないことを検出する
+A2-2.システムはタスク一覧表示画面を再表示し、エラーメッセージ「選択されたタスクに削除権限がないか、存在していません」を表示する
+A2-3.従業員は必要に応じて本ユースケースを再実行する
+A3.基本フロー6において、削除対象タスクが存在しない、または削除対象タスクの担当者とログインユーザが一致しない場合
+A3-1.システムは削除対象タスクの担当者とログインユーザが一致しないこと、または削除対象タスクが存在していないことを検出する
+A3-2.システムはタスク削除失敗画面を表示し、エラーメッセージ「選択されたタスクに削除権限がないか、存在していません」を表示する
+A3-3.従業員は必要に応じて本ユースケースを再実行する
+A4.基本フロー4において、削除を中止する場合
+A4-1.従業員は「一覧表示へ」ボタンを押下する
+A4-2.システムはタスク一覧表示画面を表示する
+A4-3.従業員は必要に応じて本ユースケースを再実行する
 </t>
-    <rPh sb="14" eb="16">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="133" eb="135">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="140" eb="143">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="147" eb="149">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="149" eb="153">
-      <t>カクニンガメン</t>
-    </rPh>
-    <rPh sb="155" eb="159">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="162" eb="164">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="198" eb="202">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="202" eb="204">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="205" eb="207">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="236" eb="238">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="287" eb="289">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="371" eb="377">
-      <t>サクジョシッパイガメン</t>
-    </rPh>
-    <rPh sb="388" eb="390">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="413" eb="416">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="432" eb="434">
-      <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>削除対象の確認画面表示後に対象タスクが削除・改ざんされる可能性を考慮し、削除実行時に存在確認および権限確認を行う。</t>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>カクニンガメン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>オコナ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1560,190 +1460,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1751,6 +1486,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1797,6 +1541,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1806,34 +1559,109 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1845,22 +1673,79 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1869,14 +1754,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3372,85 +3272,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="93"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="93"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3470,46 +3370,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="79" t="s">
+      <c r="H13" s="91"/>
+      <c r="I13" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="91"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="79"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="91"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="79"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="91"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3518,13 +3418,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="80" t="s">
+      <c r="G17" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="93"/>
+      <c r="K17" s="93"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4538,19 +4438,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="65" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="84"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4562,194 +4462,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="67" t="s">
+      <c r="G2" s="81"/>
+      <c r="H2" s="86">
+        <v>46183</v>
+      </c>
+      <c r="I2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="70">
-        <v>46183</v>
-      </c>
-      <c r="I2" s="72" t="s">
+      <c r="J2" s="75"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="94"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="111"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="95"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="114" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="123" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="124"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="41" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="46"/>
+    </row>
+    <row r="8" spans="1:10" ht="47.25" customHeight="1">
+      <c r="A8" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="66"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="101"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="98" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="41" t="s">
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
+    </row>
+    <row r="9" spans="1:10" ht="297" customHeight="1">
+      <c r="A9" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="71" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="67"/>
+      <c r="D9" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
+    </row>
+    <row r="10" spans="1:10" ht="396" customHeight="1">
+      <c r="A10" s="69"/>
+      <c r="B10" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="67"/>
+      <c r="D10" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="49"/>
+    </row>
+    <row r="11" spans="1:10" ht="212.25" customHeight="1">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="67"/>
+      <c r="D11" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
+    </row>
+    <row r="12" spans="1:10" ht="53.25" customHeight="1">
+      <c r="A12" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="101"/>
-    </row>
-    <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="98" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="99"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="101"/>
-    </row>
-    <row r="9" spans="1:10" ht="220.5" customHeight="1">
-      <c r="A9" s="117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="97"/>
-      <c r="D9" s="125" t="s">
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="46"/>
+    </row>
+    <row r="13" spans="1:10" ht="47.25" customHeight="1" thickBot="1">
+      <c r="A13" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="127"/>
-    </row>
-    <row r="10" spans="1:10" ht="393.75" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="96" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="97"/>
-      <c r="D10" s="125" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="126"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="127"/>
-    </row>
-    <row r="11" spans="1:10" ht="135.75" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="125" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="126"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="127"/>
-    </row>
-    <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="98" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="101"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="102" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="103"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="120" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="122"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5740,6 +5640,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5748,25 +5667,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5785,19 +5685,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5809,40 +5709,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68"/>
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="110"/>
       <c r="H2" s="72"/>
       <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="130"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="129"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7198,19 +7098,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7222,48 +7122,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="110"/>
+      <c r="H2" s="86">
         <v>46190</v>
       </c>
       <c r="I2" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="J2" s="73"/>
+        <v>97</v>
+      </c>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="130"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="129"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8614,19 +8514,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8638,400 +8538,400 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="110"/>
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
       <c r="I2" s="72" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="75"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="119" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="120"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="104"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="118"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="104"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="118"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="104"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="118"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="104"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="118"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="104"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="118"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="104"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="118"/>
+    </row>
+    <row r="14" spans="1:10" ht="24" customHeight="1">
+      <c r="A14" s="104"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="118"/>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1">
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="118"/>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1">
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="118"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="118"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="118"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="118"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="114"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="90"/>
+      <c r="J22" s="114"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="59"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="58"/>
-    </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="58"/>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="58"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="58"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="58"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="58"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="42"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="42"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="48" t="s">
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="41" t="s">
+      <c r="F24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="42"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="48"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="42"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
+      <c r="A26" s="126"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="42"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="42"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="42"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="45"/>
+      <c r="A29" s="127"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="129"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="47"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="131"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10012,6 +9912,22 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -10027,22 +9943,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10065,19 +9965,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -10089,426 +9989,426 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="110"/>
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
       <c r="I2" s="72" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="75"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="119" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="120"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="115" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="132"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="118"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="132"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="118"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="132"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="118"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="132"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="118"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="132"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="118"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="132"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="118"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="132"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="118"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="118"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="118"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="118"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="118"/>
+    </row>
+    <row r="19" spans="1:10" ht="21" customHeight="1">
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="118"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="104"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="118"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="114"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="113" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="90"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="56"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="58"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="58"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="58"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="58"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="58"/>
-    </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="58"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="59"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="58"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="42"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="48" t="s">
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="41" t="s">
+      <c r="F25" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="42"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="48" t="s">
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="17" t="s">
+      <c r="B26" s="124"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E26" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="17" t="s">
+      <c r="G26" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="41" t="s">
+      <c r="H26" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="42"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="42"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="42"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="42"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="38"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40"/>
+      <c r="A29" s="126"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="91"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="42"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="45"/>
+      <c r="A30" s="127"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="129"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="47"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="128"/>
+      <c r="J30" s="131"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11489,6 +11389,22 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11504,22 +11420,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11542,19 +11442,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11566,388 +11466,388 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="110"/>
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
       <c r="I2" s="72" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="75"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="119" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="120"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="132"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="118"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="132"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="118"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="132"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="118"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="132"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="118"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="104"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="118"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="104"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="118"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="104"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="118"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="118"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="118"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="118"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="118"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="118"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="114"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="90"/>
+      <c r="J22" s="114"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="77" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="59"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="58"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="58"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="58"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="58"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="58"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="58"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="42"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="42"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="48" t="s">
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="17" t="s">
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E24" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="F24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>88</v>
-      </c>
       <c r="G24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="42"/>
+        <v>82</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="38"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
+      <c r="A25" s="126"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="42"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
+      <c r="A26" s="126"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="42"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="42"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="45"/>
+      <c r="A28" s="127"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="129"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="47"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="131"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12928,14 +12828,11 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12952,11 +12849,14 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12976,182 +12876,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="78" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="78" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="109"/>
+      <c r="S1" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="121"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="110"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="117"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="118"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="142"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="65" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="66"/>
-      <c r="S1" s="65" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="78"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="55"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="58"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="130"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="133"/>
-      <c r="T4" s="138"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="75" t="s">
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="123" t="s">
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="121"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="78"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
+      <c r="T6" s="114"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="42"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="51" t="s">
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="42"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="90"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="90"/>
+      <c r="T7" s="114"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13179,11 +13079,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -13213,7 +13113,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -13243,7 +13143,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -13273,7 +13173,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -13303,7 +13203,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -13350,79 +13250,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="113" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="91"/>
+      <c r="C15" s="141" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="91"/>
+      <c r="E15" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="141" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="52" t="s">
+      <c r="F15" s="91"/>
+      <c r="G15" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="52" t="s">
+      <c r="H15" s="90"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="52" t="s">
+      <c r="K15" s="91"/>
+      <c r="L15" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="52" t="s">
+      <c r="M15" s="90"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="52" t="s">
+      <c r="P15" s="90"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="T15" s="32" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="134">
+        <v>1</v>
+      </c>
+      <c r="B16" s="91"/>
+      <c r="C16" s="135" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="139">
-        <v>1</v>
-      </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="140" t="s">
+      <c r="D16" s="91"/>
+      <c r="E16" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="140" t="s">
+      <c r="F16" s="91"/>
+      <c r="G16" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="134" t="s">
+      <c r="H16" s="90"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="134" t="s">
+      <c r="K16" s="91"/>
+      <c r="L16" s="138" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="136" t="s">
+      <c r="M16" s="90"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="138" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="136" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
+      <c r="P16" s="90"/>
+      <c r="Q16" s="91"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13434,37 +13334,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="139">
+      <c r="A17" s="134">
         <v>2</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="140" t="s">
+      <c r="B17" s="91"/>
+      <c r="C17" s="135" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="91"/>
+      <c r="E17" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="140" t="s">
+      <c r="F17" s="91"/>
+      <c r="G17" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="134" t="s">
+      <c r="H17" s="90"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="140" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="134" t="s">
+      <c r="K17" s="91"/>
+      <c r="L17" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="136" t="s">
+      <c r="M17" s="90"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="136" t="s">
-        <v>66</v>
-      </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="91"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13476,23 +13376,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="139"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="40"/>
+      <c r="A18" s="134"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="138"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="138"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13504,23 +13404,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="139"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="140"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="134"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
+      <c r="A19" s="134"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="138"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="138"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="91"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13532,23 +13432,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="139"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="40"/>
+      <c r="A20" s="134"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="138"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="91"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13560,23 +13460,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="139"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
+      <c r="A21" s="134"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="138"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="138"/>
+      <c r="P21" s="90"/>
+      <c r="Q21" s="91"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13588,23 +13488,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="139"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="40"/>
+      <c r="A22" s="134"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="91"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="138"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="91"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13616,23 +13516,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="139"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="136"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
+      <c r="A23" s="134"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="138"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="91"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13644,23 +13544,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="139"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="134"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="136"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="136"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
+      <c r="A24" s="134"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="138"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="91"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13672,23 +13572,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="139"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
+      <c r="A25" s="134"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="138"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="138"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="91"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13700,23 +13600,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="139"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="40"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="91"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13728,23 +13628,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="139"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="134"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
+      <c r="A27" s="134"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="91"/>
+      <c r="L27" s="138"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="138"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="91"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13756,23 +13656,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="139"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="134"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="40"/>
+      <c r="A28" s="134"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="135"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="140"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="91"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13784,23 +13684,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="139"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="134"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="136"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
+      <c r="A29" s="134"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="140"/>
+      <c r="K29" s="91"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="91"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13812,23 +13712,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="139"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="134"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="40"/>
+      <c r="A30" s="134"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="140"/>
+      <c r="K30" s="91"/>
+      <c r="L30" s="138"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="138"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="91"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13840,23 +13740,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="142"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="143"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="143"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="135"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="135"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="45"/>
+      <c r="A31" s="136"/>
+      <c r="B31" s="129"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="137"/>
+      <c r="F31" s="129"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="128"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="139"/>
+      <c r="M31" s="128"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="139"/>
+      <c r="P31" s="128"/>
+      <c r="Q31" s="129"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14854,6 +14754,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14878,118 +14890,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D9607E-664B-427F-8C0E-D1FBA40FF2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504AB944-D514-4BF6-8E13-156BA6634E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="17910" windowHeight="9975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>イベントフロー</t>
-  </si>
-  <si>
-    <t>基本フロー</t>
   </si>
   <si>
     <t>代替フロー</t>
@@ -520,165 +517,75 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>削除対象のタスクを担当している従業員がログインしており、
-一覧表示画面でタスクを１件以上表示している</t>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="41" eb="44">
-      <t>ケンイジョウ</t>
-    </rPh>
+    <t>・従業員がログインしており、タスク一覧表示画面が表示されていること。
+・削除対象のタスクがデータベースに登録されていること。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>基本フロー</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除確認画面表示後に対象タスクが削除・改ざんされる可能性を考慮し、削除実行時にも存在確認および権限確認を再実施する。</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">
-E1:データベース接続失敗した場合
-E1-1:基本フロー4または9でシステムがデータベース接続に失敗する
-E1-2:システムは削除失敗画面を表示する。
-E1-3:システムは「システムエラーが発生しました。しばらくしてから再度お試しください。」を表示する</t>
-    <rPh sb="66" eb="68">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.従業員がタスク一覧画面を表示する
-2.従業員は削除したいタスクに対応したラジオボタンを選択する
-(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
-3.従業員が「削除」ボタンを押下する
-4.システムが選択されたタスク情報を取得する。
-5.システムは削除対象タスクの内容を表示したタスク削除確認画面を表示する
-6.従業員が「削除実行」ボタンを押下する
-7.システムは削除対象タスクの担当者とログインユーザが一致していること確認する。
-8.システムは削除対象タスクが存在していることを確認する。
-9. システムは削除対象タスクをデータベースから削除する。
-10. システムは削除したタスクの内容を表示したタスク削除完了画面を表示する
-11.従業員は「メニュー画面へ」を押下する
-12.システムはメニュー画面を表示する
-</t>
-    <rPh sb="25" eb="27">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="173" eb="175">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="192" eb="194">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="220" eb="222">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="233" eb="235">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="235" eb="237">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="241" eb="243">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="250" eb="252">
-      <t>カクニン</t>
-    </rPh>
+E1.基本フロー7において、データベースへの削除処理に失敗した場合
+E1-1.システムはタスク情報を削除せず、タスク削除失敗画面を表示する
+E1-2.従業員はエラー画面に従い、「メニュー画面へ」ボタンを押下する
+E1-3.システムはメニュー画面を表示する
+E1-4.従業員は必要に応じて本ユースケースを再実行する
+E2.基本フロー3において、削除対象タスク情報の取得に失敗した場合
+E2-1.システムはタスク削除確認画面を表示せず、タスク一覧表示画面を再表示する
+E2-2.システムは「データベース情報の取得に失敗しました。」とエラーメッセージを表示する
+E2-3.従業員は必要に応じて本ユースケースを再実行する</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t xml:space="preserve">
-A1:タスク未選択で削除実行ボタン押下した場合
-A1-1:基本フロー3でシステムはタスク未選択を検出する
-A1-2:システムは一覧画面を再表示する
-A1-3:システムは「削除するタスクを選択してください。」と表示する
-A2:削除をキャンセルする場合
-A2-1:基本フロー5で従業員はタスク削除確認画面で「一覧表示へ」を押下する
-A2-2:システムは削除処理を実行しない
-A2-3:システムは一覧表示画面を表示する
-A3：ログインユーザとタスク担当者が不一致の状態で削除実行した場合
-A3-1：基本フロー4でシステムは選択されたタスクの担当者IDを取得する
-A3-2：基本フロー7でログイン中のユーザIDと担当者IDを比較する
-A3-3：担当者IDが一致しないことを検出する
-A3-4：システムは削除処理を実行しない
-A3-5：システムは削除失敗画面でエラーメッセージ「削除できるタスクがありません」を表示する
-A3-6：従業員は削除失敗画面で「メニューへ」を押下する
-A3-7：システムはメニュー画面を表示する
-A4：対象タスクが既に削除されている場合
-A4-1. 基本フロー4または8で、システムは対象タスクが存在しないことを検出する。
-A4-2. システムは削除処理を実行しない。
-A4-3：システムは削除失敗画面を表示する
-A4-4：従業員は削除失敗画面で「メニューへ」を押下する
-A4-5：システムはメニュー画面を表示する
+A1.タスク一覧表示画面にて、タスク未選択で削除ボタンを押下した場合
+A1-1.基本フロー2において、システムはタスク未選択を検出する
+A1-2.システムはタスク一覧表示画面を再表示する
+A1-3.システムは「削除するタスクを選択してください。」というエラーメッセージを表示する
+A1-4.従業員はエラーメッセージに従いタスクを選択し、基本フロー1から再試行する
+A2.基本フロー3において、削除対象タスクが存在しない、または削除対象タスクの担当者とログインユーザが一致しない場合
+A2-1.システムは削除対象タスクの担当者とログインユーザが一致しないこと、または削除対象タスクが存在していないことを検出する
+A2-2.システムはタスク一覧表示画面を再表示し、エラーメッセージ「選択されたタスクに削除権限がないか、存在していません」を表示する
+A2-3.従業員は必要に応じて本ユースケースを再実行する
+A3.基本フロー6において、削除対象タスクが存在しない、または削除対象タスクの担当者とログインユーザが一致しない場合
+A3-1.システムは削除対象タスクの担当者とログインユーザが一致しないこと、または削除対象タスクが存在していないことを検出する。
+A3-2.システムはタスク削除失敗画面を表示し、エラーメッセージ「選択されたタスクに削除権限がないか、存在していません」を表示する。
+A3-3.従業員は「メニュー画面へ」ボタンを押下する。
+A3-4.システムはメニュー画面を表示する。
+A3-5.従業員は「タスク一覧表示」ボタンを押下する。
+A3-6.システムはタスク一覧表示画面を表示する。
+A3-7.従業員は必要に応じて本ユースケースを再実行する。
+A4.基本フロー4において、削除を中止する場合
+A4-1.従業員は「一覧表示へ」ボタンを押下する
+A4-2.システムはタスク一覧表示画面を表示する
+A4-3.従業員は必要に応じて本ユースケースを再実行する
 </t>
-    <rPh sb="14" eb="16">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="133" eb="135">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="140" eb="143">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="147" eb="149">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="149" eb="153">
-      <t>カクニンガメン</t>
-    </rPh>
-    <rPh sb="155" eb="159">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="162" eb="164">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="198" eb="202">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="202" eb="204">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="205" eb="207">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="236" eb="238">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="287" eb="289">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="371" eb="377">
-      <t>サクジョシッパイガメン</t>
-    </rPh>
-    <rPh sb="388" eb="390">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="413" eb="416">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="432" eb="434">
-      <t>オウカ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>削除対象の確認画面表示後に対象タスクが削除・改ざんされる可能性を考慮し、削除実行時に存在確認および権限確認を行う。</t>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>カクニンガメン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>オコナ</t>
+    <t xml:space="preserve">1.従業員は削除したいタスクに対応したラジオボタンを選択する
+（従業員本人が担当者でないタスクにはラジオボタンが表示されません）
+2.従業員は「削除」ボタンを押下する
+3.システムは削除対象タスクを取得し、以下の内容を確認する
+・選択されたタスクがデータベース上に存在していること
+・削除対象タスクの担当者とログインユーザが一致していること
+4.システムはタスク削除確認画面を表示する
+（この際、削除対象タスクの情報を表示する）
+5.従業員は「削除」ボタンを押下する
+6.システムは以下の内容を確認する
+・削除対象タスクが存在していること
+・削除対象タスクの担当者とログインユーザが一致していること
+7.システムは選択されたタスクをデータベースから削除する
+8.システムはタスク削除完了画面を表示する
+</t>
+    <rPh sb="348" eb="350">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1560,145 +1467,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1716,16 +1491,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1744,6 +1528,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1818,6 +1605,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1830,10 +1620,55 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1845,7 +1680,79 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3372,85 +3279,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="93"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="93"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3470,46 +3377,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="79" t="s">
+      <c r="G13" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="79" t="s">
+      <c r="H13" s="91"/>
+      <c r="I13" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="91"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="79"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="91"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="79"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="91"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3518,13 +3425,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="80" t="s">
+      <c r="G17" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="93"/>
+      <c r="K17" s="93"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4538,19 +4445,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="65" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="84"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4562,194 +4469,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="67" t="s">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
+        <v>46183</v>
+      </c>
+      <c r="I2" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="70">
-        <v>46183</v>
-      </c>
-      <c r="I2" s="72" t="s">
+      <c r="J2" s="52"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="54"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="94"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="111"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="95"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="114" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="123" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="124"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="41" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="61"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="58"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
+    </row>
+    <row r="8" spans="1:10" ht="47.25" customHeight="1">
+      <c r="A8" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="101"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="98" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="41" t="s">
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+    </row>
+    <row r="9" spans="1:10" ht="297" customHeight="1">
+      <c r="A9" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="56"/>
+      <c r="D9" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="88"/>
+    </row>
+    <row r="10" spans="1:10" ht="409.5" customHeight="1">
+      <c r="A10" s="78"/>
+      <c r="B10" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="86" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="88"/>
+    </row>
+    <row r="11" spans="1:10" ht="231" customHeight="1">
+      <c r="A11" s="79"/>
+      <c r="B11" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="86" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="88"/>
+    </row>
+    <row r="12" spans="1:10" ht="53.25" customHeight="1">
+      <c r="A12" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="101"/>
-    </row>
-    <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="98" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="99"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="101"/>
-    </row>
-    <row r="9" spans="1:10" ht="220.5" customHeight="1">
-      <c r="A9" s="117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="97"/>
-      <c r="D9" s="125" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="127"/>
-    </row>
-    <row r="10" spans="1:10" ht="393.75" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="96" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="97"/>
-      <c r="D10" s="125" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="126"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="127"/>
-    </row>
-    <row r="11" spans="1:10" ht="135.75" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="125" t="s">
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+    </row>
+    <row r="13" spans="1:10" ht="47.25" customHeight="1" thickBot="1">
+      <c r="A13" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="126"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="127"/>
-    </row>
-    <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="98" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="101"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="102" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="103"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="120" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="122"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="82"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5785,19 +5692,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5809,40 +5716,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="130"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="129"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7198,19 +7105,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7222,48 +7129,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="110"/>
+      <c r="H2" s="46">
         <v>46190</v>
       </c>
-      <c r="I2" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="J2" s="73"/>
+      <c r="I2" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="130"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="129"/>
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8614,19 +8521,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -8638,400 +8545,400 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="110"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="52"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="129" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="130"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="131"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="123" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="104"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="128"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="104"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="128"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="104"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="128"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="104"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="128"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="104"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="128"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="104"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="128"/>
+    </row>
+    <row r="14" spans="1:10" ht="24" customHeight="1">
+      <c r="A14" s="104"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="128"/>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1">
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="128"/>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1">
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="128"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="128"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="128"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="128"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="114"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="123" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="123" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="124" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="90"/>
+      <c r="J22" s="114"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1">
-      <c r="A14" s="59"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="58"/>
-    </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="58"/>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="58"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="58"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="58"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="58"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="42"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="42"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="48" t="s">
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="41" t="s">
+      <c r="F24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="42"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="48"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
+      <c r="A25" s="120"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="122"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="42"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
+      <c r="A26" s="113"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="42"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="42"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
+      <c r="A28" s="113"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="42"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="45"/>
+      <c r="A29" s="115"/>
+      <c r="B29" s="116"/>
+      <c r="C29" s="117"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="47"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="119"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10065,19 +9972,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -10089,426 +9996,426 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="110"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="52"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="129" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="130"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="131"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="123" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="125" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="132"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="128"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="132"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="128"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="132"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="128"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="132"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="128"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="132"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="128"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="132"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="128"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="132"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="128"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="128"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="128"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="128"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="128"/>
+    </row>
+    <row r="19" spans="1:10" ht="21" customHeight="1">
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="128"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="104"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="93"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="93"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="128"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="114"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="123" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="91"/>
+      <c r="I22" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="123" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="90"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="124" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="56"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="58"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="58"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="58"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="58"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="58"/>
-    </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="58"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="59"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="58"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="42"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="48" t="s">
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="B25" s="121"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="41" t="s">
+      <c r="F25" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="42"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="48" t="s">
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="17" t="s">
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E26" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="17" t="s">
+      <c r="G26" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="41" t="s">
+      <c r="H26" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="42"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="42"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="42"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
+      <c r="A28" s="113"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="42"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="38"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40"/>
+      <c r="A29" s="113"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="91"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="42"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="45"/>
+      <c r="A30" s="115"/>
+      <c r="B30" s="116"/>
+      <c r="C30" s="117"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="47"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="116"/>
+      <c r="J30" s="119"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11542,19 +11449,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="65" t="s">
+      <c r="A1" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="65" t="s">
+      <c r="E1" s="109"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -11566,388 +11473,388 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="67" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="110"/>
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="70">
+      <c r="G2" s="110"/>
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="52"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="99"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="104"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="99"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="129" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="130"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="84" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="131"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="123" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="114"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="132"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="128"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="132"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="128"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="132"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="128"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="132"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="128"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="104"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="128"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="104"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="128"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="104"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="128"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="104"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="128"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="104"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="128"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="104"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="93"/>
+      <c r="G17" s="93"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="128"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="104"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="128"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="104"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="128"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="114"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="123" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="91"/>
+      <c r="I21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="123" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="124" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="90"/>
+      <c r="J22" s="114"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="73"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="74"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="77" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="59"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="58"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="58"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="58"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="58"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="58"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="58"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="42"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
-      <c r="I21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="42"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="48" t="s">
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="90"/>
+      <c r="J23" s="114"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="17" t="s">
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E24" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="F24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>88</v>
-      </c>
       <c r="G24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="42"/>
+        <v>82</v>
+      </c>
+      <c r="H24" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" s="90"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="38"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
+      <c r="A25" s="113"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="42"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="38"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
+      <c r="A26" s="113"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="42"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="42"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="45"/>
+      <c r="A28" s="115"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="117"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="47"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="116"/>
+      <c r="J28" s="119"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12976,182 +12883,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="109"/>
+      <c r="S1" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="131"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="104"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="110"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="127"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="104"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="128"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="112"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="138"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="65" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="66"/>
-      <c r="S1" s="65" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="78"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="68"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="55"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="69"/>
-      <c r="T3" s="58"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="130"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="133"/>
-      <c r="T4" s="138"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="75" t="s">
+      <c r="B5" s="130"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="123" t="s">
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="130"/>
+      <c r="K5" s="130"/>
+      <c r="L5" s="130"/>
+      <c r="M5" s="130"/>
+      <c r="N5" s="130"/>
+      <c r="O5" s="130"/>
+      <c r="P5" s="130"/>
+      <c r="Q5" s="130"/>
+      <c r="R5" s="130"/>
+      <c r="S5" s="130"/>
+      <c r="T5" s="131"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="78"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
+      <c r="T6" s="114"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="42"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="51" t="s">
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="91"/>
+      <c r="G7" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="42"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="90"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="90"/>
+      <c r="Q7" s="90"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="90"/>
+      <c r="T7" s="114"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13179,11 +13086,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -13213,7 +13120,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -13243,7 +13150,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -13273,7 +13180,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -13303,7 +13210,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -13350,79 +13257,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="123" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="91"/>
+      <c r="C15" s="141" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="91"/>
+      <c r="E15" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="141" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="52" t="s">
+      <c r="F15" s="91"/>
+      <c r="G15" s="124" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="52" t="s">
+      <c r="H15" s="90"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="52" t="s">
+      <c r="K15" s="91"/>
+      <c r="L15" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="52" t="s">
+      <c r="M15" s="90"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="52" t="s">
+      <c r="P15" s="90"/>
+      <c r="Q15" s="91"/>
+      <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>53</v>
-      </c>
-      <c r="T15" s="32" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
       <c r="A16" s="139">
         <v>1</v>
       </c>
-      <c r="B16" s="40"/>
+      <c r="B16" s="91"/>
       <c r="C16" s="140" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="91"/>
+      <c r="E16" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="140" t="s">
+      <c r="F16" s="91"/>
+      <c r="G16" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="134" t="s">
+      <c r="H16" s="90"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="134" t="s">
+      <c r="K16" s="91"/>
+      <c r="L16" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="136" t="s">
+      <c r="M16" s="90"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="136" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="136" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
+      <c r="P16" s="90"/>
+      <c r="Q16" s="91"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13437,34 +13344,34 @@
       <c r="A17" s="139">
         <v>2</v>
       </c>
-      <c r="B17" s="40"/>
+      <c r="B17" s="91"/>
       <c r="C17" s="140" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="91"/>
+      <c r="E17" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="140" t="s">
+      <c r="F17" s="91"/>
+      <c r="G17" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="134" t="s">
+      <c r="H17" s="90"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="134" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="134" t="s">
+      <c r="K17" s="91"/>
+      <c r="L17" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="136" t="s">
+      <c r="M17" s="90"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="136" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="136" t="s">
-        <v>66</v>
-      </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="91"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13477,22 +13384,22 @@
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
       <c r="A18" s="139"/>
-      <c r="B18" s="40"/>
+      <c r="B18" s="91"/>
       <c r="C18" s="140"/>
-      <c r="D18" s="40"/>
+      <c r="D18" s="91"/>
       <c r="E18" s="140"/>
-      <c r="F18" s="40"/>
+      <c r="F18" s="91"/>
       <c r="G18" s="134"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="91"/>
       <c r="J18" s="134"/>
-      <c r="K18" s="40"/>
+      <c r="K18" s="91"/>
       <c r="L18" s="136"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="91"/>
       <c r="O18" s="136"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="40"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="91"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13505,22 +13412,22 @@
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
       <c r="A19" s="139"/>
-      <c r="B19" s="40"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="140"/>
-      <c r="D19" s="40"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="140"/>
-      <c r="F19" s="40"/>
+      <c r="F19" s="91"/>
       <c r="G19" s="134"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="91"/>
       <c r="J19" s="134"/>
-      <c r="K19" s="40"/>
+      <c r="K19" s="91"/>
       <c r="L19" s="136"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="91"/>
       <c r="O19" s="136"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="91"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13533,22 +13440,22 @@
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
       <c r="A20" s="139"/>
-      <c r="B20" s="40"/>
+      <c r="B20" s="91"/>
       <c r="C20" s="140"/>
-      <c r="D20" s="40"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="140"/>
-      <c r="F20" s="40"/>
+      <c r="F20" s="91"/>
       <c r="G20" s="134"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="91"/>
       <c r="J20" s="134"/>
-      <c r="K20" s="40"/>
+      <c r="K20" s="91"/>
       <c r="L20" s="136"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="91"/>
       <c r="O20" s="136"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="40"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="91"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13561,22 +13468,22 @@
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
       <c r="A21" s="139"/>
-      <c r="B21" s="40"/>
+      <c r="B21" s="91"/>
       <c r="C21" s="140"/>
-      <c r="D21" s="40"/>
+      <c r="D21" s="91"/>
       <c r="E21" s="140"/>
-      <c r="F21" s="40"/>
+      <c r="F21" s="91"/>
       <c r="G21" s="134"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="91"/>
       <c r="J21" s="134"/>
-      <c r="K21" s="40"/>
+      <c r="K21" s="91"/>
       <c r="L21" s="136"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="91"/>
       <c r="O21" s="136"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
+      <c r="P21" s="90"/>
+      <c r="Q21" s="91"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13589,22 +13496,22 @@
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
       <c r="A22" s="139"/>
-      <c r="B22" s="40"/>
+      <c r="B22" s="91"/>
       <c r="C22" s="140"/>
-      <c r="D22" s="40"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="140"/>
-      <c r="F22" s="40"/>
+      <c r="F22" s="91"/>
       <c r="G22" s="134"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="91"/>
       <c r="J22" s="134"/>
-      <c r="K22" s="40"/>
+      <c r="K22" s="91"/>
       <c r="L22" s="136"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="91"/>
       <c r="O22" s="136"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="40"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="91"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13617,22 +13524,22 @@
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
       <c r="A23" s="139"/>
-      <c r="B23" s="40"/>
+      <c r="B23" s="91"/>
       <c r="C23" s="140"/>
-      <c r="D23" s="40"/>
+      <c r="D23" s="91"/>
       <c r="E23" s="140"/>
-      <c r="F23" s="40"/>
+      <c r="F23" s="91"/>
       <c r="G23" s="134"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="91"/>
       <c r="J23" s="134"/>
-      <c r="K23" s="40"/>
+      <c r="K23" s="91"/>
       <c r="L23" s="136"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="91"/>
       <c r="O23" s="136"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="91"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13645,22 +13552,22 @@
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
       <c r="A24" s="139"/>
-      <c r="B24" s="40"/>
+      <c r="B24" s="91"/>
       <c r="C24" s="140"/>
-      <c r="D24" s="40"/>
+      <c r="D24" s="91"/>
       <c r="E24" s="140"/>
-      <c r="F24" s="40"/>
+      <c r="F24" s="91"/>
       <c r="G24" s="134"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="91"/>
       <c r="J24" s="134"/>
-      <c r="K24" s="40"/>
+      <c r="K24" s="91"/>
       <c r="L24" s="136"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="91"/>
       <c r="O24" s="136"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="91"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13673,22 +13580,22 @@
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="139"/>
-      <c r="B25" s="40"/>
+      <c r="B25" s="91"/>
       <c r="C25" s="140"/>
-      <c r="D25" s="40"/>
+      <c r="D25" s="91"/>
       <c r="E25" s="140"/>
-      <c r="F25" s="40"/>
+      <c r="F25" s="91"/>
       <c r="G25" s="134"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="91"/>
       <c r="J25" s="134"/>
-      <c r="K25" s="40"/>
+      <c r="K25" s="91"/>
       <c r="L25" s="136"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="91"/>
       <c r="O25" s="136"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="91"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13701,22 +13608,22 @@
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="139"/>
-      <c r="B26" s="40"/>
+      <c r="B26" s="91"/>
       <c r="C26" s="140"/>
-      <c r="D26" s="40"/>
+      <c r="D26" s="91"/>
       <c r="E26" s="140"/>
-      <c r="F26" s="40"/>
+      <c r="F26" s="91"/>
       <c r="G26" s="134"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="91"/>
       <c r="J26" s="134"/>
-      <c r="K26" s="40"/>
+      <c r="K26" s="91"/>
       <c r="L26" s="136"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="91"/>
       <c r="O26" s="136"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="40"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="91"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13729,22 +13636,22 @@
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
       <c r="A27" s="139"/>
-      <c r="B27" s="40"/>
+      <c r="B27" s="91"/>
       <c r="C27" s="140"/>
-      <c r="D27" s="40"/>
+      <c r="D27" s="91"/>
       <c r="E27" s="140"/>
-      <c r="F27" s="40"/>
+      <c r="F27" s="91"/>
       <c r="G27" s="134"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="91"/>
       <c r="J27" s="134"/>
-      <c r="K27" s="40"/>
+      <c r="K27" s="91"/>
       <c r="L27" s="136"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="91"/>
       <c r="O27" s="136"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="91"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13757,22 +13664,22 @@
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
       <c r="A28" s="139"/>
-      <c r="B28" s="40"/>
+      <c r="B28" s="91"/>
       <c r="C28" s="140"/>
-      <c r="D28" s="40"/>
+      <c r="D28" s="91"/>
       <c r="E28" s="140"/>
-      <c r="F28" s="40"/>
+      <c r="F28" s="91"/>
       <c r="G28" s="134"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="91"/>
       <c r="J28" s="134"/>
-      <c r="K28" s="40"/>
+      <c r="K28" s="91"/>
       <c r="L28" s="136"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
       <c r="O28" s="136"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="40"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="91"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13785,22 +13692,22 @@
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
       <c r="A29" s="139"/>
-      <c r="B29" s="40"/>
+      <c r="B29" s="91"/>
       <c r="C29" s="140"/>
-      <c r="D29" s="40"/>
+      <c r="D29" s="91"/>
       <c r="E29" s="140"/>
-      <c r="F29" s="40"/>
+      <c r="F29" s="91"/>
       <c r="G29" s="134"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="91"/>
       <c r="J29" s="134"/>
-      <c r="K29" s="40"/>
+      <c r="K29" s="91"/>
       <c r="L29" s="136"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="91"/>
       <c r="O29" s="136"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="91"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13813,22 +13720,22 @@
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
       <c r="A30" s="139"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="91"/>
       <c r="C30" s="140"/>
-      <c r="D30" s="40"/>
+      <c r="D30" s="91"/>
       <c r="E30" s="140"/>
-      <c r="F30" s="40"/>
+      <c r="F30" s="91"/>
       <c r="G30" s="134"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="91"/>
       <c r="J30" s="134"/>
-      <c r="K30" s="40"/>
+      <c r="K30" s="91"/>
       <c r="L30" s="136"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="40"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="91"/>
       <c r="O30" s="136"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="40"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="91"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13841,22 +13748,22 @@
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
       <c r="A31" s="142"/>
-      <c r="B31" s="45"/>
+      <c r="B31" s="117"/>
       <c r="C31" s="143"/>
-      <c r="D31" s="45"/>
+      <c r="D31" s="117"/>
       <c r="E31" s="143"/>
-      <c r="F31" s="45"/>
+      <c r="F31" s="117"/>
       <c r="G31" s="135"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="45"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="117"/>
       <c r="J31" s="135"/>
-      <c r="K31" s="45"/>
+      <c r="K31" s="117"/>
       <c r="L31" s="137"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="45"/>
+      <c r="M31" s="116"/>
+      <c r="N31" s="117"/>
       <c r="O31" s="137"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="45"/>
+      <c r="P31" s="116"/>
+      <c r="Q31" s="117"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504AB944-D514-4BF6-8E13-156BA6634E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896B4C38-F260-40B7-B8C6-3A1B215D21EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -543,6 +543,30 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t xml:space="preserve">1.従業員は削除したいタスクに対応したラジオボタンを選択する
+（従業員本人が担当者でないタスクにはラジオボタンが表示されません）
+2.従業員は「削除」ボタンを押下する
+3.システムは削除対象タスクを取得し、以下の内容を確認する
+・選択されたタスクがデータベース上に存在していること
+・削除対象タスクの担当者とログインユーザが一致していること
+4.システムはタスク削除確認画面を表示する
+（この際、削除対象タスクの情報を表示する）
+5.従業員は「削除実行」ボタンを押下する
+6.システムは以下の内容を確認する
+・削除対象タスクが存在していること
+・削除対象タスクの担当者とログインユーザが一致していること
+7.システムは選択されたタスクをデータベースから削除する
+8.システムはタスク削除完了画面を表示する
+</t>
+    <rPh sb="228" eb="230">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="350" eb="352">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t xml:space="preserve">
 A1.タスク一覧表示画面にて、タスク未選択で削除ボタンを押下した場合
 A1-1.基本フロー2において、システムはタスク未選択を検出する
@@ -566,27 +590,6 @@
 A4-2.システムはタスク一覧表示画面を表示する
 A4-3.従業員は必要に応じて本ユースケースを再実行する
 </t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.従業員は削除したいタスクに対応したラジオボタンを選択する
-（従業員本人が担当者でないタスクにはラジオボタンが表示されません）
-2.従業員は「削除」ボタンを押下する
-3.システムは削除対象タスクを取得し、以下の内容を確認する
-・選択されたタスクがデータベース上に存在していること
-・削除対象タスクの担当者とログインユーザが一致していること
-4.システムはタスク削除確認画面を表示する
-（この際、削除対象タスクの情報を表示する）
-5.従業員は「削除」ボタンを押下する
-6.システムは以下の内容を確認する
-・削除対象タスクが存在していること
-・削除対象タスクの担当者とログインユーザが一致していること
-7.システムは選択されたタスクをデータベースから削除する
-8.システムはタスク削除完了画面を表示する
-</t>
-    <rPh sb="348" eb="350">
-      <t>カンリョウ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1467,67 +1470,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1538,6 +1496,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1584,6 +1551,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1593,32 +1569,59 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1692,41 +1695,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1749,25 +1722,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1776,14 +1764,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4445,19 +4448,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="79"/>
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="79"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4469,194 +4472,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="81"/>
+      <c r="H2" s="86">
         <v>46183</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="76"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="83" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="59" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="61"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="59" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="86" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:10" ht="297" customHeight="1">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="86" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
+    </row>
+    <row r="10" spans="1:10" ht="409.5" customHeight="1">
+      <c r="A10" s="69"/>
+      <c r="B10" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="67"/>
+      <c r="D10" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="88"/>
-    </row>
-    <row r="10" spans="1:10" ht="409.5" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="88"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="49"/>
     </row>
     <row r="11" spans="1:10" ht="231" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="55" t="s">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="86" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="88"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="59" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="61"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="1:10" ht="47.25" customHeight="1" thickBot="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="80" t="s">
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="82"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5647,6 +5650,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5655,25 +5677,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5697,11 +5700,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -5719,13 +5722,13 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40"/>
+      <c r="D2" s="80"/>
       <c r="E2" s="110"/>
-      <c r="F2" s="40"/>
+      <c r="F2" s="80"/>
       <c r="G2" s="110"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="52"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -7110,11 +7113,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -7132,21 +7135,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="80" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="86">
         <v>46190</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -8526,11 +8529,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -8548,21 +8551,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="80" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -8589,23 +8592,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="130"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="131"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="113" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="90"/>
@@ -8619,16 +8622,16 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="125"/>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="127"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="104"/>
@@ -8640,7 +8643,7 @@
       <c r="G8" s="93"/>
       <c r="H8" s="93"/>
       <c r="I8" s="93"/>
-      <c r="J8" s="128"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="104"/>
@@ -8652,7 +8655,7 @@
       <c r="G9" s="93"/>
       <c r="H9" s="93"/>
       <c r="I9" s="93"/>
-      <c r="J9" s="128"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="104"/>
@@ -8664,7 +8667,7 @@
       <c r="G10" s="93"/>
       <c r="H10" s="93"/>
       <c r="I10" s="93"/>
-      <c r="J10" s="128"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="104"/>
@@ -8676,7 +8679,7 @@
       <c r="G11" s="93"/>
       <c r="H11" s="93"/>
       <c r="I11" s="93"/>
-      <c r="J11" s="128"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="104"/>
@@ -8688,7 +8691,7 @@
       <c r="G12" s="93"/>
       <c r="H12" s="93"/>
       <c r="I12" s="93"/>
-      <c r="J12" s="128"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="104"/>
@@ -8700,7 +8703,7 @@
       <c r="G13" s="93"/>
       <c r="H13" s="93"/>
       <c r="I13" s="93"/>
-      <c r="J13" s="128"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
       <c r="A14" s="104"/>
@@ -8712,7 +8715,7 @@
       <c r="G14" s="93"/>
       <c r="H14" s="93"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="128"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
       <c r="A15" s="104"/>
@@ -8724,7 +8727,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="128"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
       <c r="A16" s="104"/>
@@ -8736,7 +8739,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="128"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -8748,7 +8751,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="128"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -8760,7 +8763,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="128"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="104"/>
@@ -8772,10 +8775,10 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="128"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="90"/>
@@ -8789,12 +8792,12 @@
       <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="90"/>
       <c r="C21" s="91"/>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="44" t="s">
         <v>75</v>
       </c>
       <c r="E21" s="90"/>
@@ -8809,7 +8812,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="123" t="s">
+      <c r="A22" s="113" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="90"/>
@@ -8826,18 +8829,18 @@
       <c r="G22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="124" t="s">
+      <c r="H22" s="122" t="s">
         <v>19</v>
       </c>
       <c r="I22" s="90"/>
       <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="121"/>
-      <c r="C23" s="122"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
       <c r="D23" s="17" t="s">
         <v>80</v>
       </c>
@@ -8850,18 +8853,18 @@
       <c r="G23" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="59" t="s">
+      <c r="H23" s="44" t="s">
         <v>91</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="122"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
@@ -8874,71 +8877,71 @@
       <c r="G24" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="44" t="s">
         <v>92</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="120"/>
-      <c r="B25" s="121"/>
-      <c r="C25" s="122"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="59"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="113"/>
+      <c r="A26" s="126"/>
       <c r="B26" s="90"/>
       <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="59"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="113"/>
+      <c r="A28" s="126"/>
       <c r="B28" s="90"/>
       <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="59"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="90"/>
       <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="115"/>
-      <c r="B29" s="116"/>
-      <c r="C29" s="117"/>
+      <c r="A29" s="127"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="129"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="119"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="131"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9919,6 +9922,22 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9934,22 +9953,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9977,11 +9980,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -9999,21 +10002,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="80" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -10040,23 +10043,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="130"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="131"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="113" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="90"/>
@@ -10070,18 +10073,18 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="125" t="e" vm="1">
+      <c r="A7" s="115" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="127"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="132"/>
@@ -10093,7 +10096,7 @@
       <c r="G8" s="133"/>
       <c r="H8" s="133"/>
       <c r="I8" s="133"/>
-      <c r="J8" s="128"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="132"/>
@@ -10105,7 +10108,7 @@
       <c r="G9" s="133"/>
       <c r="H9" s="133"/>
       <c r="I9" s="133"/>
-      <c r="J9" s="128"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="132"/>
@@ -10117,7 +10120,7 @@
       <c r="G10" s="133"/>
       <c r="H10" s="133"/>
       <c r="I10" s="133"/>
-      <c r="J10" s="128"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="132"/>
@@ -10129,7 +10132,7 @@
       <c r="G11" s="133"/>
       <c r="H11" s="133"/>
       <c r="I11" s="133"/>
-      <c r="J11" s="128"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="132"/>
@@ -10141,7 +10144,7 @@
       <c r="G12" s="133"/>
       <c r="H12" s="133"/>
       <c r="I12" s="133"/>
-      <c r="J12" s="128"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="132"/>
@@ -10153,7 +10156,7 @@
       <c r="G13" s="133"/>
       <c r="H13" s="133"/>
       <c r="I13" s="133"/>
-      <c r="J13" s="128"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="132"/>
@@ -10165,7 +10168,7 @@
       <c r="G14" s="133"/>
       <c r="H14" s="133"/>
       <c r="I14" s="133"/>
-      <c r="J14" s="128"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="104"/>
@@ -10177,7 +10180,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="128"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
       <c r="A16" s="104"/>
@@ -10189,7 +10192,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="128"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -10201,7 +10204,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="128"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -10213,7 +10216,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="128"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
       <c r="A19" s="104"/>
@@ -10225,7 +10228,7 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="128"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="104"/>
@@ -10237,10 +10240,10 @@
       <c r="G20" s="93"/>
       <c r="H20" s="93"/>
       <c r="I20" s="93"/>
-      <c r="J20" s="128"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="113" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="90"/>
@@ -10254,12 +10257,12 @@
       <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="123" t="s">
+      <c r="A22" s="113" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="90"/>
       <c r="C22" s="91"/>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="44" t="s">
         <v>78</v>
       </c>
       <c r="E22" s="90"/>
@@ -10274,7 +10277,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="113" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="90"/>
@@ -10291,18 +10294,18 @@
       <c r="G23" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="124" t="s">
+      <c r="H23" s="122" t="s">
         <v>19</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="122"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>80</v>
       </c>
@@ -10315,18 +10318,18 @@
       <c r="G24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="44" t="s">
         <v>88</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="120" t="s">
+      <c r="A25" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="121"/>
-      <c r="C25" s="122"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
       <c r="D25" s="17" t="s">
         <v>83</v>
       </c>
@@ -10339,18 +10342,18 @@
       <c r="G25" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H25" s="59" t="s">
+      <c r="H25" s="44" t="s">
         <v>89</v>
       </c>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="120" t="s">
+      <c r="A26" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="121"/>
-      <c r="C26" s="122"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="125"/>
       <c r="D26" s="17" t="s">
         <v>84</v>
       </c>
@@ -10363,59 +10366,59 @@
       <c r="G26" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H26" s="59" t="s">
+      <c r="H26" s="44" t="s">
         <v>90</v>
       </c>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="113"/>
+      <c r="A28" s="126"/>
       <c r="B28" s="90"/>
       <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="59"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="90"/>
       <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="113"/>
+      <c r="A29" s="126"/>
       <c r="B29" s="90"/>
       <c r="C29" s="91"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="59"/>
+      <c r="H29" s="44"/>
       <c r="I29" s="90"/>
       <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="115"/>
-      <c r="B30" s="116"/>
-      <c r="C30" s="117"/>
+      <c r="A30" s="127"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="129"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="116"/>
-      <c r="J30" s="119"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="128"/>
+      <c r="J30" s="131"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11396,6 +11399,22 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11411,22 +11430,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11454,11 +11457,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="78" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="78" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -11476,21 +11479,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="80" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="80" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -11517,23 +11520,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="130"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="131"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="113" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="90"/>
@@ -11547,16 +11550,16 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="125"/>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="127"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="132"/>
@@ -11568,7 +11571,7 @@
       <c r="G8" s="133"/>
       <c r="H8" s="133"/>
       <c r="I8" s="133"/>
-      <c r="J8" s="128"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="132"/>
@@ -11580,7 +11583,7 @@
       <c r="G9" s="133"/>
       <c r="H9" s="133"/>
       <c r="I9" s="133"/>
-      <c r="J9" s="128"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="132"/>
@@ -11592,7 +11595,7 @@
       <c r="G10" s="133"/>
       <c r="H10" s="133"/>
       <c r="I10" s="133"/>
-      <c r="J10" s="128"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="132"/>
@@ -11604,7 +11607,7 @@
       <c r="G11" s="133"/>
       <c r="H11" s="133"/>
       <c r="I11" s="133"/>
-      <c r="J11" s="128"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="104"/>
@@ -11616,7 +11619,7 @@
       <c r="G12" s="93"/>
       <c r="H12" s="93"/>
       <c r="I12" s="93"/>
-      <c r="J12" s="128"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="104"/>
@@ -11628,7 +11631,7 @@
       <c r="G13" s="93"/>
       <c r="H13" s="93"/>
       <c r="I13" s="93"/>
-      <c r="J13" s="128"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="104"/>
@@ -11640,7 +11643,7 @@
       <c r="G14" s="93"/>
       <c r="H14" s="93"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="128"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="104"/>
@@ -11652,7 +11655,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="128"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
       <c r="A16" s="104"/>
@@ -11664,7 +11667,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="128"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -11676,7 +11679,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="128"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -11688,7 +11691,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="128"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="104"/>
@@ -11700,10 +11703,10 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="128"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="90"/>
@@ -11717,12 +11720,12 @@
       <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="90"/>
       <c r="C21" s="91"/>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="44" t="s">
         <v>75</v>
       </c>
       <c r="E21" s="90"/>
@@ -11737,7 +11740,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="123" t="s">
+      <c r="A22" s="113" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="90"/>
@@ -11754,18 +11757,18 @@
       <c r="G22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="124" t="s">
+      <c r="H22" s="122" t="s">
         <v>19</v>
       </c>
       <c r="I22" s="90"/>
       <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="121"/>
-      <c r="C23" s="122"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
       <c r="D23" s="17" t="s">
         <v>81</v>
       </c>
@@ -11778,18 +11781,18 @@
       <c r="G23" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="59" t="s">
+      <c r="H23" s="44" t="s">
         <v>94</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="122"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
@@ -11802,59 +11805,59 @@
       <c r="G24" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="44" t="s">
         <v>93</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="113"/>
+      <c r="A25" s="126"/>
       <c r="B25" s="90"/>
       <c r="C25" s="91"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="59"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="113"/>
+      <c r="A26" s="126"/>
       <c r="B26" s="90"/>
       <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="59"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
+      <c r="A27" s="126"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="115"/>
-      <c r="B28" s="116"/>
-      <c r="C28" s="117"/>
+      <c r="A28" s="127"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="129"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="119"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="131"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12835,14 +12838,11 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12859,11 +12859,14 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12883,7 +12886,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="53" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="102"/>
@@ -12891,30 +12894,30 @@
       <c r="D1" s="102"/>
       <c r="E1" s="102"/>
       <c r="F1" s="103"/>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
       <c r="J1" s="109"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
       <c r="N1" s="109"/>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="78" t="s">
         <v>8</v>
       </c>
       <c r="P1" s="109"/>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="78" t="s">
         <v>9</v>
       </c>
       <c r="R1" s="109"/>
-      <c r="S1" s="38" t="s">
+      <c r="S1" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="131"/>
+      <c r="T1" s="121"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="104"/>
@@ -12923,20 +12926,20 @@
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
       <c r="F2" s="105"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
       <c r="J2" s="110"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
       <c r="N2" s="110"/>
-      <c r="O2" s="40"/>
+      <c r="O2" s="80"/>
       <c r="P2" s="110"/>
-      <c r="Q2" s="40"/>
+      <c r="Q2" s="80"/>
       <c r="R2" s="110"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="127"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="117"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -12958,7 +12961,7 @@
       <c r="Q3" s="111"/>
       <c r="R3" s="105"/>
       <c r="S3" s="111"/>
-      <c r="T3" s="128"/>
+      <c r="T3" s="118"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="106"/>
@@ -12980,36 +12983,36 @@
       <c r="Q4" s="112"/>
       <c r="R4" s="108"/>
       <c r="S4" s="112"/>
-      <c r="T4" s="138"/>
+      <c r="T4" s="142"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
       <c r="F5" s="109"/>
-      <c r="G5" s="83" t="s">
+      <c r="G5" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="130"/>
-      <c r="Q5" s="130"/>
-      <c r="R5" s="130"/>
-      <c r="S5" s="130"/>
-      <c r="T5" s="131"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="121"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="113" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="90"/>
@@ -13017,7 +13020,7 @@
       <c r="D6" s="90"/>
       <c r="E6" s="90"/>
       <c r="F6" s="91"/>
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="44" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="90"/>
@@ -13035,7 +13038,7 @@
       <c r="T6" s="114"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="123" t="s">
+      <c r="A7" s="113" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="90"/>
@@ -13043,7 +13046,7 @@
       <c r="D7" s="90"/>
       <c r="E7" s="90"/>
       <c r="F7" s="91"/>
-      <c r="G7" s="59" t="s">
+      <c r="G7" s="44" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="90"/>
@@ -13257,7 +13260,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="123" t="s">
+      <c r="A15" s="113" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="91"/>
@@ -13265,25 +13268,25 @@
         <v>39</v>
       </c>
       <c r="D15" s="91"/>
-      <c r="E15" s="124" t="s">
+      <c r="E15" s="122" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="91"/>
-      <c r="G15" s="124" t="s">
+      <c r="G15" s="122" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="90"/>
       <c r="I15" s="91"/>
-      <c r="J15" s="124" t="s">
+      <c r="J15" s="122" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="91"/>
-      <c r="L15" s="124" t="s">
+      <c r="L15" s="122" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="90"/>
       <c r="N15" s="91"/>
-      <c r="O15" s="124" t="s">
+      <c r="O15" s="122" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="90"/>
@@ -13299,33 +13302,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="139">
+      <c r="A16" s="134">
         <v>1</v>
       </c>
       <c r="B16" s="91"/>
-      <c r="C16" s="140" t="s">
+      <c r="C16" s="135" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="91"/>
-      <c r="E16" s="140" t="s">
+      <c r="E16" s="135" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="91"/>
-      <c r="G16" s="134" t="s">
+      <c r="G16" s="140" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="90"/>
       <c r="I16" s="91"/>
-      <c r="J16" s="134" t="s">
+      <c r="J16" s="140" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="91"/>
-      <c r="L16" s="136" t="s">
+      <c r="L16" s="138" t="s">
         <v>58</v>
       </c>
       <c r="M16" s="90"/>
       <c r="N16" s="91"/>
-      <c r="O16" s="136" t="s">
+      <c r="O16" s="138" t="s">
         <v>59</v>
       </c>
       <c r="P16" s="90"/>
@@ -13341,33 +13344,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="139">
+      <c r="A17" s="134">
         <v>2</v>
       </c>
       <c r="B17" s="91"/>
-      <c r="C17" s="140" t="s">
+      <c r="C17" s="135" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="91"/>
-      <c r="E17" s="140" t="s">
+      <c r="E17" s="135" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="91"/>
-      <c r="G17" s="134" t="s">
+      <c r="G17" s="140" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="134" t="s">
+      <c r="J17" s="140" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="91"/>
-      <c r="L17" s="136" t="s">
+      <c r="L17" s="138" t="s">
         <v>64</v>
       </c>
       <c r="M17" s="90"/>
       <c r="N17" s="91"/>
-      <c r="O17" s="136" t="s">
+      <c r="O17" s="138" t="s">
         <v>65</v>
       </c>
       <c r="P17" s="90"/>
@@ -13383,21 +13386,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="139"/>
+      <c r="A18" s="134"/>
       <c r="B18" s="91"/>
-      <c r="C18" s="140"/>
+      <c r="C18" s="135"/>
       <c r="D18" s="91"/>
-      <c r="E18" s="140"/>
+      <c r="E18" s="135"/>
       <c r="F18" s="91"/>
-      <c r="G18" s="134"/>
+      <c r="G18" s="140"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="134"/>
+      <c r="J18" s="140"/>
       <c r="K18" s="91"/>
-      <c r="L18" s="136"/>
+      <c r="L18" s="138"/>
       <c r="M18" s="90"/>
       <c r="N18" s="91"/>
-      <c r="O18" s="136"/>
+      <c r="O18" s="138"/>
       <c r="P18" s="90"/>
       <c r="Q18" s="91"/>
       <c r="R18" s="33"/>
@@ -13411,21 +13414,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="139"/>
+      <c r="A19" s="134"/>
       <c r="B19" s="91"/>
-      <c r="C19" s="140"/>
+      <c r="C19" s="135"/>
       <c r="D19" s="91"/>
-      <c r="E19" s="140"/>
+      <c r="E19" s="135"/>
       <c r="F19" s="91"/>
-      <c r="G19" s="134"/>
+      <c r="G19" s="140"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91"/>
-      <c r="J19" s="134"/>
+      <c r="J19" s="140"/>
       <c r="K19" s="91"/>
-      <c r="L19" s="136"/>
+      <c r="L19" s="138"/>
       <c r="M19" s="90"/>
       <c r="N19" s="91"/>
-      <c r="O19" s="136"/>
+      <c r="O19" s="138"/>
       <c r="P19" s="90"/>
       <c r="Q19" s="91"/>
       <c r="R19" s="33"/>
@@ -13439,21 +13442,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="139"/>
+      <c r="A20" s="134"/>
       <c r="B20" s="91"/>
-      <c r="C20" s="140"/>
+      <c r="C20" s="135"/>
       <c r="D20" s="91"/>
-      <c r="E20" s="140"/>
+      <c r="E20" s="135"/>
       <c r="F20" s="91"/>
-      <c r="G20" s="134"/>
+      <c r="G20" s="140"/>
       <c r="H20" s="90"/>
       <c r="I20" s="91"/>
-      <c r="J20" s="134"/>
+      <c r="J20" s="140"/>
       <c r="K20" s="91"/>
-      <c r="L20" s="136"/>
+      <c r="L20" s="138"/>
       <c r="M20" s="90"/>
       <c r="N20" s="91"/>
-      <c r="O20" s="136"/>
+      <c r="O20" s="138"/>
       <c r="P20" s="90"/>
       <c r="Q20" s="91"/>
       <c r="R20" s="33"/>
@@ -13467,21 +13470,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="139"/>
+      <c r="A21" s="134"/>
       <c r="B21" s="91"/>
-      <c r="C21" s="140"/>
+      <c r="C21" s="135"/>
       <c r="D21" s="91"/>
-      <c r="E21" s="140"/>
+      <c r="E21" s="135"/>
       <c r="F21" s="91"/>
-      <c r="G21" s="134"/>
+      <c r="G21" s="140"/>
       <c r="H21" s="90"/>
       <c r="I21" s="91"/>
-      <c r="J21" s="134"/>
+      <c r="J21" s="140"/>
       <c r="K21" s="91"/>
-      <c r="L21" s="136"/>
+      <c r="L21" s="138"/>
       <c r="M21" s="90"/>
       <c r="N21" s="91"/>
-      <c r="O21" s="136"/>
+      <c r="O21" s="138"/>
       <c r="P21" s="90"/>
       <c r="Q21" s="91"/>
       <c r="R21" s="33"/>
@@ -13495,21 +13498,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="139"/>
+      <c r="A22" s="134"/>
       <c r="B22" s="91"/>
-      <c r="C22" s="140"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="91"/>
-      <c r="E22" s="140"/>
+      <c r="E22" s="135"/>
       <c r="F22" s="91"/>
-      <c r="G22" s="134"/>
+      <c r="G22" s="140"/>
       <c r="H22" s="90"/>
       <c r="I22" s="91"/>
-      <c r="J22" s="134"/>
+      <c r="J22" s="140"/>
       <c r="K22" s="91"/>
-      <c r="L22" s="136"/>
+      <c r="L22" s="138"/>
       <c r="M22" s="90"/>
       <c r="N22" s="91"/>
-      <c r="O22" s="136"/>
+      <c r="O22" s="138"/>
       <c r="P22" s="90"/>
       <c r="Q22" s="91"/>
       <c r="R22" s="33"/>
@@ -13523,21 +13526,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="139"/>
+      <c r="A23" s="134"/>
       <c r="B23" s="91"/>
-      <c r="C23" s="140"/>
+      <c r="C23" s="135"/>
       <c r="D23" s="91"/>
-      <c r="E23" s="140"/>
+      <c r="E23" s="135"/>
       <c r="F23" s="91"/>
-      <c r="G23" s="134"/>
+      <c r="G23" s="140"/>
       <c r="H23" s="90"/>
       <c r="I23" s="91"/>
-      <c r="J23" s="134"/>
+      <c r="J23" s="140"/>
       <c r="K23" s="91"/>
-      <c r="L23" s="136"/>
+      <c r="L23" s="138"/>
       <c r="M23" s="90"/>
       <c r="N23" s="91"/>
-      <c r="O23" s="136"/>
+      <c r="O23" s="138"/>
       <c r="P23" s="90"/>
       <c r="Q23" s="91"/>
       <c r="R23" s="33"/>
@@ -13551,21 +13554,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="139"/>
+      <c r="A24" s="134"/>
       <c r="B24" s="91"/>
-      <c r="C24" s="140"/>
+      <c r="C24" s="135"/>
       <c r="D24" s="91"/>
-      <c r="E24" s="140"/>
+      <c r="E24" s="135"/>
       <c r="F24" s="91"/>
-      <c r="G24" s="134"/>
+      <c r="G24" s="140"/>
       <c r="H24" s="90"/>
       <c r="I24" s="91"/>
-      <c r="J24" s="134"/>
+      <c r="J24" s="140"/>
       <c r="K24" s="91"/>
-      <c r="L24" s="136"/>
+      <c r="L24" s="138"/>
       <c r="M24" s="90"/>
       <c r="N24" s="91"/>
-      <c r="O24" s="136"/>
+      <c r="O24" s="138"/>
       <c r="P24" s="90"/>
       <c r="Q24" s="91"/>
       <c r="R24" s="33"/>
@@ -13579,21 +13582,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="139"/>
+      <c r="A25" s="134"/>
       <c r="B25" s="91"/>
-      <c r="C25" s="140"/>
+      <c r="C25" s="135"/>
       <c r="D25" s="91"/>
-      <c r="E25" s="140"/>
+      <c r="E25" s="135"/>
       <c r="F25" s="91"/>
-      <c r="G25" s="134"/>
+      <c r="G25" s="140"/>
       <c r="H25" s="90"/>
       <c r="I25" s="91"/>
-      <c r="J25" s="134"/>
+      <c r="J25" s="140"/>
       <c r="K25" s="91"/>
-      <c r="L25" s="136"/>
+      <c r="L25" s="138"/>
       <c r="M25" s="90"/>
       <c r="N25" s="91"/>
-      <c r="O25" s="136"/>
+      <c r="O25" s="138"/>
       <c r="P25" s="90"/>
       <c r="Q25" s="91"/>
       <c r="R25" s="33"/>
@@ -13607,21 +13610,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="139"/>
+      <c r="A26" s="134"/>
       <c r="B26" s="91"/>
-      <c r="C26" s="140"/>
+      <c r="C26" s="135"/>
       <c r="D26" s="91"/>
-      <c r="E26" s="140"/>
+      <c r="E26" s="135"/>
       <c r="F26" s="91"/>
-      <c r="G26" s="134"/>
+      <c r="G26" s="140"/>
       <c r="H26" s="90"/>
       <c r="I26" s="91"/>
-      <c r="J26" s="134"/>
+      <c r="J26" s="140"/>
       <c r="K26" s="91"/>
-      <c r="L26" s="136"/>
+      <c r="L26" s="138"/>
       <c r="M26" s="90"/>
       <c r="N26" s="91"/>
-      <c r="O26" s="136"/>
+      <c r="O26" s="138"/>
       <c r="P26" s="90"/>
       <c r="Q26" s="91"/>
       <c r="R26" s="33"/>
@@ -13635,21 +13638,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="139"/>
+      <c r="A27" s="134"/>
       <c r="B27" s="91"/>
-      <c r="C27" s="140"/>
+      <c r="C27" s="135"/>
       <c r="D27" s="91"/>
-      <c r="E27" s="140"/>
+      <c r="E27" s="135"/>
       <c r="F27" s="91"/>
-      <c r="G27" s="134"/>
+      <c r="G27" s="140"/>
       <c r="H27" s="90"/>
       <c r="I27" s="91"/>
-      <c r="J27" s="134"/>
+      <c r="J27" s="140"/>
       <c r="K27" s="91"/>
-      <c r="L27" s="136"/>
+      <c r="L27" s="138"/>
       <c r="M27" s="90"/>
       <c r="N27" s="91"/>
-      <c r="O27" s="136"/>
+      <c r="O27" s="138"/>
       <c r="P27" s="90"/>
       <c r="Q27" s="91"/>
       <c r="R27" s="33"/>
@@ -13663,21 +13666,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="139"/>
+      <c r="A28" s="134"/>
       <c r="B28" s="91"/>
-      <c r="C28" s="140"/>
+      <c r="C28" s="135"/>
       <c r="D28" s="91"/>
-      <c r="E28" s="140"/>
+      <c r="E28" s="135"/>
       <c r="F28" s="91"/>
-      <c r="G28" s="134"/>
+      <c r="G28" s="140"/>
       <c r="H28" s="90"/>
       <c r="I28" s="91"/>
-      <c r="J28" s="134"/>
+      <c r="J28" s="140"/>
       <c r="K28" s="91"/>
-      <c r="L28" s="136"/>
+      <c r="L28" s="138"/>
       <c r="M28" s="90"/>
       <c r="N28" s="91"/>
-      <c r="O28" s="136"/>
+      <c r="O28" s="138"/>
       <c r="P28" s="90"/>
       <c r="Q28" s="91"/>
       <c r="R28" s="33"/>
@@ -13691,21 +13694,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="139"/>
+      <c r="A29" s="134"/>
       <c r="B29" s="91"/>
-      <c r="C29" s="140"/>
+      <c r="C29" s="135"/>
       <c r="D29" s="91"/>
-      <c r="E29" s="140"/>
+      <c r="E29" s="135"/>
       <c r="F29" s="91"/>
-      <c r="G29" s="134"/>
+      <c r="G29" s="140"/>
       <c r="H29" s="90"/>
       <c r="I29" s="91"/>
-      <c r="J29" s="134"/>
+      <c r="J29" s="140"/>
       <c r="K29" s="91"/>
-      <c r="L29" s="136"/>
+      <c r="L29" s="138"/>
       <c r="M29" s="90"/>
       <c r="N29" s="91"/>
-      <c r="O29" s="136"/>
+      <c r="O29" s="138"/>
       <c r="P29" s="90"/>
       <c r="Q29" s="91"/>
       <c r="R29" s="33"/>
@@ -13719,21 +13722,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="139"/>
+      <c r="A30" s="134"/>
       <c r="B30" s="91"/>
-      <c r="C30" s="140"/>
+      <c r="C30" s="135"/>
       <c r="D30" s="91"/>
-      <c r="E30" s="140"/>
+      <c r="E30" s="135"/>
       <c r="F30" s="91"/>
-      <c r="G30" s="134"/>
+      <c r="G30" s="140"/>
       <c r="H30" s="90"/>
       <c r="I30" s="91"/>
-      <c r="J30" s="134"/>
+      <c r="J30" s="140"/>
       <c r="K30" s="91"/>
-      <c r="L30" s="136"/>
+      <c r="L30" s="138"/>
       <c r="M30" s="90"/>
       <c r="N30" s="91"/>
-      <c r="O30" s="136"/>
+      <c r="O30" s="138"/>
       <c r="P30" s="90"/>
       <c r="Q30" s="91"/>
       <c r="R30" s="33"/>
@@ -13747,23 +13750,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="142"/>
-      <c r="B31" s="117"/>
-      <c r="C31" s="143"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="143"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="135"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="135"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="116"/>
-      <c r="N31" s="117"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="116"/>
-      <c r="Q31" s="117"/>
+      <c r="A31" s="136"/>
+      <c r="B31" s="129"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="137"/>
+      <c r="F31" s="129"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="128"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="139"/>
+      <c r="M31" s="128"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="139"/>
+      <c r="P31" s="128"/>
+      <c r="Q31" s="129"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14761,6 +14764,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14785,118 +14900,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896B4C38-F260-40B7-B8C6-3A1B215D21EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37762D9D-C1A4-4087-8F69-A149C69E0A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -543,30 +543,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1.従業員は削除したいタスクに対応したラジオボタンを選択する
-（従業員本人が担当者でないタスクにはラジオボタンが表示されません）
-2.従業員は「削除」ボタンを押下する
-3.システムは削除対象タスクを取得し、以下の内容を確認する
-・選択されたタスクがデータベース上に存在していること
-・削除対象タスクの担当者とログインユーザが一致していること
-4.システムはタスク削除確認画面を表示する
-（この際、削除対象タスクの情報を表示する）
-5.従業員は「削除実行」ボタンを押下する
-6.システムは以下の内容を確認する
-・削除対象タスクが存在していること
-・削除対象タスクの担当者とログインユーザが一致していること
-7.システムは選択されたタスクをデータベースから削除する
-8.システムはタスク削除完了画面を表示する
-</t>
-    <rPh sb="228" eb="230">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="350" eb="352">
-      <t>カンリョウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t xml:space="preserve">
 A1.タスク一覧表示画面にて、タスク未選択で削除ボタンを押下した場合
 A1-1.基本フロー2において、システムはタスク未選択を検出する
@@ -590,6 +566,30 @@
 A4-2.システムはタスク一覧表示画面を表示する
 A4-3.従業員は必要に応じて本ユースケースを再実行する
 </t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.従業員は削除したいタスクに対応したラジオボタンを選択する
+（従業員本人が担当者でないタスクにはラジオボタンが表示されません）
+2.従業員は「削除」ボタンを押下する
+3.システムは削除対象タスクを取得し、以下の内容を確認する
+・削除対象タスクがデータベース上に存在していること
+・削除対象タスクの担当者とログインユーザが一致していること
+4.システムはタスク削除確認画面を表示する
+（この際、削除対象タスクの情報を表示する）
+5.従業員は「削除実行」ボタンを押下する
+6.システムは以下の内容を確認する
+・削除対象タスクが存在していること
+・削除対象タスクの担当者とログインユーザが一致していること
+7.システムは削除対象タスクをデータベースから削除する
+8.システムはタスク削除完了画面を表示する
+</t>
+    <rPh sb="227" eb="229">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="348" eb="350">
+      <t>カンリョウ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1470,22 +1470,67 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1496,15 +1541,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1551,15 +1587,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1569,59 +1596,32 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1695,11 +1695,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1722,40 +1752,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1764,29 +1779,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4448,19 +4448,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="79"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="79"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4472,194 +4472,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="86">
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46183</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="76"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="61"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="44" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="47" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
     </row>
     <row r="9" spans="1:10" ht="297" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="47" t="s">
+      <c r="C9" s="56"/>
+      <c r="D9" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="88"/>
+    </row>
+    <row r="10" spans="1:10" ht="409.5" customHeight="1">
+      <c r="A10" s="78"/>
+      <c r="B10" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="86" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
-    </row>
-    <row r="10" spans="1:10" ht="409.5" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="88"/>
     </row>
     <row r="11" spans="1:10" ht="231" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="79"/>
+      <c r="B11" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="47" t="s">
+      <c r="C11" s="56"/>
+      <c r="D11" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="88"/>
     </row>
     <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="65" t="s">
+      <c r="A12" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="44" t="s">
+      <c r="B12" s="58"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="46"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
     </row>
     <row r="13" spans="1:10" ht="47.25" customHeight="1" thickBot="1">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="38" t="s">
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="80" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="82"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5650,17 +5650,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -5669,14 +5666,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5700,11 +5700,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -5722,13 +5722,13 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="80"/>
+      <c r="D2" s="40"/>
       <c r="E2" s="110"/>
-      <c r="F2" s="80"/>
+      <c r="F2" s="40"/>
       <c r="G2" s="110"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="75"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -7113,11 +7113,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -7135,21 +7135,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="40" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="86">
+      <c r="H2" s="46">
         <v>46190</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -8529,11 +8529,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -8551,21 +8551,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="40" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="86">
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -8592,23 +8592,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="120"/>
+      <c r="B5" s="130"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="131"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="123" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="90"/>
@@ -8622,16 +8622,16 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="104"/>
@@ -8643,7 +8643,7 @@
       <c r="G8" s="93"/>
       <c r="H8" s="93"/>
       <c r="I8" s="93"/>
-      <c r="J8" s="118"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="104"/>
@@ -8655,7 +8655,7 @@
       <c r="G9" s="93"/>
       <c r="H9" s="93"/>
       <c r="I9" s="93"/>
-      <c r="J9" s="118"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="104"/>
@@ -8667,7 +8667,7 @@
       <c r="G10" s="93"/>
       <c r="H10" s="93"/>
       <c r="I10" s="93"/>
-      <c r="J10" s="118"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="104"/>
@@ -8679,7 +8679,7 @@
       <c r="G11" s="93"/>
       <c r="H11" s="93"/>
       <c r="I11" s="93"/>
-      <c r="J11" s="118"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="104"/>
@@ -8691,7 +8691,7 @@
       <c r="G12" s="93"/>
       <c r="H12" s="93"/>
       <c r="I12" s="93"/>
-      <c r="J12" s="118"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="104"/>
@@ -8703,7 +8703,7 @@
       <c r="G13" s="93"/>
       <c r="H13" s="93"/>
       <c r="I13" s="93"/>
-      <c r="J13" s="118"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
       <c r="A14" s="104"/>
@@ -8715,7 +8715,7 @@
       <c r="G14" s="93"/>
       <c r="H14" s="93"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
       <c r="A15" s="104"/>
@@ -8727,7 +8727,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="118"/>
+      <c r="J15" s="128"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
       <c r="A16" s="104"/>
@@ -8739,7 +8739,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="128"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -8751,7 +8751,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="128"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -8763,7 +8763,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="128"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="104"/>
@@ -8775,10 +8775,10 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="128"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="123" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="90"/>
@@ -8792,12 +8792,12 @@
       <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="123" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="90"/>
       <c r="C21" s="91"/>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="59" t="s">
         <v>75</v>
       </c>
       <c r="E21" s="90"/>
@@ -8812,7 +8812,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="123" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="90"/>
@@ -8829,18 +8829,18 @@
       <c r="G22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="122" t="s">
+      <c r="H22" s="124" t="s">
         <v>19</v>
       </c>
       <c r="I22" s="90"/>
       <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="124"/>
-      <c r="C23" s="125"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
       <c r="D23" s="17" t="s">
         <v>80</v>
       </c>
@@ -8853,18 +8853,18 @@
       <c r="G23" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="59" t="s">
         <v>91</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="123" t="s">
+      <c r="A24" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="124"/>
-      <c r="C24" s="125"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
       <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
@@ -8877,71 +8877,71 @@
       <c r="G24" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="59" t="s">
         <v>92</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="123"/>
-      <c r="B25" s="124"/>
-      <c r="C25" s="125"/>
+      <c r="A25" s="120"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="122"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
+      <c r="H25" s="59"/>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="126"/>
+      <c r="A26" s="113"/>
       <c r="B26" s="90"/>
       <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
+      <c r="H26" s="59"/>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="126"/>
+      <c r="A27" s="113"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
+      <c r="H27" s="59"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="126"/>
+      <c r="A28" s="113"/>
       <c r="B28" s="90"/>
       <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
+      <c r="H28" s="59"/>
       <c r="I28" s="90"/>
       <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="127"/>
-      <c r="B29" s="128"/>
-      <c r="C29" s="129"/>
+      <c r="A29" s="115"/>
+      <c r="B29" s="116"/>
+      <c r="C29" s="117"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="130"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="131"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="119"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9922,22 +9922,6 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9953,6 +9937,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9980,11 +9980,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -10002,21 +10002,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="40" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="86">
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -10043,23 +10043,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="120"/>
+      <c r="B5" s="130"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="131"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="123" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="90"/>
@@ -10073,18 +10073,18 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115" t="e" vm="1">
+      <c r="A7" s="125" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="132"/>
@@ -10096,7 +10096,7 @@
       <c r="G8" s="133"/>
       <c r="H8" s="133"/>
       <c r="I8" s="133"/>
-      <c r="J8" s="118"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="132"/>
@@ -10108,7 +10108,7 @@
       <c r="G9" s="133"/>
       <c r="H9" s="133"/>
       <c r="I9" s="133"/>
-      <c r="J9" s="118"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="132"/>
@@ -10120,7 +10120,7 @@
       <c r="G10" s="133"/>
       <c r="H10" s="133"/>
       <c r="I10" s="133"/>
-      <c r="J10" s="118"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="132"/>
@@ -10132,7 +10132,7 @@
       <c r="G11" s="133"/>
       <c r="H11" s="133"/>
       <c r="I11" s="133"/>
-      <c r="J11" s="118"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="132"/>
@@ -10144,7 +10144,7 @@
       <c r="G12" s="133"/>
       <c r="H12" s="133"/>
       <c r="I12" s="133"/>
-      <c r="J12" s="118"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="132"/>
@@ -10156,7 +10156,7 @@
       <c r="G13" s="133"/>
       <c r="H13" s="133"/>
       <c r="I13" s="133"/>
-      <c r="J13" s="118"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="132"/>
@@ -10168,7 +10168,7 @@
       <c r="G14" s="133"/>
       <c r="H14" s="133"/>
       <c r="I14" s="133"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="104"/>
@@ -10180,7 +10180,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="118"/>
+      <c r="J15" s="128"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
       <c r="A16" s="104"/>
@@ -10192,7 +10192,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="128"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -10204,7 +10204,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="128"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -10216,7 +10216,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="128"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
       <c r="A19" s="104"/>
@@ -10228,7 +10228,7 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="128"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="104"/>
@@ -10240,10 +10240,10 @@
       <c r="G20" s="93"/>
       <c r="H20" s="93"/>
       <c r="I20" s="93"/>
-      <c r="J20" s="118"/>
+      <c r="J20" s="128"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="123" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="90"/>
@@ -10257,12 +10257,12 @@
       <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="123" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="90"/>
       <c r="C22" s="91"/>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="59" t="s">
         <v>78</v>
       </c>
       <c r="E22" s="90"/>
@@ -10277,7 +10277,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="113" t="s">
+      <c r="A23" s="123" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="90"/>
@@ -10294,18 +10294,18 @@
       <c r="G23" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="122" t="s">
+      <c r="H23" s="124" t="s">
         <v>19</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="123" t="s">
+      <c r="A24" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="124"/>
-      <c r="C24" s="125"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
       <c r="D24" s="17" t="s">
         <v>80</v>
       </c>
@@ -10318,18 +10318,18 @@
       <c r="G24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="59" t="s">
         <v>88</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="123" t="s">
+      <c r="A25" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="124"/>
-      <c r="C25" s="125"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="122"/>
       <c r="D25" s="17" t="s">
         <v>83</v>
       </c>
@@ -10342,18 +10342,18 @@
       <c r="G25" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="59" t="s">
         <v>89</v>
       </c>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="123" t="s">
+      <c r="A26" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="124"/>
-      <c r="C26" s="125"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
       <c r="D26" s="17" t="s">
         <v>84</v>
       </c>
@@ -10366,59 +10366,59 @@
       <c r="G26" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="59" t="s">
         <v>90</v>
       </c>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="126"/>
+      <c r="A27" s="113"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
+      <c r="H27" s="59"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="126"/>
+      <c r="A28" s="113"/>
       <c r="B28" s="90"/>
       <c r="C28" s="91"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="44"/>
+      <c r="H28" s="59"/>
       <c r="I28" s="90"/>
       <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="126"/>
+      <c r="A29" s="113"/>
       <c r="B29" s="90"/>
       <c r="C29" s="91"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="44"/>
+      <c r="H29" s="59"/>
       <c r="I29" s="90"/>
       <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="127"/>
-      <c r="B30" s="128"/>
-      <c r="C30" s="129"/>
+      <c r="A30" s="115"/>
+      <c r="B30" s="116"/>
+      <c r="C30" s="117"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="131"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="116"/>
+      <c r="J30" s="119"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11399,22 +11399,6 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11430,6 +11414,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11457,11 +11457,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="78" t="s">
+      <c r="D1" s="38" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="78" t="s">
+      <c r="F1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -11479,21 +11479,21 @@
       <c r="A2" s="104"/>
       <c r="B2" s="93"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="80" t="s">
+      <c r="D2" s="40" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="40" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="86">
+      <c r="H2" s="46">
         <v>46188</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="75"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -11520,23 +11520,23 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="120"/>
+      <c r="B5" s="130"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="121"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="131"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="123" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="90"/>
@@ -11550,16 +11550,16 @@
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="132"/>
@@ -11571,7 +11571,7 @@
       <c r="G8" s="133"/>
       <c r="H8" s="133"/>
       <c r="I8" s="133"/>
-      <c r="J8" s="118"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="132"/>
@@ -11583,7 +11583,7 @@
       <c r="G9" s="133"/>
       <c r="H9" s="133"/>
       <c r="I9" s="133"/>
-      <c r="J9" s="118"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="132"/>
@@ -11595,7 +11595,7 @@
       <c r="G10" s="133"/>
       <c r="H10" s="133"/>
       <c r="I10" s="133"/>
-      <c r="J10" s="118"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="132"/>
@@ -11607,7 +11607,7 @@
       <c r="G11" s="133"/>
       <c r="H11" s="133"/>
       <c r="I11" s="133"/>
-      <c r="J11" s="118"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="104"/>
@@ -11619,7 +11619,7 @@
       <c r="G12" s="93"/>
       <c r="H12" s="93"/>
       <c r="I12" s="93"/>
-      <c r="J12" s="118"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="104"/>
@@ -11631,7 +11631,7 @@
       <c r="G13" s="93"/>
       <c r="H13" s="93"/>
       <c r="I13" s="93"/>
-      <c r="J13" s="118"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="104"/>
@@ -11643,7 +11643,7 @@
       <c r="G14" s="93"/>
       <c r="H14" s="93"/>
       <c r="I14" s="93"/>
-      <c r="J14" s="118"/>
+      <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="104"/>
@@ -11655,7 +11655,7 @@
       <c r="G15" s="93"/>
       <c r="H15" s="93"/>
       <c r="I15" s="93"/>
-      <c r="J15" s="118"/>
+      <c r="J15" s="128"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
       <c r="A16" s="104"/>
@@ -11667,7 +11667,7 @@
       <c r="G16" s="93"/>
       <c r="H16" s="93"/>
       <c r="I16" s="93"/>
-      <c r="J16" s="118"/>
+      <c r="J16" s="128"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
@@ -11679,7 +11679,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="93"/>
       <c r="I17" s="93"/>
-      <c r="J17" s="118"/>
+      <c r="J17" s="128"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
@@ -11691,7 +11691,7 @@
       <c r="G18" s="93"/>
       <c r="H18" s="93"/>
       <c r="I18" s="93"/>
-      <c r="J18" s="118"/>
+      <c r="J18" s="128"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="104"/>
@@ -11703,10 +11703,10 @@
       <c r="G19" s="93"/>
       <c r="H19" s="93"/>
       <c r="I19" s="93"/>
-      <c r="J19" s="118"/>
+      <c r="J19" s="128"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="123" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="90"/>
@@ -11720,12 +11720,12 @@
       <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="123" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="90"/>
       <c r="C21" s="91"/>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="59" t="s">
         <v>75</v>
       </c>
       <c r="E21" s="90"/>
@@ -11740,7 +11740,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="113" t="s">
+      <c r="A22" s="123" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="90"/>
@@ -11757,18 +11757,18 @@
       <c r="G22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="122" t="s">
+      <c r="H22" s="124" t="s">
         <v>19</v>
       </c>
       <c r="I22" s="90"/>
       <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="124"/>
-      <c r="C23" s="125"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
       <c r="D23" s="17" t="s">
         <v>81</v>
       </c>
@@ -11781,18 +11781,18 @@
       <c r="G23" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="59" t="s">
         <v>94</v>
       </c>
       <c r="I23" s="90"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="123" t="s">
+      <c r="A24" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="124"/>
-      <c r="C24" s="125"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
       <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
@@ -11805,59 +11805,59 @@
       <c r="G24" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="59" t="s">
         <v>93</v>
       </c>
       <c r="I24" s="90"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="126"/>
+      <c r="A25" s="113"/>
       <c r="B25" s="90"/>
       <c r="C25" s="91"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="44"/>
+      <c r="H25" s="59"/>
       <c r="I25" s="90"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="126"/>
+      <c r="A26" s="113"/>
       <c r="B26" s="90"/>
       <c r="C26" s="91"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="44"/>
+      <c r="H26" s="59"/>
       <c r="I26" s="90"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="126"/>
+      <c r="A27" s="113"/>
       <c r="B27" s="90"/>
       <c r="C27" s="91"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="44"/>
+      <c r="H27" s="59"/>
       <c r="I27" s="90"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="127"/>
-      <c r="B28" s="128"/>
-      <c r="C28" s="129"/>
+      <c r="A28" s="115"/>
+      <c r="B28" s="116"/>
+      <c r="C28" s="117"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="128"/>
-      <c r="J28" s="131"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="116"/>
+      <c r="J28" s="119"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12838,11 +12838,14 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12859,14 +12862,11 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12886,7 +12886,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="65" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="102"/>
@@ -12894,30 +12894,30 @@
       <c r="D1" s="102"/>
       <c r="E1" s="102"/>
       <c r="F1" s="103"/>
-      <c r="G1" s="78" t="s">
+      <c r="G1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
       <c r="J1" s="109"/>
-      <c r="K1" s="78" t="s">
+      <c r="K1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
       <c r="N1" s="109"/>
-      <c r="O1" s="78" t="s">
+      <c r="O1" s="38" t="s">
         <v>8</v>
       </c>
       <c r="P1" s="109"/>
-      <c r="Q1" s="78" t="s">
+      <c r="Q1" s="38" t="s">
         <v>9</v>
       </c>
       <c r="R1" s="109"/>
-      <c r="S1" s="78" t="s">
+      <c r="S1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="121"/>
+      <c r="T1" s="131"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="104"/>
@@ -12926,20 +12926,20 @@
       <c r="D2" s="93"/>
       <c r="E2" s="93"/>
       <c r="F2" s="105"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
       <c r="J2" s="110"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
       <c r="N2" s="110"/>
-      <c r="O2" s="80"/>
+      <c r="O2" s="40"/>
       <c r="P2" s="110"/>
-      <c r="Q2" s="80"/>
+      <c r="Q2" s="40"/>
       <c r="R2" s="110"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="117"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="127"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="104"/>
@@ -12961,7 +12961,7 @@
       <c r="Q3" s="111"/>
       <c r="R3" s="105"/>
       <c r="S3" s="111"/>
-      <c r="T3" s="118"/>
+      <c r="T3" s="128"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="106"/>
@@ -12983,36 +12983,36 @@
       <c r="Q4" s="112"/>
       <c r="R4" s="108"/>
       <c r="S4" s="112"/>
-      <c r="T4" s="142"/>
+      <c r="T4" s="138"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
       <c r="F5" s="109"/>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="120"/>
-      <c r="J5" s="120"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="120"/>
-      <c r="M5" s="120"/>
-      <c r="N5" s="120"/>
-      <c r="O5" s="120"/>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="120"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="120"/>
-      <c r="T5" s="121"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="130"/>
+      <c r="K5" s="130"/>
+      <c r="L5" s="130"/>
+      <c r="M5" s="130"/>
+      <c r="N5" s="130"/>
+      <c r="O5" s="130"/>
+      <c r="P5" s="130"/>
+      <c r="Q5" s="130"/>
+      <c r="R5" s="130"/>
+      <c r="S5" s="130"/>
+      <c r="T5" s="131"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="123" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="90"/>
@@ -13020,7 +13020,7 @@
       <c r="D6" s="90"/>
       <c r="E6" s="90"/>
       <c r="F6" s="91"/>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="59" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="90"/>
@@ -13038,7 +13038,7 @@
       <c r="T6" s="114"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="123" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="90"/>
@@ -13046,7 +13046,7 @@
       <c r="D7" s="90"/>
       <c r="E7" s="90"/>
       <c r="F7" s="91"/>
-      <c r="G7" s="44" t="s">
+      <c r="G7" s="59" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="90"/>
@@ -13260,7 +13260,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="113" t="s">
+      <c r="A15" s="123" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="91"/>
@@ -13268,25 +13268,25 @@
         <v>39</v>
       </c>
       <c r="D15" s="91"/>
-      <c r="E15" s="122" t="s">
+      <c r="E15" s="124" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="91"/>
-      <c r="G15" s="122" t="s">
+      <c r="G15" s="124" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="90"/>
       <c r="I15" s="91"/>
-      <c r="J15" s="122" t="s">
+      <c r="J15" s="124" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="91"/>
-      <c r="L15" s="122" t="s">
+      <c r="L15" s="124" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="90"/>
       <c r="N15" s="91"/>
-      <c r="O15" s="122" t="s">
+      <c r="O15" s="124" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="90"/>
@@ -13302,33 +13302,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="134">
+      <c r="A16" s="139">
         <v>1</v>
       </c>
       <c r="B16" s="91"/>
-      <c r="C16" s="135" t="s">
+      <c r="C16" s="140" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="91"/>
-      <c r="E16" s="135" t="s">
+      <c r="E16" s="140" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="91"/>
-      <c r="G16" s="140" t="s">
+      <c r="G16" s="134" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="90"/>
       <c r="I16" s="91"/>
-      <c r="J16" s="140" t="s">
+      <c r="J16" s="134" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="91"/>
-      <c r="L16" s="138" t="s">
+      <c r="L16" s="136" t="s">
         <v>58</v>
       </c>
       <c r="M16" s="90"/>
       <c r="N16" s="91"/>
-      <c r="O16" s="138" t="s">
+      <c r="O16" s="136" t="s">
         <v>59</v>
       </c>
       <c r="P16" s="90"/>
@@ -13344,33 +13344,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="134">
+      <c r="A17" s="139">
         <v>2</v>
       </c>
       <c r="B17" s="91"/>
-      <c r="C17" s="135" t="s">
+      <c r="C17" s="140" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="91"/>
-      <c r="E17" s="135" t="s">
+      <c r="E17" s="140" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="91"/>
-      <c r="G17" s="140" t="s">
+      <c r="G17" s="134" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="140" t="s">
+      <c r="J17" s="134" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="91"/>
-      <c r="L17" s="138" t="s">
+      <c r="L17" s="136" t="s">
         <v>64</v>
       </c>
       <c r="M17" s="90"/>
       <c r="N17" s="91"/>
-      <c r="O17" s="138" t="s">
+      <c r="O17" s="136" t="s">
         <v>65</v>
       </c>
       <c r="P17" s="90"/>
@@ -13386,21 +13386,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="134"/>
+      <c r="A18" s="139"/>
       <c r="B18" s="91"/>
-      <c r="C18" s="135"/>
+      <c r="C18" s="140"/>
       <c r="D18" s="91"/>
-      <c r="E18" s="135"/>
+      <c r="E18" s="140"/>
       <c r="F18" s="91"/>
-      <c r="G18" s="140"/>
+      <c r="G18" s="134"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="140"/>
+      <c r="J18" s="134"/>
       <c r="K18" s="91"/>
-      <c r="L18" s="138"/>
+      <c r="L18" s="136"/>
       <c r="M18" s="90"/>
       <c r="N18" s="91"/>
-      <c r="O18" s="138"/>
+      <c r="O18" s="136"/>
       <c r="P18" s="90"/>
       <c r="Q18" s="91"/>
       <c r="R18" s="33"/>
@@ -13414,21 +13414,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="134"/>
+      <c r="A19" s="139"/>
       <c r="B19" s="91"/>
-      <c r="C19" s="135"/>
+      <c r="C19" s="140"/>
       <c r="D19" s="91"/>
-      <c r="E19" s="135"/>
+      <c r="E19" s="140"/>
       <c r="F19" s="91"/>
-      <c r="G19" s="140"/>
+      <c r="G19" s="134"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91"/>
-      <c r="J19" s="140"/>
+      <c r="J19" s="134"/>
       <c r="K19" s="91"/>
-      <c r="L19" s="138"/>
+      <c r="L19" s="136"/>
       <c r="M19" s="90"/>
       <c r="N19" s="91"/>
-      <c r="O19" s="138"/>
+      <c r="O19" s="136"/>
       <c r="P19" s="90"/>
       <c r="Q19" s="91"/>
       <c r="R19" s="33"/>
@@ -13442,21 +13442,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="134"/>
+      <c r="A20" s="139"/>
       <c r="B20" s="91"/>
-      <c r="C20" s="135"/>
+      <c r="C20" s="140"/>
       <c r="D20" s="91"/>
-      <c r="E20" s="135"/>
+      <c r="E20" s="140"/>
       <c r="F20" s="91"/>
-      <c r="G20" s="140"/>
+      <c r="G20" s="134"/>
       <c r="H20" s="90"/>
       <c r="I20" s="91"/>
-      <c r="J20" s="140"/>
+      <c r="J20" s="134"/>
       <c r="K20" s="91"/>
-      <c r="L20" s="138"/>
+      <c r="L20" s="136"/>
       <c r="M20" s="90"/>
       <c r="N20" s="91"/>
-      <c r="O20" s="138"/>
+      <c r="O20" s="136"/>
       <c r="P20" s="90"/>
       <c r="Q20" s="91"/>
       <c r="R20" s="33"/>
@@ -13470,21 +13470,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="134"/>
+      <c r="A21" s="139"/>
       <c r="B21" s="91"/>
-      <c r="C21" s="135"/>
+      <c r="C21" s="140"/>
       <c r="D21" s="91"/>
-      <c r="E21" s="135"/>
+      <c r="E21" s="140"/>
       <c r="F21" s="91"/>
-      <c r="G21" s="140"/>
+      <c r="G21" s="134"/>
       <c r="H21" s="90"/>
       <c r="I21" s="91"/>
-      <c r="J21" s="140"/>
+      <c r="J21" s="134"/>
       <c r="K21" s="91"/>
-      <c r="L21" s="138"/>
+      <c r="L21" s="136"/>
       <c r="M21" s="90"/>
       <c r="N21" s="91"/>
-      <c r="O21" s="138"/>
+      <c r="O21" s="136"/>
       <c r="P21" s="90"/>
       <c r="Q21" s="91"/>
       <c r="R21" s="33"/>
@@ -13498,21 +13498,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="134"/>
+      <c r="A22" s="139"/>
       <c r="B22" s="91"/>
-      <c r="C22" s="135"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="91"/>
-      <c r="E22" s="135"/>
+      <c r="E22" s="140"/>
       <c r="F22" s="91"/>
-      <c r="G22" s="140"/>
+      <c r="G22" s="134"/>
       <c r="H22" s="90"/>
       <c r="I22" s="91"/>
-      <c r="J22" s="140"/>
+      <c r="J22" s="134"/>
       <c r="K22" s="91"/>
-      <c r="L22" s="138"/>
+      <c r="L22" s="136"/>
       <c r="M22" s="90"/>
       <c r="N22" s="91"/>
-      <c r="O22" s="138"/>
+      <c r="O22" s="136"/>
       <c r="P22" s="90"/>
       <c r="Q22" s="91"/>
       <c r="R22" s="33"/>
@@ -13526,21 +13526,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="134"/>
+      <c r="A23" s="139"/>
       <c r="B23" s="91"/>
-      <c r="C23" s="135"/>
+      <c r="C23" s="140"/>
       <c r="D23" s="91"/>
-      <c r="E23" s="135"/>
+      <c r="E23" s="140"/>
       <c r="F23" s="91"/>
-      <c r="G23" s="140"/>
+      <c r="G23" s="134"/>
       <c r="H23" s="90"/>
       <c r="I23" s="91"/>
-      <c r="J23" s="140"/>
+      <c r="J23" s="134"/>
       <c r="K23" s="91"/>
-      <c r="L23" s="138"/>
+      <c r="L23" s="136"/>
       <c r="M23" s="90"/>
       <c r="N23" s="91"/>
-      <c r="O23" s="138"/>
+      <c r="O23" s="136"/>
       <c r="P23" s="90"/>
       <c r="Q23" s="91"/>
       <c r="R23" s="33"/>
@@ -13554,21 +13554,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="134"/>
+      <c r="A24" s="139"/>
       <c r="B24" s="91"/>
-      <c r="C24" s="135"/>
+      <c r="C24" s="140"/>
       <c r="D24" s="91"/>
-      <c r="E24" s="135"/>
+      <c r="E24" s="140"/>
       <c r="F24" s="91"/>
-      <c r="G24" s="140"/>
+      <c r="G24" s="134"/>
       <c r="H24" s="90"/>
       <c r="I24" s="91"/>
-      <c r="J24" s="140"/>
+      <c r="J24" s="134"/>
       <c r="K24" s="91"/>
-      <c r="L24" s="138"/>
+      <c r="L24" s="136"/>
       <c r="M24" s="90"/>
       <c r="N24" s="91"/>
-      <c r="O24" s="138"/>
+      <c r="O24" s="136"/>
       <c r="P24" s="90"/>
       <c r="Q24" s="91"/>
       <c r="R24" s="33"/>
@@ -13582,21 +13582,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="134"/>
+      <c r="A25" s="139"/>
       <c r="B25" s="91"/>
-      <c r="C25" s="135"/>
+      <c r="C25" s="140"/>
       <c r="D25" s="91"/>
-      <c r="E25" s="135"/>
+      <c r="E25" s="140"/>
       <c r="F25" s="91"/>
-      <c r="G25" s="140"/>
+      <c r="G25" s="134"/>
       <c r="H25" s="90"/>
       <c r="I25" s="91"/>
-      <c r="J25" s="140"/>
+      <c r="J25" s="134"/>
       <c r="K25" s="91"/>
-      <c r="L25" s="138"/>
+      <c r="L25" s="136"/>
       <c r="M25" s="90"/>
       <c r="N25" s="91"/>
-      <c r="O25" s="138"/>
+      <c r="O25" s="136"/>
       <c r="P25" s="90"/>
       <c r="Q25" s="91"/>
       <c r="R25" s="33"/>
@@ -13610,21 +13610,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="134"/>
+      <c r="A26" s="139"/>
       <c r="B26" s="91"/>
-      <c r="C26" s="135"/>
+      <c r="C26" s="140"/>
       <c r="D26" s="91"/>
-      <c r="E26" s="135"/>
+      <c r="E26" s="140"/>
       <c r="F26" s="91"/>
-      <c r="G26" s="140"/>
+      <c r="G26" s="134"/>
       <c r="H26" s="90"/>
       <c r="I26" s="91"/>
-      <c r="J26" s="140"/>
+      <c r="J26" s="134"/>
       <c r="K26" s="91"/>
-      <c r="L26" s="138"/>
+      <c r="L26" s="136"/>
       <c r="M26" s="90"/>
       <c r="N26" s="91"/>
-      <c r="O26" s="138"/>
+      <c r="O26" s="136"/>
       <c r="P26" s="90"/>
       <c r="Q26" s="91"/>
       <c r="R26" s="33"/>
@@ -13638,21 +13638,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="134"/>
+      <c r="A27" s="139"/>
       <c r="B27" s="91"/>
-      <c r="C27" s="135"/>
+      <c r="C27" s="140"/>
       <c r="D27" s="91"/>
-      <c r="E27" s="135"/>
+      <c r="E27" s="140"/>
       <c r="F27" s="91"/>
-      <c r="G27" s="140"/>
+      <c r="G27" s="134"/>
       <c r="H27" s="90"/>
       <c r="I27" s="91"/>
-      <c r="J27" s="140"/>
+      <c r="J27" s="134"/>
       <c r="K27" s="91"/>
-      <c r="L27" s="138"/>
+      <c r="L27" s="136"/>
       <c r="M27" s="90"/>
       <c r="N27" s="91"/>
-      <c r="O27" s="138"/>
+      <c r="O27" s="136"/>
       <c r="P27" s="90"/>
       <c r="Q27" s="91"/>
       <c r="R27" s="33"/>
@@ -13666,21 +13666,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="134"/>
+      <c r="A28" s="139"/>
       <c r="B28" s="91"/>
-      <c r="C28" s="135"/>
+      <c r="C28" s="140"/>
       <c r="D28" s="91"/>
-      <c r="E28" s="135"/>
+      <c r="E28" s="140"/>
       <c r="F28" s="91"/>
-      <c r="G28" s="140"/>
+      <c r="G28" s="134"/>
       <c r="H28" s="90"/>
       <c r="I28" s="91"/>
-      <c r="J28" s="140"/>
+      <c r="J28" s="134"/>
       <c r="K28" s="91"/>
-      <c r="L28" s="138"/>
+      <c r="L28" s="136"/>
       <c r="M28" s="90"/>
       <c r="N28" s="91"/>
-      <c r="O28" s="138"/>
+      <c r="O28" s="136"/>
       <c r="P28" s="90"/>
       <c r="Q28" s="91"/>
       <c r="R28" s="33"/>
@@ -13694,21 +13694,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="134"/>
+      <c r="A29" s="139"/>
       <c r="B29" s="91"/>
-      <c r="C29" s="135"/>
+      <c r="C29" s="140"/>
       <c r="D29" s="91"/>
-      <c r="E29" s="135"/>
+      <c r="E29" s="140"/>
       <c r="F29" s="91"/>
-      <c r="G29" s="140"/>
+      <c r="G29" s="134"/>
       <c r="H29" s="90"/>
       <c r="I29" s="91"/>
-      <c r="J29" s="140"/>
+      <c r="J29" s="134"/>
       <c r="K29" s="91"/>
-      <c r="L29" s="138"/>
+      <c r="L29" s="136"/>
       <c r="M29" s="90"/>
       <c r="N29" s="91"/>
-      <c r="O29" s="138"/>
+      <c r="O29" s="136"/>
       <c r="P29" s="90"/>
       <c r="Q29" s="91"/>
       <c r="R29" s="33"/>
@@ -13722,21 +13722,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="134"/>
+      <c r="A30" s="139"/>
       <c r="B30" s="91"/>
-      <c r="C30" s="135"/>
+      <c r="C30" s="140"/>
       <c r="D30" s="91"/>
-      <c r="E30" s="135"/>
+      <c r="E30" s="140"/>
       <c r="F30" s="91"/>
-      <c r="G30" s="140"/>
+      <c r="G30" s="134"/>
       <c r="H30" s="90"/>
       <c r="I30" s="91"/>
-      <c r="J30" s="140"/>
+      <c r="J30" s="134"/>
       <c r="K30" s="91"/>
-      <c r="L30" s="138"/>
+      <c r="L30" s="136"/>
       <c r="M30" s="90"/>
       <c r="N30" s="91"/>
-      <c r="O30" s="138"/>
+      <c r="O30" s="136"/>
       <c r="P30" s="90"/>
       <c r="Q30" s="91"/>
       <c r="R30" s="33"/>
@@ -13750,23 +13750,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="136"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="137"/>
-      <c r="D31" s="129"/>
-      <c r="E31" s="137"/>
-      <c r="F31" s="129"/>
-      <c r="G31" s="143"/>
-      <c r="H31" s="128"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="143"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="139"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="139"/>
-      <c r="P31" s="128"/>
-      <c r="Q31" s="129"/>
+      <c r="A31" s="142"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="143"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="143"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="135"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="137"/>
+      <c r="M31" s="116"/>
+      <c r="N31" s="117"/>
+      <c r="O31" s="137"/>
+      <c r="P31" s="116"/>
+      <c r="Q31" s="117"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14764,62 +14764,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14844,62 +14844,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク削除機能_詳細設計書.xlsx
+++ b/document/タスク削除機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37762D9D-C1A4-4087-8F69-A149C69E0A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C24C55C-3637-4B85-9EBC-8FE02F43B4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -517,11 +517,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>・従業員がログインしており、タスク一覧表示画面が表示されていること。
-・削除対象のタスクがデータベースに登録されていること。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>基本フロー</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -569,6 +564,11 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>・従業員がログインしており、タスク一覧表示画面が表示されていること。
+・削除対象タスクがデータベースに登録されていること。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t xml:space="preserve">1.従業員は削除したいタスクに対応したラジオボタンを選択する
 （従業員本人が担当者でないタスクにはラジオボタンが表示されません）
 2.従業員は「削除」ボタンを押下する
@@ -579,7 +579,7 @@
 （この際、削除対象タスクの情報を表示する）
 5.従業員は「削除実行」ボタンを押下する
 6.システムは以下の内容を確認する
-・削除対象タスクが存在していること
+・削除対象タスクがデータベース上に存在していること
 ・削除対象タスクの担当者とログインユーザが一致していること
 7.システムは削除対象タスクをデータベースから削除する
 8.システムはタスク削除完了画面を表示する
@@ -587,7 +587,7 @@
     <rPh sb="227" eb="229">
       <t>ジッコウ</t>
     </rPh>
-    <rPh sb="348" eb="350">
+    <rPh sb="356" eb="358">
       <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -1470,67 +1470,46 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1541,6 +1520,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1587,6 +1575,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1596,55 +1593,58 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1695,41 +1695,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1752,25 +1722,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1779,14 +1764,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3282,85 +3282,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="93"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3380,46 +3380,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="96" t="s">
+      <c r="E8" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="89" t="s">
+      <c r="G13" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="91"/>
-      <c r="I13" s="89" t="s">
+      <c r="H13" s="40"/>
+      <c r="I13" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="90"/>
-      <c r="K13" s="91"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="89"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="91"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="40"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="89"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="91"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3428,13 +3428,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="92" t="s">
+      <c r="G17" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4448,19 +4448,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="38" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="87"/>
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="39"/>
+      <c r="G1" s="87"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -4472,194 +4472,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="40" t="s">
+      <c r="A2" s="64"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="40" t="s">
+      <c r="E2" s="89"/>
+      <c r="F2" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="46">
+      <c r="G2" s="89"/>
+      <c r="H2" s="94">
         <v>46183</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="84"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="83" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="59" t="s">
+      <c r="B6" s="74"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="61"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="59" t="s">
+      <c r="B7" s="74"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
     </row>
     <row r="8" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="86" t="s">
+      <c r="B8" s="74"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="54"/>
+    </row>
+    <row r="9" spans="1:10" ht="297" customHeight="1">
+      <c r="A9" s="76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="79" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61"/>
-    </row>
-    <row r="9" spans="1:10" ht="297" customHeight="1">
-      <c r="A9" s="77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="55" t="s">
+      <c r="C9" s="75"/>
+      <c r="D9" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="57"/>
+    </row>
+    <row r="10" spans="1:10" ht="409.5" customHeight="1">
+      <c r="A10" s="77"/>
+      <c r="B10" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="75"/>
+      <c r="D10" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="57"/>
+    </row>
+    <row r="11" spans="1:10" ht="231" customHeight="1">
+      <c r="A11" s="78"/>
+      <c r="B11" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="75"/>
+      <c r="D11" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+    </row>
+    <row r="12" spans="1:10" ht="53.25" customHeight="1">
+      <c r="A12" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="74"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="54"/>
+    </row>
+    <row r="13" spans="1:10" ht="47.25" customHeight="1" thickBot="1">
+      <c r="A13" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="59"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="86" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="88"/>
-    </row>
-    <row r="10" spans="1:10" ht="409.5" customHeight="1">
-      <c r="A10" s="78"/>
-      <c r="B10" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="88"/>
-    </row>
-    <row r="11" spans="1:10" ht="231" customHeight="1">
-      <c r="A11" s="79"/>
-      <c r="B11" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="86" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="88"/>
-    </row>
-    <row r="12" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A12" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="61"/>
-    </row>
-    <row r="13" spans="1:10" ht="47.25" customHeight="1" thickBot="1">
-      <c r="A13" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="80" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="82"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5650,6 +5650,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -5658,25 +5677,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5700,11 +5700,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="86" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -5720,19 +5720,19 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40"/>
+      <c r="D2" s="88"/>
       <c r="E2" s="110"/>
-      <c r="F2" s="40"/>
+      <c r="F2" s="88"/>
       <c r="G2" s="110"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="52"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="105"/>
       <c r="D3" s="111"/>
       <c r="E3" s="105"/>
@@ -7113,11 +7113,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="86" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -7133,27 +7133,27 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="88" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="88" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="94">
         <v>46190</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="105"/>
       <c r="D3" s="111"/>
       <c r="E3" s="105"/>
@@ -8529,11 +8529,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="86" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -8549,27 +8549,27 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="88" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="88" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="94">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="105"/>
       <c r="D3" s="111"/>
       <c r="E3" s="105"/>
@@ -8581,7 +8581,7 @@
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="104"/>
-      <c r="B4" s="93"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="105"/>
       <c r="D4" s="111"/>
       <c r="E4" s="105"/>
@@ -8592,218 +8592,218 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="130"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="131"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="125"/>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="127"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="104"/>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="128"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="104"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="128"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="104"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="128"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="104"/>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="128"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="104"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="128"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="104"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="128"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
       <c r="A14" s="104"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="128"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="24" customHeight="1">
       <c r="A15" s="104"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="128"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
       <c r="A16" s="104"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="128"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="128"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="128"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="104"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="128"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
       <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="59" t="s">
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="91"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="15" t="s">
         <v>27</v>
       </c>
@@ -8812,11 +8812,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="123" t="s">
+      <c r="A22" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="15" t="s">
         <v>29</v>
       </c>
@@ -8829,18 +8829,18 @@
       <c r="G22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="124" t="s">
+      <c r="H22" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="90"/>
+      <c r="I22" s="39"/>
       <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="121"/>
-      <c r="C23" s="122"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
       <c r="D23" s="17" t="s">
         <v>80</v>
       </c>
@@ -8853,18 +8853,18 @@
       <c r="G23" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="59" t="s">
+      <c r="H23" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="I23" s="90"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="122"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
@@ -8877,71 +8877,71 @@
       <c r="G24" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="I24" s="90"/>
+      <c r="I24" s="39"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="120"/>
-      <c r="B25" s="121"/>
-      <c r="C25" s="122"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="90"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="113"/>
-      <c r="B26" s="90"/>
-      <c r="C26" s="91"/>
+      <c r="A26" s="126"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="90"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="39"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="91"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="90"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="39"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="113"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="91"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="90"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="39"/>
       <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="115"/>
-      <c r="B29" s="116"/>
-      <c r="C29" s="117"/>
+      <c r="A29" s="127"/>
+      <c r="B29" s="128"/>
+      <c r="C29" s="129"/>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="119"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="128"/>
+      <c r="J29" s="131"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9922,6 +9922,22 @@
     <row r="1006" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A7:J19"/>
@@ -9937,22 +9953,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D21:H21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9980,11 +9980,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="86" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -10000,27 +10000,27 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="88" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="88" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="94">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="105"/>
       <c r="D3" s="111"/>
       <c r="E3" s="105"/>
@@ -10032,7 +10032,7 @@
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="104"/>
-      <c r="B4" s="93"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="105"/>
       <c r="D4" s="111"/>
       <c r="E4" s="105"/>
@@ -10043,48 +10043,48 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="130"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="131"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="125" t="e" vm="1">
+      <c r="A7" s="115" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="127"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="132"/>
@@ -10096,7 +10096,7 @@
       <c r="G8" s="133"/>
       <c r="H8" s="133"/>
       <c r="I8" s="133"/>
-      <c r="J8" s="128"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="132"/>
@@ -10108,7 +10108,7 @@
       <c r="G9" s="133"/>
       <c r="H9" s="133"/>
       <c r="I9" s="133"/>
-      <c r="J9" s="128"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="132"/>
@@ -10120,7 +10120,7 @@
       <c r="G10" s="133"/>
       <c r="H10" s="133"/>
       <c r="I10" s="133"/>
-      <c r="J10" s="128"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="132"/>
@@ -10132,7 +10132,7 @@
       <c r="G11" s="133"/>
       <c r="H11" s="133"/>
       <c r="I11" s="133"/>
-      <c r="J11" s="128"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="132"/>
@@ -10144,7 +10144,7 @@
       <c r="G12" s="133"/>
       <c r="H12" s="133"/>
       <c r="I12" s="133"/>
-      <c r="J12" s="128"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="132"/>
@@ -10156,7 +10156,7 @@
       <c r="G13" s="133"/>
       <c r="H13" s="133"/>
       <c r="I13" s="133"/>
-      <c r="J13" s="128"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="132"/>
@@ -10168,107 +10168,107 @@
       <c r="G14" s="133"/>
       <c r="H14" s="133"/>
       <c r="I14" s="133"/>
-      <c r="J14" s="128"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="104"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="128"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
       <c r="A16" s="104"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="128"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="128"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="128"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="21" customHeight="1">
       <c r="A19" s="104"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="128"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="104"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="128"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="118"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
       <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="123" t="s">
+      <c r="A22" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="59" t="s">
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="91"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
       <c r="I22" s="15" t="s">
         <v>27</v>
       </c>
@@ -10277,11 +10277,11 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="123" t="s">
+      <c r="A23" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="90"/>
-      <c r="C23" s="91"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="15" t="s">
         <v>29</v>
       </c>
@@ -10294,18 +10294,18 @@
       <c r="G23" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="124" t="s">
+      <c r="H23" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="90"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="122"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>80</v>
       </c>
@@ -10318,18 +10318,18 @@
       <c r="G24" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="I24" s="90"/>
+      <c r="I24" s="39"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="120" t="s">
+      <c r="A25" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="121"/>
-      <c r="C25" s="122"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="125"/>
       <c r="D25" s="17" t="s">
         <v>83</v>
       </c>
@@ -10342,18 +10342,18 @@
       <c r="G25" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H25" s="59" t="s">
+      <c r="H25" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="I25" s="90"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="120" t="s">
+      <c r="A26" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="121"/>
-      <c r="C26" s="122"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="125"/>
       <c r="D26" s="17" t="s">
         <v>84</v>
       </c>
@@ -10366,59 +10366,59 @@
       <c r="G26" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H26" s="59" t="s">
+      <c r="H26" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="I26" s="90"/>
+      <c r="I26" s="39"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="91"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="90"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="39"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="113"/>
-      <c r="B28" s="90"/>
-      <c r="C28" s="91"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="90"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="39"/>
       <c r="J28" s="114"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="113"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="91"/>
+      <c r="A29" s="126"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="90"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="39"/>
       <c r="J29" s="114"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A30" s="115"/>
-      <c r="B30" s="116"/>
-      <c r="C30" s="117"/>
+      <c r="A30" s="127"/>
+      <c r="B30" s="128"/>
+      <c r="C30" s="129"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="116"/>
-      <c r="J30" s="119"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="128"/>
+      <c r="J30" s="131"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11399,6 +11399,22 @@
     <row r="1007" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J20"/>
@@ -11414,22 +11430,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D22:H22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11457,11 +11457,11 @@
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="103"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="86" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="109"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="86" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="109"/>
@@ -11477,27 +11477,27 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
+      <c r="B2" s="42"/>
       <c r="C2" s="105"/>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="88" t="s">
         <v>66</v>
       </c>
       <c r="E2" s="110"/>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="88" t="s">
         <v>67</v>
       </c>
       <c r="G2" s="110"/>
-      <c r="H2" s="46">
+      <c r="H2" s="94">
         <v>46188</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="83"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
+      <c r="B3" s="42"/>
       <c r="C3" s="105"/>
       <c r="D3" s="111"/>
       <c r="E3" s="105"/>
@@ -11509,7 +11509,7 @@
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="104"/>
-      <c r="B4" s="93"/>
+      <c r="B4" s="42"/>
       <c r="C4" s="105"/>
       <c r="D4" s="111"/>
       <c r="E4" s="105"/>
@@ -11520,46 +11520,46 @@
       <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="130"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="109"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="131"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="121"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
       <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="125"/>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="127"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="132"/>
@@ -11571,7 +11571,7 @@
       <c r="G8" s="133"/>
       <c r="H8" s="133"/>
       <c r="I8" s="133"/>
-      <c r="J8" s="128"/>
+      <c r="J8" s="118"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="132"/>
@@ -11583,7 +11583,7 @@
       <c r="G9" s="133"/>
       <c r="H9" s="133"/>
       <c r="I9" s="133"/>
-      <c r="J9" s="128"/>
+      <c r="J9" s="118"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="132"/>
@@ -11595,7 +11595,7 @@
       <c r="G10" s="133"/>
       <c r="H10" s="133"/>
       <c r="I10" s="133"/>
-      <c r="J10" s="128"/>
+      <c r="J10" s="118"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="132"/>
@@ -11607,131 +11607,131 @@
       <c r="G11" s="133"/>
       <c r="H11" s="133"/>
       <c r="I11" s="133"/>
-      <c r="J11" s="128"/>
+      <c r="J11" s="118"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="104"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="128"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="118"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="104"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="128"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="118"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
       <c r="A14" s="104"/>
-      <c r="B14" s="93"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
-      <c r="I14" s="93"/>
-      <c r="J14" s="128"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="118"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
       <c r="A15" s="104"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="93"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="93"/>
-      <c r="J15" s="128"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="118"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
       <c r="A16" s="104"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="93"/>
-      <c r="F16" s="93"/>
-      <c r="G16" s="93"/>
-      <c r="H16" s="93"/>
-      <c r="I16" s="93"/>
-      <c r="J16" s="128"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="118"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="104"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="93"/>
-      <c r="G17" s="93"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="128"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
       <c r="A18" s="104"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="93"/>
-      <c r="E18" s="93"/>
-      <c r="F18" s="93"/>
-      <c r="G18" s="93"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="93"/>
-      <c r="J18" s="128"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="118"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="104"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="128"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="118"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
       <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="59" t="s">
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="91"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="15" t="s">
         <v>27</v>
       </c>
@@ -11740,11 +11740,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="123" t="s">
+      <c r="A22" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="15" t="s">
         <v>29</v>
       </c>
@@ -11757,18 +11757,18 @@
       <c r="G22" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="124" t="s">
+      <c r="H22" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="90"/>
+      <c r="I22" s="39"/>
       <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="120" t="s">
+      <c r="A23" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="121"/>
-      <c r="C23" s="122"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
       <c r="D23" s="17" t="s">
         <v>81</v>
       </c>
@@ -11781,18 +11781,18 @@
       <c r="G23" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="59" t="s">
+      <c r="H23" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="I23" s="90"/>
+      <c r="I23" s="39"/>
       <c r="J23" s="114"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="121"/>
-      <c r="C24" s="122"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="125"/>
       <c r="D24" s="17" t="s">
         <v>82</v>
       </c>
@@ -11805,59 +11805,59 @@
       <c r="G24" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="59" t="s">
+      <c r="H24" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="I24" s="90"/>
+      <c r="I24" s="39"/>
       <c r="J24" s="114"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="113"/>
-      <c r="B25" s="90"/>
-      <c r="C25" s="91"/>
+      <c r="A25" s="126"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="90"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="39"/>
       <c r="J25" s="114"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="113"/>
-      <c r="B26" s="90"/>
-      <c r="C26" s="91"/>
+      <c r="A26" s="126"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="90"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="39"/>
       <c r="J26" s="114"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="113"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="91"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="90"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="39"/>
       <c r="J27" s="114"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="115"/>
-      <c r="B28" s="116"/>
-      <c r="C28" s="117"/>
+      <c r="A28" s="127"/>
+      <c r="B28" s="128"/>
+      <c r="C28" s="129"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="119"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="131"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12838,14 +12838,11 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12862,11 +12859,14 @@
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12886,7 +12886,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="61" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="102"/>
@@ -12894,74 +12894,74 @@
       <c r="D1" s="102"/>
       <c r="E1" s="102"/>
       <c r="F1" s="103"/>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
       <c r="J1" s="109"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
       <c r="N1" s="109"/>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="86" t="s">
         <v>8</v>
       </c>
       <c r="P1" s="109"/>
-      <c r="Q1" s="38" t="s">
+      <c r="Q1" s="86" t="s">
         <v>9</v>
       </c>
       <c r="R1" s="109"/>
-      <c r="S1" s="38" t="s">
+      <c r="S1" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="131"/>
+      <c r="T1" s="121"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="104"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
       <c r="F2" s="105"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
       <c r="J2" s="110"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
       <c r="N2" s="110"/>
-      <c r="O2" s="40"/>
+      <c r="O2" s="88"/>
       <c r="P2" s="110"/>
-      <c r="Q2" s="40"/>
+      <c r="Q2" s="88"/>
       <c r="R2" s="110"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="127"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="117"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="104"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
       <c r="F3" s="105"/>
       <c r="G3" s="111"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
       <c r="J3" s="105"/>
       <c r="K3" s="111"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
       <c r="N3" s="105"/>
       <c r="O3" s="111"/>
       <c r="P3" s="105"/>
       <c r="Q3" s="111"/>
       <c r="R3" s="105"/>
       <c r="S3" s="111"/>
-      <c r="T3" s="128"/>
+      <c r="T3" s="118"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="106"/>
@@ -12983,84 +12983,84 @@
       <c r="Q4" s="112"/>
       <c r="R4" s="108"/>
       <c r="S4" s="112"/>
-      <c r="T4" s="138"/>
+      <c r="T4" s="142"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
       <c r="F5" s="109"/>
-      <c r="G5" s="83" t="s">
+      <c r="G5" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="130"/>
-      <c r="Q5" s="130"/>
-      <c r="R5" s="130"/>
-      <c r="S5" s="130"/>
-      <c r="T5" s="131"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="121"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="59" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="90"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
       <c r="T6" s="114"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="123" t="s">
+      <c r="A7" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="59" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="90"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="90"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
       <c r="T7" s="114"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
@@ -13260,37 +13260,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="123" t="s">
+      <c r="A15" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="91"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="91"/>
-      <c r="E15" s="124" t="s">
+      <c r="D15" s="40"/>
+      <c r="E15" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="124" t="s">
+      <c r="F15" s="40"/>
+      <c r="G15" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="90"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="124" t="s">
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="91"/>
-      <c r="L15" s="124" t="s">
+      <c r="K15" s="40"/>
+      <c r="L15" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="90"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="124" t="s">
+      <c r="M15" s="39"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="91"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="40"/>
       <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
@@ -13302,37 +13302,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="139">
+      <c r="A16" s="134">
         <v>1</v>
       </c>
-      <c r="B16" s="91"/>
-      <c r="C16" s="140" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="91"/>
-      <c r="E16" s="140" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="135" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="91"/>
-      <c r="G16" s="134" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="90"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="134" t="s">
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="91"/>
-      <c r="L16" s="136" t="s">
+      <c r="K16" s="40"/>
+      <c r="L16" s="138" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="90"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="136" t="s">
+      <c r="M16" s="39"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="138" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="91"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -13344,37 +13344,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="139">
+      <c r="A17" s="134">
         <v>2</v>
       </c>
-      <c r="B17" s="91"/>
-      <c r="C17" s="140" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="91"/>
-      <c r="E17" s="140" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="135" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="91"/>
-      <c r="G17" s="134" t="s">
+      <c r="F17" s="40"/>
+      <c r="G17" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="90"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="134" t="s">
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="140" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="91"/>
-      <c r="L17" s="136" t="s">
+      <c r="K17" s="40"/>
+      <c r="L17" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="90"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="136" t="s">
+      <c r="M17" s="39"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="91"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="40"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -13386,23 +13386,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="139"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="140"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="91"/>
+      <c r="A18" s="134"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="138"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="138"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -13414,23 +13414,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="139"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="140"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="140"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="134"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="91"/>
+      <c r="A19" s="134"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="138"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="138"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -13442,23 +13442,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="139"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="91"/>
+      <c r="A20" s="134"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="138"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -13470,23 +13470,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="139"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="140"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="91"/>
+      <c r="A21" s="134"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="138"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="138"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -13498,23 +13498,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="139"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="140"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="91"/>
+      <c r="A22" s="134"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="138"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -13526,23 +13526,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="139"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="136"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="91"/>
+      <c r="A23" s="134"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="138"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -13554,23 +13554,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="139"/>
-      <c r="B24" s="91"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="134"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="136"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="136"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="91"/>
+      <c r="A24" s="134"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="138"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="138"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -13582,23 +13582,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="139"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="91"/>
+      <c r="A25" s="134"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="138"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="138"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -13610,23 +13610,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="139"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="90"/>
-      <c r="Q26" s="91"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -13638,23 +13638,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="139"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="134"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="91"/>
+      <c r="A27" s="134"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="138"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="138"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -13666,23 +13666,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="139"/>
-      <c r="B28" s="91"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="134"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="90"/>
-      <c r="Q28" s="91"/>
+      <c r="A28" s="134"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="135"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="140"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -13694,23 +13694,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="139"/>
-      <c r="B29" s="91"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="134"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="136"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="91"/>
+      <c r="A29" s="134"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="140"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -13722,23 +13722,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="139"/>
-      <c r="B30" s="91"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="134"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="90"/>
-      <c r="N30" s="91"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="90"/>
-      <c r="Q30" s="91"/>
+      <c r="A30" s="134"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="140"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="138"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="138"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -13750,23 +13750,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="142"/>
-      <c r="B31" s="117"/>
-      <c r="C31" s="143"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="143"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="135"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="135"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="116"/>
-      <c r="N31" s="117"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="116"/>
-      <c r="Q31" s="117"/>
+      <c r="A31" s="136"/>
+      <c r="B31" s="129"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="137"/>
+      <c r="F31" s="129"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="128"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="139"/>
+      <c r="M31" s="128"/>
+      <c r="N31" s="129"/>
+      <c r="O31" s="139"/>
+      <c r="P31" s="128"/>
+      <c r="Q31" s="129"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -14764,6 +14764,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14788,118 +14900,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
